--- a/Ams.WebApi/wwwroot/data.xlsx
+++ b/Ams.WebApi/wwwroot/data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\App Develop\VS2024\Lean.Ams\Ams.WebApi\wwwroot\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Mine\public\ZrAdminNet\ZR.Admin.WebApi\wwwroot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8B8A364-0AD7-49C0-BF54-ED00B7AD99B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEFD95FC-F6A7-4CC2-9BD6-1E869E04FC2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="30" windowWidth="28770" windowHeight="15450" tabRatio="849" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" tabRatio="849" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="user" sheetId="2" r:id="rId1"/>
@@ -22,10 +22,11 @@
     <sheet name="task" sheetId="8" r:id="rId7"/>
     <sheet name="post" sheetId="5" r:id="rId8"/>
     <sheet name="dict_type" sheetId="9" r:id="rId9"/>
-    <sheet name="dept" sheetId="11" r:id="rId10"/>
-    <sheet name="dict_data" sheetId="10" r:id="rId11"/>
+    <sheet name="dict_data" sheetId="10" r:id="rId10"/>
+    <sheet name="dept" sheetId="11" r:id="rId11"/>
     <sheet name="article_category" sheetId="12" r:id="rId12"/>
-    <sheet name="notice" sheetId="13" r:id="rId13"/>
+    <sheet name="article_topic" sheetId="14" r:id="rId13"/>
+    <sheet name="notice" sheetId="13" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">menu!$A$1:$A$118</definedName>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1059" uniqueCount="678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="695">
   <si>
     <t>系统管理</t>
   </si>
@@ -933,6 +934,10 @@
     <t>Visible</t>
   </si>
   <si>
+    <t>Status</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Perms</t>
   </si>
   <si>
@@ -975,6 +980,12 @@
     <t>Sex</t>
   </si>
   <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>DelFlag</t>
+  </si>
+  <si>
     <t>DeptId</t>
   </si>
   <si>
@@ -1010,6 +1021,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>DelFlag</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>DataScope</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1070,9 +1085,6 @@
     <t>sys.account.register</t>
   </si>
   <si>
-    <t>文章预览地址</t>
-  </si>
-  <si>
     <t>ConfigId</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2242,11 +2254,66 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>IsStated</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsDeleted</t>
+    <t>TopicName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JoinNum</t>
+  </si>
+  <si>
+    <t>美食</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>健身</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吃什么</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交友</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宠物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>允许评论</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>article.comment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0、全放开1、绑定手机号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>允许发布内容</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>article.publish</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>官方圈子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内容目录类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>article_category_type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>圈子</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2470,9 +2537,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2510,7 +2577,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2616,7 +2683,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2758,7 +2825,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2767,53 +2834,53 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D00AC0F-0226-4E9A-8157-8C2F558D581D}">
   <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="10" max="10" width="33.375" customWidth="1"/>
+    <col min="10" max="10" width="33.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F1" t="s">
+        <v>316</v>
+      </c>
+      <c r="G1" t="s">
+        <v>311</v>
+      </c>
+      <c r="H1" t="s">
         <v>312</v>
       </c>
-      <c r="C1" t="s">
-        <v>306</v>
-      </c>
-      <c r="D1" t="s">
-        <v>307</v>
-      </c>
-      <c r="E1" t="s">
-        <v>308</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
+        <v>310</v>
+      </c>
+      <c r="J1" t="s">
+        <v>522</v>
+      </c>
+      <c r="K1" t="s">
         <v>313</v>
       </c>
-      <c r="G1" t="s">
-        <v>310</v>
-      </c>
-      <c r="H1" t="s">
-        <v>311</v>
-      </c>
-      <c r="I1" t="s">
-        <v>309</v>
-      </c>
-      <c r="J1" t="s">
-        <v>519</v>
-      </c>
-      <c r="K1" t="s">
-        <v>676</v>
-      </c>
       <c r="L1" t="s">
-        <v>677</v>
+        <v>314</v>
       </c>
       <c r="M1" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2821,7 +2888,7 @@
         <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -2830,27 +2897,27 @@
         <v>0</v>
       </c>
       <c r="J2" t="s">
+        <v>304</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2" t="s">
         <v>303</v>
       </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D3" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -2859,7 +2926,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -2868,18 +2935,18 @@
         <v>0</v>
       </c>
       <c r="M3" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="D4" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -2888,7 +2955,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -2897,7 +2964,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
     </row>
   </sheetData>
@@ -2908,34 +2975,1285 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66E508F4-5906-4688-BE06-7243F5B00B2A}">
+  <dimension ref="A1:K44"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="8.6640625" style="12"/>
+    <col min="5" max="5" width="20.08203125" customWidth="1"/>
+    <col min="10" max="10" width="12.9140625" customWidth="1"/>
+    <col min="11" max="11" width="19.08203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>506</v>
+      </c>
+      <c r="B1" t="s">
+        <v>507</v>
+      </c>
+      <c r="C1" t="s">
+        <v>508</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>509</v>
+      </c>
+      <c r="E1" t="s">
+        <v>502</v>
+      </c>
+      <c r="F1" t="s">
+        <v>510</v>
+      </c>
+      <c r="G1" t="s">
+        <v>511</v>
+      </c>
+      <c r="H1" t="s">
+        <v>512</v>
+      </c>
+      <c r="I1" t="s">
+        <v>298</v>
+      </c>
+      <c r="J1" t="s">
+        <v>317</v>
+      </c>
+      <c r="K1" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>441</v>
+      </c>
+      <c r="D2" s="12">
+        <v>0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>407</v>
+      </c>
+      <c r="H2" t="s">
+        <v>332</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2" t="s">
+        <v>442</v>
+      </c>
+      <c r="K2" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>443</v>
+      </c>
+      <c r="D3" s="12">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>407</v>
+      </c>
+      <c r="H3" t="s">
+        <v>444</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3" t="s">
+        <v>445</v>
+      </c>
+      <c r="K3" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>446</v>
+      </c>
+      <c r="D4" s="12">
+        <v>2</v>
+      </c>
+      <c r="E4" t="s">
+        <v>407</v>
+      </c>
+      <c r="H4" t="s">
+        <v>444</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4" t="s">
+        <v>447</v>
+      </c>
+      <c r="K4" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>448</v>
+      </c>
+      <c r="D5" s="12">
+        <v>0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>410</v>
+      </c>
+      <c r="G5" t="s">
+        <v>449</v>
+      </c>
+      <c r="H5" t="s">
+        <v>332</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5" t="s">
+        <v>450</v>
+      </c>
+      <c r="K5" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>451</v>
+      </c>
+      <c r="D6" s="12">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>410</v>
+      </c>
+      <c r="G6" t="s">
+        <v>452</v>
+      </c>
+      <c r="H6" t="s">
+        <v>444</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6" t="s">
+        <v>453</v>
+      </c>
+      <c r="K6" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>454</v>
+      </c>
+      <c r="D7" s="12">
+        <v>0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>413</v>
+      </c>
+      <c r="G7" t="s">
+        <v>449</v>
+      </c>
+      <c r="H7" t="s">
+        <v>332</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7" t="s">
+        <v>455</v>
+      </c>
+      <c r="K7" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>456</v>
+      </c>
+      <c r="D8" s="12">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>413</v>
+      </c>
+      <c r="G8" t="s">
+        <v>452</v>
+      </c>
+      <c r="H8" t="s">
+        <v>444</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8" t="s">
+        <v>457</v>
+      </c>
+      <c r="K8" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>454</v>
+      </c>
+      <c r="D9" s="12">
+        <v>0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>416</v>
+      </c>
+      <c r="G9" t="s">
+        <v>449</v>
+      </c>
+      <c r="H9" t="s">
+        <v>332</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9" t="s">
+        <v>455</v>
+      </c>
+      <c r="K9" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10" t="s">
+        <v>458</v>
+      </c>
+      <c r="D10" s="12">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>416</v>
+      </c>
+      <c r="G10" t="s">
+        <v>452</v>
+      </c>
+      <c r="H10" t="s">
+        <v>444</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10" t="s">
+        <v>457</v>
+      </c>
+      <c r="K10" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>459</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>460</v>
+      </c>
+      <c r="E11" t="s">
+        <v>419</v>
+      </c>
+      <c r="H11" t="s">
+        <v>332</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11" t="s">
+        <v>461</v>
+      </c>
+      <c r="K11" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12" t="s">
+        <v>462</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="E12" t="s">
+        <v>419</v>
+      </c>
+      <c r="H12" t="s">
+        <v>444</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12" t="s">
+        <v>463</v>
+      </c>
+      <c r="K12" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>464</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="E13" t="s">
+        <v>422</v>
+      </c>
+      <c r="G13" t="s">
+        <v>449</v>
+      </c>
+      <c r="H13" t="s">
+        <v>332</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13" t="s">
+        <v>465</v>
+      </c>
+      <c r="K13" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14" t="s">
+        <v>466</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="E14" t="s">
+        <v>422</v>
+      </c>
+      <c r="G14" t="s">
+        <v>452</v>
+      </c>
+      <c r="H14" t="s">
+        <v>444</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14" t="s">
+        <v>467</v>
+      </c>
+      <c r="K14" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>468</v>
+      </c>
+      <c r="D15" s="12">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
+        <v>425</v>
+      </c>
+      <c r="G15" t="s">
+        <v>469</v>
+      </c>
+      <c r="H15" t="s">
+        <v>332</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+      <c r="C16" t="s">
+        <v>470</v>
+      </c>
+      <c r="D16" s="12">
+        <v>2</v>
+      </c>
+      <c r="E16" t="s">
+        <v>425</v>
+      </c>
+      <c r="G16" t="s">
+        <v>471</v>
+      </c>
+      <c r="H16" t="s">
+        <v>444</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>454</v>
+      </c>
+      <c r="D17" s="12">
+        <v>0</v>
+      </c>
+      <c r="E17" t="s">
+        <v>428</v>
+      </c>
+      <c r="G17" t="s">
+        <v>449</v>
+      </c>
+      <c r="H17" t="s">
+        <v>332</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18" t="s">
+        <v>472</v>
+      </c>
+      <c r="D18" s="12">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>428</v>
+      </c>
+      <c r="G18" t="s">
+        <v>452</v>
+      </c>
+      <c r="H18" t="s">
+        <v>444</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19" t="s">
+        <v>474</v>
+      </c>
+      <c r="D19" s="12">
+        <v>0</v>
+      </c>
+      <c r="E19" t="s">
+        <v>431</v>
+      </c>
+      <c r="G19" t="s">
+        <v>475</v>
+      </c>
+      <c r="H19" t="s">
+        <v>444</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
+        <v>263</v>
+      </c>
+      <c r="D20" s="12">
+        <v>1</v>
+      </c>
+      <c r="E20" t="s">
+        <v>431</v>
+      </c>
+      <c r="G20" t="s">
+        <v>475</v>
+      </c>
+      <c r="H20" t="s">
+        <v>444</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>2</v>
+      </c>
+      <c r="C21" t="s">
+        <v>267</v>
+      </c>
+      <c r="D21" s="12">
+        <v>2</v>
+      </c>
+      <c r="E21" t="s">
+        <v>431</v>
+      </c>
+      <c r="G21" t="s">
+        <v>475</v>
+      </c>
+      <c r="H21" t="s">
+        <v>444</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>3</v>
+      </c>
+      <c r="C22" t="s">
+        <v>265</v>
+      </c>
+      <c r="D22" s="12">
+        <v>3</v>
+      </c>
+      <c r="E22" t="s">
+        <v>431</v>
+      </c>
+      <c r="G22" t="s">
+        <v>452</v>
+      </c>
+      <c r="H22" t="s">
+        <v>444</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>4</v>
+      </c>
+      <c r="C23" t="s">
+        <v>480</v>
+      </c>
+      <c r="D23" s="12">
+        <v>4</v>
+      </c>
+      <c r="E23" t="s">
+        <v>431</v>
+      </c>
+      <c r="G23" t="s">
+        <v>449</v>
+      </c>
+      <c r="H23" t="s">
+        <v>444</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>5</v>
+      </c>
+      <c r="C24" t="s">
+        <v>269</v>
+      </c>
+      <c r="D24" s="12">
+        <v>5</v>
+      </c>
+      <c r="E24" t="s">
+        <v>431</v>
+      </c>
+      <c r="G24" t="s">
+        <v>469</v>
+      </c>
+      <c r="H24" t="s">
+        <v>444</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>6</v>
+      </c>
+      <c r="C25" t="s">
+        <v>483</v>
+      </c>
+      <c r="D25" s="12">
+        <v>6</v>
+      </c>
+      <c r="E25" t="s">
+        <v>431</v>
+      </c>
+      <c r="G25" t="s">
+        <v>469</v>
+      </c>
+      <c r="H25" t="s">
+        <v>444</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>7</v>
+      </c>
+      <c r="C26" t="s">
+        <v>485</v>
+      </c>
+      <c r="D26" s="12">
+        <v>7</v>
+      </c>
+      <c r="E26" t="s">
+        <v>431</v>
+      </c>
+      <c r="G26" t="s">
+        <v>452</v>
+      </c>
+      <c r="H26" t="s">
+        <v>444</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>8</v>
+      </c>
+      <c r="C27" t="s">
+        <v>247</v>
+      </c>
+      <c r="D27" s="12">
+        <v>8</v>
+      </c>
+      <c r="E27" t="s">
+        <v>431</v>
+      </c>
+      <c r="G27" t="s">
+        <v>469</v>
+      </c>
+      <c r="H27" t="s">
+        <v>444</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>9</v>
+      </c>
+      <c r="C28" t="s">
+        <v>488</v>
+      </c>
+      <c r="D28" s="12">
+        <v>9</v>
+      </c>
+      <c r="E28" t="s">
+        <v>431</v>
+      </c>
+      <c r="G28" t="s">
+        <v>452</v>
+      </c>
+      <c r="H28" t="s">
+        <v>444</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>490</v>
+      </c>
+      <c r="D29" s="12">
+        <v>0</v>
+      </c>
+      <c r="E29" t="s">
+        <v>434</v>
+      </c>
+      <c r="G29" t="s">
+        <v>449</v>
+      </c>
+      <c r="H29" t="s">
+        <v>444</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>2</v>
+      </c>
+      <c r="C30" t="s">
+        <v>491</v>
+      </c>
+      <c r="D30" s="12">
+        <v>1</v>
+      </c>
+      <c r="E30" t="s">
+        <v>434</v>
+      </c>
+      <c r="G30" t="s">
+        <v>452</v>
+      </c>
+      <c r="H30" t="s">
+        <v>524</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
+        <v>492</v>
+      </c>
+      <c r="D31" s="12">
+        <v>1</v>
+      </c>
+      <c r="E31" t="s">
+        <v>437</v>
+      </c>
+      <c r="H31" t="s">
+        <v>524</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>2</v>
+      </c>
+      <c r="C32" t="s">
+        <v>493</v>
+      </c>
+      <c r="D32" s="12">
+        <v>2</v>
+      </c>
+      <c r="E32" t="s">
+        <v>437</v>
+      </c>
+      <c r="H32" t="s">
+        <v>524</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
+        <v>494</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>495</v>
+      </c>
+      <c r="E33" t="s">
+        <v>439</v>
+      </c>
+      <c r="H33" t="s">
+        <v>524</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>2</v>
+      </c>
+      <c r="C34" t="s">
+        <v>496</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>497</v>
+      </c>
+      <c r="E34" t="s">
+        <v>439</v>
+      </c>
+      <c r="H34" t="s">
+        <v>524</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>3</v>
+      </c>
+      <c r="C35" t="s">
+        <v>498</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>499</v>
+      </c>
+      <c r="E35" t="s">
+        <v>439</v>
+      </c>
+      <c r="H35" t="s">
+        <v>524</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s">
+        <v>534</v>
+      </c>
+      <c r="D36" s="12">
+        <v>1</v>
+      </c>
+      <c r="E36" t="s">
+        <v>531</v>
+      </c>
+      <c r="G36" t="s">
+        <v>537</v>
+      </c>
+      <c r="H36" t="s">
+        <v>524</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>2</v>
+      </c>
+      <c r="C37" t="s">
+        <v>535</v>
+      </c>
+      <c r="D37" s="12">
+        <v>2</v>
+      </c>
+      <c r="E37" t="s">
+        <v>531</v>
+      </c>
+      <c r="G37" t="s">
+        <v>538</v>
+      </c>
+      <c r="H37" t="s">
+        <v>524</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>3</v>
+      </c>
+      <c r="C38" t="s">
+        <v>536</v>
+      </c>
+      <c r="D38" s="12">
+        <v>3</v>
+      </c>
+      <c r="E38" t="s">
+        <v>531</v>
+      </c>
+      <c r="G38" t="s">
+        <v>539</v>
+      </c>
+      <c r="H38" t="s">
+        <v>524</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39" t="s">
+        <v>664</v>
+      </c>
+      <c r="D39" s="12">
+        <v>0</v>
+      </c>
+      <c r="E39" t="s">
+        <v>662</v>
+      </c>
+      <c r="H39" t="s">
+        <v>524</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>2</v>
+      </c>
+      <c r="C40" t="s">
+        <v>677</v>
+      </c>
+      <c r="D40" s="12">
+        <v>1</v>
+      </c>
+      <c r="E40" t="s">
+        <v>662</v>
+      </c>
+      <c r="H40" t="s">
+        <v>524</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>3</v>
+      </c>
+      <c r="C41" t="s">
+        <v>665</v>
+      </c>
+      <c r="D41" s="12">
+        <v>2</v>
+      </c>
+      <c r="E41" t="s">
+        <v>662</v>
+      </c>
+      <c r="H41" t="s">
+        <v>524</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>4</v>
+      </c>
+      <c r="C42" t="s">
+        <v>676</v>
+      </c>
+      <c r="D42" s="12">
+        <v>3</v>
+      </c>
+      <c r="E42" t="s">
+        <v>662</v>
+      </c>
+      <c r="H42" t="s">
+        <v>524</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43" t="s">
+        <v>664</v>
+      </c>
+      <c r="D43" s="12">
+        <v>0</v>
+      </c>
+      <c r="E43" t="s">
+        <v>693</v>
+      </c>
+      <c r="H43" t="s">
+        <v>524</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>2</v>
+      </c>
+      <c r="C44" t="s">
+        <v>694</v>
+      </c>
+      <c r="D44" s="12">
+        <v>1</v>
+      </c>
+      <c r="E44" t="s">
+        <v>693</v>
+      </c>
+      <c r="H44" t="s">
+        <v>524</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39F8E602-C602-4DBE-8251-6DDEB8D8D144}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="B1" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="C1" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="E1" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="F1" t="s">
-        <v>676</v>
+        <v>298</v>
       </c>
       <c r="G1" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2943,7 +4261,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -2955,7 +4273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2963,7 +4281,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -2975,7 +4293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2983,7 +4301,7 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -2995,7 +4313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3003,7 +4321,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -3015,7 +4333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3023,7 +4341,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -3042,1244 +4360,39 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66E508F4-5906-4688-BE06-7243F5B00B2A}">
-  <dimension ref="A1:K42"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="4" max="4" width="8.625" style="12"/>
-    <col min="5" max="5" width="20.125" customWidth="1"/>
-    <col min="10" max="10" width="12.875" customWidth="1"/>
-    <col min="11" max="11" width="19.125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>503</v>
-      </c>
-      <c r="B1" t="s">
-        <v>504</v>
-      </c>
-      <c r="C1" t="s">
-        <v>505</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>506</v>
-      </c>
-      <c r="E1" t="s">
-        <v>499</v>
-      </c>
-      <c r="F1" t="s">
-        <v>507</v>
-      </c>
-      <c r="G1" t="s">
-        <v>508</v>
-      </c>
-      <c r="H1" t="s">
-        <v>509</v>
-      </c>
-      <c r="I1" t="s">
-        <v>676</v>
-      </c>
-      <c r="J1" t="s">
-        <v>314</v>
-      </c>
-      <c r="K1" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>438</v>
-      </c>
-      <c r="D2" s="12">
-        <v>0</v>
-      </c>
-      <c r="E2" t="s">
-        <v>404</v>
-      </c>
-      <c r="H2" t="s">
-        <v>328</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2" t="s">
-        <v>439</v>
-      </c>
-      <c r="K2" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>440</v>
-      </c>
-      <c r="D3" s="12">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
-        <v>404</v>
-      </c>
-      <c r="H3" t="s">
-        <v>441</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3" t="s">
-        <v>442</v>
-      </c>
-      <c r="K3" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>443</v>
-      </c>
-      <c r="D4" s="12">
-        <v>2</v>
-      </c>
-      <c r="E4" t="s">
-        <v>404</v>
-      </c>
-      <c r="H4" t="s">
-        <v>441</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4" t="s">
-        <v>444</v>
-      </c>
-      <c r="K4" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
-        <v>445</v>
-      </c>
-      <c r="D5" s="12">
-        <v>0</v>
-      </c>
-      <c r="E5" t="s">
-        <v>407</v>
-      </c>
-      <c r="G5" t="s">
-        <v>446</v>
-      </c>
-      <c r="H5" t="s">
-        <v>328</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5" t="s">
-        <v>447</v>
-      </c>
-      <c r="K5" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6" t="s">
-        <v>448</v>
-      </c>
-      <c r="D6" s="12">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>407</v>
-      </c>
-      <c r="G6" t="s">
-        <v>449</v>
-      </c>
-      <c r="H6" t="s">
-        <v>441</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6" t="s">
-        <v>450</v>
-      </c>
-      <c r="K6" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" t="s">
-        <v>451</v>
-      </c>
-      <c r="D7" s="12">
-        <v>0</v>
-      </c>
-      <c r="E7" t="s">
-        <v>410</v>
-      </c>
-      <c r="G7" t="s">
-        <v>446</v>
-      </c>
-      <c r="H7" t="s">
-        <v>328</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7" t="s">
-        <v>452</v>
-      </c>
-      <c r="K7" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>2</v>
-      </c>
-      <c r="C8" t="s">
-        <v>453</v>
-      </c>
-      <c r="D8" s="12">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
-        <v>410</v>
-      </c>
-      <c r="G8" t="s">
-        <v>449</v>
-      </c>
-      <c r="H8" t="s">
-        <v>441</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8" t="s">
-        <v>454</v>
-      </c>
-      <c r="K8" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9" t="s">
-        <v>451</v>
-      </c>
-      <c r="D9" s="12">
-        <v>0</v>
-      </c>
-      <c r="E9" t="s">
-        <v>413</v>
-      </c>
-      <c r="G9" t="s">
-        <v>446</v>
-      </c>
-      <c r="H9" t="s">
-        <v>328</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9" t="s">
-        <v>452</v>
-      </c>
-      <c r="K9" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>2</v>
-      </c>
-      <c r="C10" t="s">
-        <v>455</v>
-      </c>
-      <c r="D10" s="12">
-        <v>1</v>
-      </c>
-      <c r="E10" t="s">
-        <v>413</v>
-      </c>
-      <c r="G10" t="s">
-        <v>449</v>
-      </c>
-      <c r="H10" t="s">
-        <v>441</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10" t="s">
-        <v>454</v>
-      </c>
-      <c r="K10" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
-        <v>456</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>457</v>
-      </c>
-      <c r="E11" t="s">
-        <v>416</v>
-      </c>
-      <c r="H11" t="s">
-        <v>328</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11" t="s">
-        <v>458</v>
-      </c>
-      <c r="K11" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12">
-        <v>2</v>
-      </c>
-      <c r="C12" t="s">
-        <v>459</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>381</v>
-      </c>
-      <c r="E12" t="s">
-        <v>416</v>
-      </c>
-      <c r="H12" t="s">
-        <v>441</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12" t="s">
-        <v>460</v>
-      </c>
-      <c r="K12" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13" t="s">
-        <v>461</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>328</v>
-      </c>
-      <c r="E13" t="s">
-        <v>419</v>
-      </c>
-      <c r="G13" t="s">
-        <v>446</v>
-      </c>
-      <c r="H13" t="s">
-        <v>328</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13" t="s">
-        <v>462</v>
-      </c>
-      <c r="K13" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14">
-        <v>2</v>
-      </c>
-      <c r="C14" t="s">
-        <v>463</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>441</v>
-      </c>
-      <c r="E14" t="s">
-        <v>419</v>
-      </c>
-      <c r="G14" t="s">
-        <v>449</v>
-      </c>
-      <c r="H14" t="s">
-        <v>441</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14" t="s">
-        <v>464</v>
-      </c>
-      <c r="K14" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15" t="s">
-        <v>465</v>
-      </c>
-      <c r="D15" s="12">
-        <v>1</v>
-      </c>
-      <c r="E15" t="s">
-        <v>422</v>
-      </c>
-      <c r="G15" t="s">
-        <v>466</v>
-      </c>
-      <c r="H15" t="s">
-        <v>328</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16">
-        <v>2</v>
-      </c>
-      <c r="C16" t="s">
-        <v>467</v>
-      </c>
-      <c r="D16" s="12">
-        <v>2</v>
-      </c>
-      <c r="E16" t="s">
-        <v>422</v>
-      </c>
-      <c r="G16" t="s">
-        <v>468</v>
-      </c>
-      <c r="H16" t="s">
-        <v>441</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17" t="s">
-        <v>451</v>
-      </c>
-      <c r="D17" s="12">
-        <v>0</v>
-      </c>
-      <c r="E17" t="s">
-        <v>425</v>
-      </c>
-      <c r="G17" t="s">
-        <v>446</v>
-      </c>
-      <c r="H17" t="s">
-        <v>328</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18">
-        <v>2</v>
-      </c>
-      <c r="C18" t="s">
-        <v>469</v>
-      </c>
-      <c r="D18" s="12">
-        <v>1</v>
-      </c>
-      <c r="E18" t="s">
-        <v>425</v>
-      </c>
-      <c r="G18" t="s">
-        <v>449</v>
-      </c>
-      <c r="H18" t="s">
-        <v>441</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-      <c r="C19" t="s">
-        <v>471</v>
-      </c>
-      <c r="D19" s="12">
-        <v>0</v>
-      </c>
-      <c r="E19" t="s">
-        <v>428</v>
-      </c>
-      <c r="G19" t="s">
-        <v>472</v>
-      </c>
-      <c r="H19" t="s">
-        <v>441</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20" t="s">
-        <v>263</v>
-      </c>
-      <c r="D20" s="12">
-        <v>1</v>
-      </c>
-      <c r="E20" t="s">
-        <v>428</v>
-      </c>
-      <c r="G20" t="s">
-        <v>472</v>
-      </c>
-      <c r="H20" t="s">
-        <v>441</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21">
-        <v>2</v>
-      </c>
-      <c r="C21" t="s">
-        <v>267</v>
-      </c>
-      <c r="D21" s="12">
-        <v>2</v>
-      </c>
-      <c r="E21" t="s">
-        <v>428</v>
-      </c>
-      <c r="G21" t="s">
-        <v>472</v>
-      </c>
-      <c r="H21" t="s">
-        <v>441</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22">
-        <v>3</v>
-      </c>
-      <c r="C22" t="s">
-        <v>265</v>
-      </c>
-      <c r="D22" s="12">
-        <v>3</v>
-      </c>
-      <c r="E22" t="s">
-        <v>428</v>
-      </c>
-      <c r="G22" t="s">
-        <v>449</v>
-      </c>
-      <c r="H22" t="s">
-        <v>441</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23">
-        <v>4</v>
-      </c>
-      <c r="C23" t="s">
-        <v>477</v>
-      </c>
-      <c r="D23" s="12">
-        <v>4</v>
-      </c>
-      <c r="E23" t="s">
-        <v>428</v>
-      </c>
-      <c r="G23" t="s">
-        <v>446</v>
-      </c>
-      <c r="H23" t="s">
-        <v>441</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24">
-        <v>5</v>
-      </c>
-      <c r="C24" t="s">
-        <v>269</v>
-      </c>
-      <c r="D24" s="12">
-        <v>5</v>
-      </c>
-      <c r="E24" t="s">
-        <v>428</v>
-      </c>
-      <c r="G24" t="s">
-        <v>466</v>
-      </c>
-      <c r="H24" t="s">
-        <v>441</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25">
-        <v>6</v>
-      </c>
-      <c r="C25" t="s">
-        <v>480</v>
-      </c>
-      <c r="D25" s="12">
-        <v>6</v>
-      </c>
-      <c r="E25" t="s">
-        <v>428</v>
-      </c>
-      <c r="G25" t="s">
-        <v>466</v>
-      </c>
-      <c r="H25" t="s">
-        <v>441</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26">
-        <v>7</v>
-      </c>
-      <c r="C26" t="s">
-        <v>482</v>
-      </c>
-      <c r="D26" s="12">
-        <v>7</v>
-      </c>
-      <c r="E26" t="s">
-        <v>428</v>
-      </c>
-      <c r="G26" t="s">
-        <v>449</v>
-      </c>
-      <c r="H26" t="s">
-        <v>441</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27">
-        <v>8</v>
-      </c>
-      <c r="C27" t="s">
-        <v>247</v>
-      </c>
-      <c r="D27" s="12">
-        <v>8</v>
-      </c>
-      <c r="E27" t="s">
-        <v>428</v>
-      </c>
-      <c r="G27" t="s">
-        <v>466</v>
-      </c>
-      <c r="H27" t="s">
-        <v>441</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28">
-        <v>9</v>
-      </c>
-      <c r="C28" t="s">
-        <v>485</v>
-      </c>
-      <c r="D28" s="12">
-        <v>9</v>
-      </c>
-      <c r="E28" t="s">
-        <v>428</v>
-      </c>
-      <c r="G28" t="s">
-        <v>449</v>
-      </c>
-      <c r="H28" t="s">
-        <v>441</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29">
-        <v>1</v>
-      </c>
-      <c r="C29" t="s">
-        <v>487</v>
-      </c>
-      <c r="D29" s="12">
-        <v>0</v>
-      </c>
-      <c r="E29" t="s">
-        <v>431</v>
-      </c>
-      <c r="G29" t="s">
-        <v>446</v>
-      </c>
-      <c r="H29" t="s">
-        <v>441</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30">
-        <v>2</v>
-      </c>
-      <c r="C30" t="s">
-        <v>488</v>
-      </c>
-      <c r="D30" s="12">
-        <v>1</v>
-      </c>
-      <c r="E30" t="s">
-        <v>431</v>
-      </c>
-      <c r="G30" t="s">
-        <v>449</v>
-      </c>
-      <c r="H30" t="s">
-        <v>521</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31">
-        <v>1</v>
-      </c>
-      <c r="C31" t="s">
-        <v>489</v>
-      </c>
-      <c r="D31" s="12">
-        <v>1</v>
-      </c>
-      <c r="E31" t="s">
-        <v>434</v>
-      </c>
-      <c r="H31" t="s">
-        <v>521</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32">
-        <v>2</v>
-      </c>
-      <c r="C32" t="s">
-        <v>490</v>
-      </c>
-      <c r="D32" s="12">
-        <v>2</v>
-      </c>
-      <c r="E32" t="s">
-        <v>434</v>
-      </c>
-      <c r="H32" t="s">
-        <v>521</v>
-      </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33">
-        <v>1</v>
-      </c>
-      <c r="C33" t="s">
-        <v>491</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>492</v>
-      </c>
-      <c r="E33" t="s">
-        <v>436</v>
-      </c>
-      <c r="H33" t="s">
-        <v>521</v>
-      </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34">
-        <v>2</v>
-      </c>
-      <c r="C34" t="s">
-        <v>493</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>494</v>
-      </c>
-      <c r="E34" t="s">
-        <v>436</v>
-      </c>
-      <c r="H34" t="s">
-        <v>521</v>
-      </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35">
-        <v>3</v>
-      </c>
-      <c r="C35" t="s">
-        <v>495</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>496</v>
-      </c>
-      <c r="E35" t="s">
-        <v>436</v>
-      </c>
-      <c r="H35" t="s">
-        <v>521</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36">
-        <v>1</v>
-      </c>
-      <c r="C36" t="s">
-        <v>531</v>
-      </c>
-      <c r="D36" s="12">
-        <v>1</v>
-      </c>
-      <c r="E36" t="s">
-        <v>528</v>
-      </c>
-      <c r="G36" t="s">
-        <v>534</v>
-      </c>
-      <c r="H36" t="s">
-        <v>521</v>
-      </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37">
-        <v>2</v>
-      </c>
-      <c r="C37" t="s">
-        <v>532</v>
-      </c>
-      <c r="D37" s="12">
-        <v>2</v>
-      </c>
-      <c r="E37" t="s">
-        <v>528</v>
-      </c>
-      <c r="G37" t="s">
-        <v>535</v>
-      </c>
-      <c r="H37" t="s">
-        <v>521</v>
-      </c>
-      <c r="I37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38">
-        <v>3</v>
-      </c>
-      <c r="C38" t="s">
-        <v>533</v>
-      </c>
-      <c r="D38" s="12">
-        <v>3</v>
-      </c>
-      <c r="E38" t="s">
-        <v>528</v>
-      </c>
-      <c r="G38" t="s">
-        <v>536</v>
-      </c>
-      <c r="H38" t="s">
-        <v>521</v>
-      </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39">
-        <v>1</v>
-      </c>
-      <c r="C39" t="s">
-        <v>661</v>
-      </c>
-      <c r="D39" s="12">
-        <v>0</v>
-      </c>
-      <c r="E39" t="s">
-        <v>659</v>
-      </c>
-      <c r="H39" t="s">
-        <v>521</v>
-      </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40">
-        <v>2</v>
-      </c>
-      <c r="C40" t="s">
-        <v>674</v>
-      </c>
-      <c r="D40" s="12">
-        <v>1</v>
-      </c>
-      <c r="E40" t="s">
-        <v>659</v>
-      </c>
-      <c r="H40" t="s">
-        <v>521</v>
-      </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
-      <c r="J40" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41">
-        <v>3</v>
-      </c>
-      <c r="C41" t="s">
-        <v>662</v>
-      </c>
-      <c r="D41" s="12">
-        <v>2</v>
-      </c>
-      <c r="E41" t="s">
-        <v>659</v>
-      </c>
-      <c r="H41" t="s">
-        <v>521</v>
-      </c>
-      <c r="I41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42">
-        <v>4</v>
-      </c>
-      <c r="C42" t="s">
-        <v>673</v>
-      </c>
-      <c r="D42" s="12">
-        <v>3</v>
-      </c>
-      <c r="E42" t="s">
-        <v>659</v>
-      </c>
-      <c r="H42" t="s">
-        <v>521</v>
-      </c>
-      <c r="I42">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D59B089-6BFD-4898-97D7-5E5DB5B781E2}">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.125" customWidth="1"/>
+    <col min="1" max="1" width="11.08203125" customWidth="1"/>
     <col min="4" max="4" width="13.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C1" t="s">
         <v>291</v>
       </c>
       <c r="D1" t="s">
+        <v>669</v>
+      </c>
+      <c r="E1" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>666</v>
       </c>
-      <c r="E1" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>663</v>
-      </c>
       <c r="C2">
         <v>0</v>
       </c>
@@ -4287,15 +4400,15 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -4304,15 +4417,15 @@
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -4321,15 +4434,15 @@
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -4338,7 +4451,21 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>672</v>
+        <v>675</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>691</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4349,43 +4476,105 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1499BA89-84F4-45F4-9C1A-AC4400B29F1F}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>679</v>
+      </c>
+      <c r="B1" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>681</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>682</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>683</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>684</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>685</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A140A180-7D1B-4334-9A7F-5459F016CE4B}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="18.875" customWidth="1"/>
-    <col min="4" max="4" width="80.375" customWidth="1"/>
+    <col min="3" max="3" width="18.9140625" customWidth="1"/>
+    <col min="4" max="4" width="80.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A1" s="10" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C1" s="11" t="s">
+        <v>652</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>649</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="E1" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="9">
-        <v>1</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>646</v>
       </c>
       <c r="C2" s="9">
         <v>2</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="E2" s="9">
         <v>0</v>
@@ -4401,18 +4590,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N131"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16.5" customWidth="1"/>
-    <col min="4" max="4" width="11.625" customWidth="1"/>
-    <col min="5" max="6" width="23.625" customWidth="1"/>
+    <col min="2" max="2" width="16.4140625" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" customWidth="1"/>
+    <col min="5" max="6" width="23.58203125" customWidth="1"/>
     <col min="11" max="11" width="22.75" customWidth="1"/>
-    <col min="12" max="12" width="10.625" customWidth="1"/>
-    <col min="13" max="13" width="18.375" customWidth="1"/>
+    <col min="12" max="12" width="10.58203125" customWidth="1"/>
+    <col min="13" max="13" width="18.4140625" customWidth="1"/>
     <col min="14" max="14" width="21.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>289</v>
       </c>
@@ -4441,22 +4630,22 @@
         <v>297</v>
       </c>
       <c r="J1" t="s">
-        <v>676</v>
+        <v>298</v>
       </c>
       <c r="K1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M1" t="s">
+        <v>302</v>
+      </c>
+      <c r="N1" t="s">
         <v>301</v>
       </c>
-      <c r="N1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4491,7 +4680,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4526,7 +4715,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4561,7 +4750,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>5</v>
       </c>
@@ -4596,7 +4785,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>6</v>
       </c>
@@ -4634,12 +4823,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -4651,7 +4840,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4660,18 +4849,18 @@
         <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="N7" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -4680,7 +4869,7 @@
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -4695,18 +4884,18 @@
         <v>0</v>
       </c>
       <c r="L8" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="N8" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C9">
         <v>7</v>
@@ -4715,16 +4904,16 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
+        <v>558</v>
+      </c>
+      <c r="F9" t="s">
         <v>555</v>
       </c>
-      <c r="F9" t="s">
-        <v>552</v>
-      </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -4733,18 +4922,18 @@
         <v>0</v>
       </c>
       <c r="L9" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="N9" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -4753,16 +4942,16 @@
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="F10" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="G10">
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -4771,16 +4960,16 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="L10" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="N10" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>100</v>
       </c>
@@ -4821,7 +5010,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>101</v>
       </c>
@@ -4862,7 +5051,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>102</v>
       </c>
@@ -4903,7 +5092,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>103</v>
       </c>
@@ -4944,7 +5133,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>104</v>
       </c>
@@ -4985,7 +5174,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>105</v>
       </c>
@@ -5026,7 +5215,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>106</v>
       </c>
@@ -5064,7 +5253,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>107</v>
       </c>
@@ -5105,7 +5294,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>108</v>
       </c>
@@ -5140,7 +5329,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>109</v>
       </c>
@@ -5181,7 +5370,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>110</v>
       </c>
@@ -5195,7 +5384,7 @@
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="F21" t="s">
         <v>75</v>
@@ -5219,7 +5408,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>111</v>
       </c>
@@ -5257,7 +5446,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>112</v>
       </c>
@@ -5298,7 +5487,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>113</v>
       </c>
@@ -5339,7 +5528,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>114</v>
       </c>
@@ -5380,7 +5569,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>115</v>
       </c>
@@ -5421,7 +5610,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>116</v>
       </c>
@@ -5462,7 +5651,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>117</v>
       </c>
@@ -5476,7 +5665,7 @@
         <v>4</v>
       </c>
       <c r="E28" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="F28" t="s">
         <v>110</v>
@@ -5494,21 +5683,21 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="L28" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="N28" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>118</v>
       </c>
       <c r="B29" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="C29">
         <v>3</v>
@@ -5538,12 +5727,12 @@
         <v>114</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>119</v>
       </c>
       <c r="B30" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="C30">
         <v>118</v>
@@ -5555,7 +5744,7 @@
         <v>115</v>
       </c>
       <c r="F30" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -5579,7 +5768,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>500</v>
       </c>
@@ -5620,7 +5809,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>501</v>
       </c>
@@ -5661,12 +5850,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>502</v>
       </c>
       <c r="B33" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="C33">
         <v>108</v>
@@ -5675,16 +5864,16 @@
         <v>3</v>
       </c>
       <c r="E33" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="F33" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="G33">
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -5693,16 +5882,16 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
+        <v>551</v>
+      </c>
+      <c r="L33" t="s">
         <v>548</v>
       </c>
-      <c r="L33" t="s">
-        <v>545</v>
-      </c>
       <c r="N33" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1001</v>
       </c>
@@ -5731,7 +5920,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>1002</v>
       </c>
@@ -5760,7 +5949,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>1003</v>
       </c>
@@ -5789,7 +5978,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>1004</v>
       </c>
@@ -5818,7 +6007,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>1005</v>
       </c>
@@ -5850,7 +6039,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>1006</v>
       </c>
@@ -5882,7 +6071,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1007</v>
       </c>
@@ -5914,7 +6103,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>1008</v>
       </c>
@@ -5946,7 +6135,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>1009</v>
       </c>
@@ -5978,7 +6167,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>1010</v>
       </c>
@@ -6010,7 +6199,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>1011</v>
       </c>
@@ -6042,7 +6231,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>1012</v>
       </c>
@@ -6074,7 +6263,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>1013</v>
       </c>
@@ -6106,7 +6295,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>1014</v>
       </c>
@@ -6138,7 +6327,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>1015</v>
       </c>
@@ -6170,7 +6359,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>1016</v>
       </c>
@@ -6202,7 +6391,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>1017</v>
       </c>
@@ -6231,7 +6420,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>1018</v>
       </c>
@@ -6260,7 +6449,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>1019</v>
       </c>
@@ -6289,7 +6478,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>1020</v>
       </c>
@@ -6318,7 +6507,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>1021</v>
       </c>
@@ -6347,7 +6536,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>1022</v>
       </c>
@@ -6376,7 +6565,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>1023</v>
       </c>
@@ -6405,7 +6594,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>1024</v>
       </c>
@@ -6434,7 +6623,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>1025</v>
       </c>
@@ -6463,7 +6652,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>1026</v>
       </c>
@@ -6492,7 +6681,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>1027</v>
       </c>
@@ -6521,7 +6710,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>1028</v>
       </c>
@@ -6550,7 +6739,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>1029</v>
       </c>
@@ -6579,7 +6768,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>1030</v>
       </c>
@@ -6608,7 +6797,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>1031</v>
       </c>
@@ -6637,7 +6826,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>1032</v>
       </c>
@@ -6672,7 +6861,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>1033</v>
       </c>
@@ -6704,7 +6893,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>1034</v>
       </c>
@@ -6736,7 +6925,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>1035</v>
       </c>
@@ -6768,7 +6957,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>1036</v>
       </c>
@@ -6800,7 +6989,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>1037</v>
       </c>
@@ -6832,7 +7021,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>1038</v>
       </c>
@@ -6864,7 +7053,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>1039</v>
       </c>
@@ -6902,7 +7091,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>1040</v>
       </c>
@@ -6934,7 +7123,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>1041</v>
       </c>
@@ -6966,7 +7155,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>1042</v>
       </c>
@@ -6998,7 +7187,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>1043</v>
       </c>
@@ -7030,7 +7219,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>1044</v>
       </c>
@@ -7062,7 +7251,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>1045</v>
       </c>
@@ -7094,7 +7283,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>1046</v>
       </c>
@@ -7126,12 +7315,12 @@
         <v>224</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>1047</v>
       </c>
       <c r="B80" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="C80">
         <v>3</v>
@@ -7140,16 +7329,16 @@
         <v>2</v>
       </c>
       <c r="E80" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="F80" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="G80">
         <v>0</v>
       </c>
       <c r="H80" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="I80">
         <v>1</v>
@@ -7158,18 +7347,18 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="L80" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>1049</v>
       </c>
       <c r="B81" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="C81">
         <v>118</v>
@@ -7196,12 +7385,12 @@
         <v>225</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>1050</v>
       </c>
       <c r="B82" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="C82">
         <v>118</v>
@@ -7228,7 +7417,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>1051</v>
       </c>
@@ -7260,7 +7449,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>1052</v>
       </c>
@@ -7292,7 +7481,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>1053</v>
       </c>
@@ -7324,7 +7513,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>1054</v>
       </c>
@@ -7356,7 +7545,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>1055</v>
       </c>
@@ -7388,7 +7577,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>1060</v>
       </c>
@@ -7423,7 +7612,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>1061</v>
       </c>
@@ -7455,7 +7644,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>1062</v>
       </c>
@@ -7487,7 +7676,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>1063</v>
       </c>
@@ -7519,7 +7708,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>1064</v>
       </c>
@@ -7551,7 +7740,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>1065</v>
       </c>
@@ -7583,7 +7772,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>1070</v>
       </c>
@@ -7612,7 +7801,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>1071</v>
       </c>
@@ -7641,7 +7830,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>1072</v>
       </c>
@@ -7682,7 +7871,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>1073</v>
       </c>
@@ -7714,7 +7903,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>1074</v>
       </c>
@@ -7746,7 +7935,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>1075</v>
       </c>
@@ -7778,7 +7967,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>1076</v>
       </c>
@@ -7810,7 +7999,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>1077</v>
       </c>
@@ -7842,7 +8031,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>1078</v>
       </c>
@@ -7883,7 +8072,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>1079</v>
       </c>
@@ -7915,7 +8104,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>1080</v>
       </c>
@@ -7947,7 +8136,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>1081</v>
       </c>
@@ -7979,7 +8168,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>1082</v>
       </c>
@@ -8011,12 +8200,12 @@
         <v>280</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>1090</v>
       </c>
       <c r="B107" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C107">
         <v>1078</v>
@@ -8025,13 +8214,13 @@
         <v>5</v>
       </c>
       <c r="E107" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="G107">
         <v>0</v>
       </c>
       <c r="H107" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="I107">
         <v>0</v>
@@ -8040,10 +8229,10 @@
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.2">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>1083</v>
       </c>
@@ -8075,12 +8264,12 @@
         <v>281</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" s="4">
         <v>1084</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="C109" s="4">
         <v>118</v>
@@ -8092,7 +8281,7 @@
         <v>282</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="G109" s="4">
         <v>0</v>
@@ -8114,10 +8303,10 @@
       </c>
       <c r="M109" s="4"/>
       <c r="N109" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.2">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" s="4">
         <v>1085</v>
       </c>
@@ -8152,7 +8341,7 @@
       <c r="L110" s="4"/>
       <c r="M110" s="4"/>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" s="4">
         <v>1086</v>
       </c>
@@ -8187,7 +8376,7 @@
       <c r="L111" s="4"/>
       <c r="M111" s="4"/>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" s="4">
         <v>1087</v>
       </c>
@@ -8222,7 +8411,7 @@
       <c r="L112" s="4"/>
       <c r="M112" s="4"/>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A113" s="4">
         <v>1088</v>
       </c>
@@ -8257,7 +8446,7 @@
       <c r="L113" s="4"/>
       <c r="M113" s="4"/>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A114" s="4">
         <v>1089</v>
       </c>
@@ -8292,12 +8481,12 @@
       <c r="L114" s="4"/>
       <c r="M114" s="4"/>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>1092</v>
       </c>
       <c r="B115" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C115">
         <v>111</v>
@@ -8309,7 +8498,7 @@
         <v>0</v>
       </c>
       <c r="H115" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="I115">
         <v>0</v>
@@ -8318,18 +8507,18 @@
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="M115" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.2">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>1091</v>
       </c>
       <c r="B116" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C116">
         <v>111</v>
@@ -8341,7 +8530,7 @@
         <v>0</v>
       </c>
       <c r="H116" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="I116">
         <v>0</v>
@@ -8350,18 +8539,18 @@
         <v>0</v>
       </c>
       <c r="K116" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="M116" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.2">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>1102</v>
       </c>
       <c r="B117" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="C117">
         <v>502</v>
@@ -8373,7 +8562,7 @@
         <v>0</v>
       </c>
       <c r="H117" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="I117">
         <v>0</v>
@@ -8382,18 +8571,18 @@
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="M117" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.2">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>1103</v>
       </c>
       <c r="B118" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C118">
         <v>502</v>
@@ -8405,7 +8594,7 @@
         <v>0</v>
       </c>
       <c r="H118" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="I118">
         <v>0</v>
@@ -8414,18 +8603,18 @@
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="M118" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.2">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A119" s="5">
         <v>1104</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C119" s="5">
         <v>9</v>
@@ -8434,16 +8623,16 @@
         <v>1</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="G119" s="5">
         <v>0</v>
       </c>
       <c r="H119" s="5" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="I119" s="5">
         <v>0</v>
@@ -8452,22 +8641,22 @@
         <v>0</v>
       </c>
       <c r="K119" s="5" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="L119" s="5" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="M119" s="5"/>
       <c r="N119" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="120" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="5">
         <v>1105</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="C120" s="5">
         <v>1104</v>
@@ -8481,7 +8670,7 @@
         <v>0</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="I120" s="5">
         <v>0</v>
@@ -8490,17 +8679,17 @@
         <v>0</v>
       </c>
       <c r="K120" s="5" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="L120" s="5"/>
       <c r="M120" s="5"/>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A121" s="5">
         <v>1106</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C121" s="5">
         <v>1104</v>
@@ -8514,7 +8703,7 @@
         <v>0</v>
       </c>
       <c r="H121" s="5" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="I121" s="5">
         <v>0</v>
@@ -8523,17 +8712,17 @@
         <v>0</v>
       </c>
       <c r="K121" s="5" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="L121" s="5"/>
       <c r="M121" s="5"/>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A122" s="5">
         <v>1107</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="C122" s="5">
         <v>1104</v>
@@ -8547,7 +8736,7 @@
         <v>0</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="I122" s="5">
         <v>0</v>
@@ -8556,17 +8745,17 @@
         <v>0</v>
       </c>
       <c r="K122" s="5" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="L122" s="5"/>
       <c r="M122" s="5"/>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A123" s="6">
         <v>1108</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="C123" s="6">
         <v>108</v>
@@ -8575,40 +8764,40 @@
         <v>1</v>
       </c>
       <c r="E123" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="F123" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="G123" s="6">
+        <v>0</v>
+      </c>
+      <c r="H123" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="I123" s="6">
+        <v>0</v>
+      </c>
+      <c r="J123" s="6">
+        <v>0</v>
+      </c>
+      <c r="K123" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="L123" s="6" t="s">
         <v>594</v>
-      </c>
-      <c r="F123" s="6" t="s">
-        <v>595</v>
-      </c>
-      <c r="G123" s="6">
-        <v>0</v>
-      </c>
-      <c r="H123" s="6" t="s">
-        <v>544</v>
-      </c>
-      <c r="I123" s="6">
-        <v>0</v>
-      </c>
-      <c r="J123" s="6">
-        <v>0</v>
-      </c>
-      <c r="K123" s="6" t="s">
-        <v>596</v>
-      </c>
-      <c r="L123" s="6" t="s">
-        <v>591</v>
       </c>
       <c r="M123" s="6"/>
       <c r="N123" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.2">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A124" s="6">
         <v>1109</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="C124" s="6">
         <v>1108</v>
@@ -8622,7 +8811,7 @@
         <v>0</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="I124" s="6">
         <v>0</v>
@@ -8631,17 +8820,17 @@
         <v>0</v>
       </c>
       <c r="K124" s="6" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="L124" s="6"/>
       <c r="M124" s="6"/>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A125" s="6">
         <v>1110</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="C125" s="6">
         <v>1108</v>
@@ -8655,7 +8844,7 @@
         <v>0</v>
       </c>
       <c r="H125" s="6" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="I125" s="6">
         <v>0</v>
@@ -8664,17 +8853,17 @@
         <v>0</v>
       </c>
       <c r="K125" s="6" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="L125" s="6"/>
       <c r="M125" s="6"/>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A126" s="4">
         <v>1111</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C126" s="4">
         <v>9</v>
@@ -8683,16 +8872,16 @@
         <v>1</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="G126" s="4">
         <v>0</v>
       </c>
       <c r="H126" s="4" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="I126" s="4">
         <v>0</v>
@@ -8701,24 +8890,24 @@
         <v>0</v>
       </c>
       <c r="K126" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="L126" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="M126" s="4" t="s">
         <v>611</v>
       </c>
-      <c r="L126" s="4" t="s">
-        <v>609</v>
-      </c>
-      <c r="M126" s="4" t="s">
-        <v>608</v>
-      </c>
       <c r="N126" s="4" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.2">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A127" s="4">
         <v>1112</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="C127" s="4">
         <v>1111</v>
@@ -8732,7 +8921,7 @@
         <v>0</v>
       </c>
       <c r="H127" s="4" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="I127" s="4">
         <v>0</v>
@@ -8741,17 +8930,17 @@
         <v>0</v>
       </c>
       <c r="K127" s="4" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="L127" s="4"/>
       <c r="M127" s="4"/>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A128" s="4">
         <v>1113</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="C128" s="4">
         <v>1111</v>
@@ -8765,7 +8954,7 @@
         <v>0</v>
       </c>
       <c r="H128" s="4" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="I128" s="4">
         <v>0</v>
@@ -8774,17 +8963,17 @@
         <v>0</v>
       </c>
       <c r="K128" s="4" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="L128" s="4"/>
       <c r="M128" s="4"/>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A129" s="7">
         <v>1114</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="C129" s="7">
         <v>2</v>
@@ -8793,16 +8982,16 @@
         <v>1</v>
       </c>
       <c r="E129" s="7" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="F129" s="7" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="G129" s="7">
         <v>0</v>
       </c>
       <c r="H129" s="7" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="I129" s="7">
         <v>0</v>
@@ -8811,22 +9000,22 @@
         <v>0</v>
       </c>
       <c r="K129" s="7" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="L129" s="7" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="M129" s="7"/>
       <c r="N129" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.2">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A130" s="7">
         <v>1115</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C130" s="7">
         <v>1114</v>
@@ -8840,7 +9029,7 @@
         <v>0</v>
       </c>
       <c r="H130" s="7" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="I130" s="7">
         <v>0</v>
@@ -8849,17 +9038,17 @@
         <v>0</v>
       </c>
       <c r="K130" s="7" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="L130" s="7"/>
       <c r="M130" s="7"/>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A131" s="7">
         <v>1116</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="C131" s="7">
         <v>1114</v>
@@ -8873,7 +9062,7 @@
         <v>0</v>
       </c>
       <c r="H131" s="7" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="I131" s="7">
         <v>0</v>
@@ -8882,7 +9071,7 @@
         <v>0</v>
       </c>
       <c r="K131" s="7" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="L131" s="7"/>
       <c r="M131" s="7"/>
@@ -8913,51 +9102,51 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE4172CB-C633-40F1-9E06-DA7BE35E7941}">
   <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="6" max="6" width="13.375" customWidth="1"/>
-    <col min="7" max="7" width="15.375" customWidth="1"/>
+    <col min="6" max="6" width="13.4140625" customWidth="1"/>
+    <col min="7" max="7" width="15.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C1" t="s">
+        <v>323</v>
+      </c>
+      <c r="D1" t="s">
+        <v>324</v>
+      </c>
+      <c r="E1" t="s">
+        <v>326</v>
+      </c>
+      <c r="F1" t="s">
+        <v>327</v>
+      </c>
+      <c r="G1" t="s">
+        <v>328</v>
+      </c>
+      <c r="H1" t="s">
+        <v>298</v>
+      </c>
+      <c r="I1" t="s">
+        <v>325</v>
+      </c>
+      <c r="J1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>318</v>
-      </c>
-      <c r="B1" t="s">
-        <v>319</v>
-      </c>
-      <c r="C1" t="s">
-        <v>320</v>
-      </c>
-      <c r="D1" t="s">
-        <v>321</v>
-      </c>
-      <c r="E1" t="s">
-        <v>322</v>
-      </c>
-      <c r="F1" t="s">
-        <v>323</v>
-      </c>
-      <c r="G1" t="s">
-        <v>324</v>
-      </c>
-      <c r="H1" t="s">
-        <v>676</v>
-      </c>
-      <c r="I1" t="s">
-        <v>677</v>
-      </c>
-      <c r="J1" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>315</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -8981,18 +9170,18 @@
         <v>0</v>
       </c>
       <c r="J2" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C3" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -9013,18 +9202,18 @@
         <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>606</v>
+      </c>
+      <c r="C4" t="s">
         <v>603</v>
-      </c>
-      <c r="C4" t="s">
-        <v>600</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -9045,7 +9234,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
     </row>
   </sheetData>
@@ -9058,20 +9247,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{337D2D18-B37B-4DF5-9944-49704E9D0445}">
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C1" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2</v>
       </c>
@@ -9079,7 +9268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -9087,7 +9276,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -9095,7 +9284,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -9103,7 +9292,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2</v>
       </c>
@@ -9111,7 +9300,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2</v>
       </c>
@@ -9119,7 +9308,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2</v>
       </c>
@@ -9127,7 +9316,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2</v>
       </c>
@@ -9135,7 +9324,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -9143,7 +9332,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -9151,7 +9340,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -9159,7 +9348,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>2</v>
       </c>
@@ -9167,7 +9356,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>2</v>
       </c>
@@ -9175,7 +9364,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>2</v>
       </c>
@@ -9183,7 +9372,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>3</v>
       </c>
@@ -9191,7 +9380,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>2</v>
       </c>
@@ -9199,7 +9388,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>2</v>
       </c>
@@ -9207,7 +9396,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>2</v>
       </c>
@@ -9215,7 +9404,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>2</v>
       </c>
@@ -9223,7 +9412,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>2</v>
       </c>
@@ -9231,7 +9420,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -9239,7 +9428,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>2</v>
       </c>
@@ -9247,7 +9436,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>2</v>
       </c>
@@ -9255,7 +9444,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>2</v>
       </c>
@@ -9263,7 +9452,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>2</v>
       </c>
@@ -9271,7 +9460,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>2</v>
       </c>
@@ -9279,7 +9468,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>3</v>
       </c>
@@ -9287,10 +9476,10 @@
         <v>1084</v>
       </c>
       <c r="C28" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>3</v>
       </c>
@@ -9298,10 +9487,10 @@
         <v>1085</v>
       </c>
       <c r="C29" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>3</v>
       </c>
@@ -9309,10 +9498,10 @@
         <v>1086</v>
       </c>
       <c r="C30" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>3</v>
       </c>
@@ -9320,10 +9509,10 @@
         <v>1087</v>
       </c>
       <c r="C31" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>3</v>
       </c>
@@ -9331,10 +9520,10 @@
         <v>1088</v>
       </c>
       <c r="C32" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>3</v>
       </c>
@@ -9342,10 +9531,10 @@
         <v>1089</v>
       </c>
       <c r="C33" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>3</v>
       </c>
@@ -9353,10 +9542,10 @@
         <v>1048</v>
       </c>
       <c r="C34" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>3</v>
       </c>
@@ -9364,10 +9553,10 @@
         <v>1049</v>
       </c>
       <c r="C35" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>3</v>
       </c>
@@ -9375,10 +9564,10 @@
         <v>1050</v>
       </c>
       <c r="C36" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>3</v>
       </c>
@@ -9386,10 +9575,10 @@
         <v>119</v>
       </c>
       <c r="C37" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>3</v>
       </c>
@@ -9397,10 +9586,10 @@
         <v>3</v>
       </c>
       <c r="C38" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>3</v>
       </c>
@@ -9422,141 +9611,170 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BA152B8-C1FA-4646-A501-2C7774BC6ACC}">
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="23.375" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" customWidth="1"/>
     <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.625" customWidth="1"/>
+    <col min="4" max="4" width="35.58203125" customWidth="1"/>
     <col min="6" max="6" width="83.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B1" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="D1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F1" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D2" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F2" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C3" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D3">
         <v>123456</v>
       </c>
       <c r="E3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F3" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C4" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="D4" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="E4" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F4" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C5" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F5" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C6" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>341</v>
+        <v>686</v>
+      </c>
+      <c r="C7" t="s">
+        <v>687</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>328</v>
+        <v>505</v>
+      </c>
+      <c r="F7" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>689</v>
+      </c>
+      <c r="C8" t="s">
+        <v>690</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>505</v>
+      </c>
+      <c r="F8" t="s">
+        <v>688</v>
       </c>
     </row>
   </sheetData>
@@ -9568,17 +9786,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDFFA53F-160B-48BA-80B0-079F0EA2A7A7}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B1" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -9586,7 +9804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -9594,7 +9812,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -9611,88 +9829,88 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2040177-E526-42D3-A91B-661E4F43E409}">
   <dimension ref="A1:Q2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="10.625" customWidth="1"/>
-    <col min="8" max="8" width="14.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" customWidth="1"/>
+    <col min="8" max="8" width="14.4140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.58203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.75" customWidth="1"/>
-    <col min="17" max="17" width="15.625" customWidth="1"/>
-    <col min="18" max="18" width="14.375" customWidth="1"/>
+    <col min="17" max="17" width="15.6640625" customWidth="1"/>
+    <col min="18" max="18" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C1" t="s">
+        <v>391</v>
+      </c>
+      <c r="D1" t="s">
+        <v>392</v>
+      </c>
+      <c r="E1" t="s">
+        <v>393</v>
+      </c>
+      <c r="F1" t="s">
+        <v>394</v>
+      </c>
+      <c r="G1" t="s">
+        <v>395</v>
+      </c>
+      <c r="H1" t="s">
+        <v>396</v>
+      </c>
+      <c r="I1" t="s">
+        <v>397</v>
+      </c>
+      <c r="J1" t="s">
+        <v>398</v>
+      </c>
+      <c r="K1" t="s">
+        <v>399</v>
+      </c>
+      <c r="L1" t="s">
+        <v>400</v>
+      </c>
+      <c r="M1" t="s">
+        <v>401</v>
+      </c>
+      <c r="N1" t="s">
+        <v>402</v>
+      </c>
+      <c r="O1" t="s">
+        <v>403</v>
+      </c>
+      <c r="P1" t="s">
+        <v>404</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B2" t="s">
+        <v>383</v>
+      </c>
+      <c r="C2" t="s">
+        <v>384</v>
+      </c>
+      <c r="D2" t="s">
         <v>385</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F2" t="s">
         <v>387</v>
-      </c>
-      <c r="C1" t="s">
-        <v>388</v>
-      </c>
-      <c r="D1" t="s">
-        <v>389</v>
-      </c>
-      <c r="E1" t="s">
-        <v>390</v>
-      </c>
-      <c r="F1" t="s">
-        <v>391</v>
-      </c>
-      <c r="G1" t="s">
-        <v>392</v>
-      </c>
-      <c r="H1" t="s">
-        <v>393</v>
-      </c>
-      <c r="I1" t="s">
-        <v>394</v>
-      </c>
-      <c r="J1" t="s">
-        <v>395</v>
-      </c>
-      <c r="K1" t="s">
-        <v>396</v>
-      </c>
-      <c r="L1" t="s">
-        <v>397</v>
-      </c>
-      <c r="M1" t="s">
-        <v>398</v>
-      </c>
-      <c r="N1" t="s">
-        <v>399</v>
-      </c>
-      <c r="O1" t="s">
-        <v>400</v>
-      </c>
-      <c r="P1" t="s">
-        <v>401</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="B2" t="s">
-        <v>380</v>
-      </c>
-      <c r="C2" t="s">
-        <v>381</v>
-      </c>
-      <c r="D2" t="s">
-        <v>382</v>
-      </c>
-      <c r="E2" t="s">
-        <v>383</v>
-      </c>
-      <c r="F2" t="s">
-        <v>384</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -9725,37 +9943,37 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F9C4135-AFDC-4222-9830-710D942A3AED}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="14.375" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D1" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E1" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -9764,15 +9982,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C3" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -9781,15 +9999,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C4" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -9798,15 +10016,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C5" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -9815,15 +10033,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C6" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -9832,15 +10050,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C7" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -9849,15 +10067,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C8" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -9866,15 +10084,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C9" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -9883,15 +10101,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C10" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -9900,15 +10118,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C11" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -9917,15 +10135,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C12" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -9934,15 +10152,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C13" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -9951,15 +10169,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C14" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -9976,336 +10194,354 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3DA66D3-8315-4018-BF52-5D786631F136}">
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="2" max="2" width="12.33203125" customWidth="1"/>
     <col min="3" max="3" width="19.25" customWidth="1"/>
-    <col min="4" max="5" width="8.875" style="3"/>
-    <col min="6" max="6" width="17.625" customWidth="1"/>
-    <col min="7" max="7" width="70.625" customWidth="1"/>
+    <col min="4" max="5" width="8.9140625" style="3"/>
+    <col min="6" max="6" width="17.58203125" customWidth="1"/>
+    <col min="7" max="7" width="70.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B1" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C1" t="s">
-        <v>499</v>
-      </c>
-      <c r="D1" t="s">
-        <v>676</v>
+        <v>502</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>298</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="F1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="G1" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="D2" s="3">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F2" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C3" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D3" s="3">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F3" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C4" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="D4" s="3">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F4" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C5" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D5" s="3">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F5" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C6" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="D6" s="3">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F6" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C7" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="D7" s="3">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F7" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C8" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="D8" s="3">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F8" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C9" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D9" s="3">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F9" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C10" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="D10" s="3">
         <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F10" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C11" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="D11" s="3">
         <v>0</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F11" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C12" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D12" s="3">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C13" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="D13" s="3">
         <v>0</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F13" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C14" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="D14" s="3">
         <v>0</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F14" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C15" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="D15" s="3">
         <v>0</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F15" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="G15" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C16" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="D16" s="3">
         <v>0</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F16" t="s">
-        <v>658</v>
+        <v>661</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>692</v>
+      </c>
+      <c r="C17" t="s">
+        <v>693</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>505</v>
       </c>
     </row>
   </sheetData>

--- a/Ams.WebApi/wwwroot/data.xlsx
+++ b/Ams.WebApi/wwwroot/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\App Develop\VS2024\Lean.Ams\Ams.WebApi\wwwroot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{022AC00D-D003-443E-8E8D-419A5EE59E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C52716-F2D8-40FB-9FE3-53F3CC0C5938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="30" windowWidth="28770" windowHeight="15450" tabRatio="849" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="849" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="user" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1161" uniqueCount="730">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1301" uniqueCount="794">
   <si>
     <t>系统管理</t>
   </si>
@@ -1061,84 +1061,6 @@
   </si>
   <si>
     <t>ConfigType</t>
-  </si>
-  <si>
-    <t>CEO</t>
-  </si>
-  <si>
-    <t>董事长</t>
-  </si>
-  <si>
-    <t>SE</t>
-  </si>
-  <si>
-    <t>项目经理</t>
-  </si>
-  <si>
-    <t>HR</t>
-  </si>
-  <si>
-    <t>人力资源</t>
-  </si>
-  <si>
-    <t>USER</t>
-  </si>
-  <si>
-    <t>普通员工</t>
-  </si>
-  <si>
-    <t>PM</t>
-  </si>
-  <si>
-    <t>人事经理</t>
-  </si>
-  <si>
-    <t>GM</t>
-  </si>
-  <si>
-    <t>总经理</t>
-  </si>
-  <si>
-    <t>COO</t>
-  </si>
-  <si>
-    <t>首席运营官</t>
-  </si>
-  <si>
-    <t>CFO</t>
-  </si>
-  <si>
-    <t>首席财务官</t>
-  </si>
-  <si>
-    <t>CTO</t>
-  </si>
-  <si>
-    <t>首席技术官</t>
-  </si>
-  <si>
-    <t>HRD</t>
-  </si>
-  <si>
-    <t>人力资源总监</t>
-  </si>
-  <si>
-    <t>VP</t>
-  </si>
-  <si>
-    <t>副总裁</t>
-  </si>
-  <si>
-    <t>OD</t>
-  </si>
-  <si>
-    <t>运营总监</t>
-  </si>
-  <si>
-    <t>MD</t>
-  </si>
-  <si>
-    <t>市场总监</t>
   </si>
   <si>
     <t>PostId</t>
@@ -2476,6 +2398,314 @@
   </si>
   <si>
     <t>SortingNum</t>
+  </si>
+  <si>
+    <t>PostLevel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>M5</t>
+  </si>
+  <si>
+    <t>M6</t>
+  </si>
+  <si>
+    <t>M7</t>
+  </si>
+  <si>
+    <t>M8</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>M10</t>
+  </si>
+  <si>
+    <t>M11</t>
+  </si>
+  <si>
+    <t>M12</t>
+  </si>
+  <si>
+    <t>M13</t>
+  </si>
+  <si>
+    <t>主管</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>副部长</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>部长</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>P4</t>
+  </si>
+  <si>
+    <t>P5</t>
+  </si>
+  <si>
+    <t>P6</t>
+  </si>
+  <si>
+    <t>P7</t>
+  </si>
+  <si>
+    <t>P8</t>
+  </si>
+  <si>
+    <t>P9</t>
+  </si>
+  <si>
+    <t>P10</t>
+  </si>
+  <si>
+    <t>P11</t>
+  </si>
+  <si>
+    <t>P12</t>
+  </si>
+  <si>
+    <t>P13</t>
+  </si>
+  <si>
+    <t>P14</t>
+  </si>
+  <si>
+    <t>P15</t>
+  </si>
+  <si>
+    <t>P16</t>
+  </si>
+  <si>
+    <t>P17</t>
+  </si>
+  <si>
+    <t>P18</t>
+  </si>
+  <si>
+    <t>P19</t>
+  </si>
+  <si>
+    <t>P20</t>
+  </si>
+  <si>
+    <t>助理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>专员</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高级专员</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>副总监</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>总监</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资深专家</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>总经理助理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>副总经理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>总经理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>副总裁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高级副总裁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>总裁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高级总裁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>首席执行官</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>副主席</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主席</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高级主席</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>董事长</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M14</t>
+  </si>
+  <si>
+    <t>M15</t>
+  </si>
+  <si>
+    <t>M16</t>
+  </si>
+  <si>
+    <t>M17</t>
+  </si>
+  <si>
+    <t>M18</t>
+  </si>
+  <si>
+    <t>M19</t>
+  </si>
+  <si>
+    <t>M20</t>
+  </si>
+  <si>
+    <t>M21</t>
+  </si>
+  <si>
+    <t>M22</t>
+  </si>
+  <si>
+    <t>M23</t>
+  </si>
+  <si>
+    <t>M24</t>
+  </si>
+  <si>
+    <t>C1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>员工</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>组长</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>副组长</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>C5</t>
+  </si>
+  <si>
+    <t>副主任</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主任</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高级主任</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C6</t>
+  </si>
+  <si>
+    <t>C7</t>
+  </si>
+  <si>
+    <t>C8</t>
+  </si>
+  <si>
+    <t>副理经</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>经理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高级经理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C9</t>
+  </si>
+  <si>
+    <t>C10</t>
+  </si>
+  <si>
+    <t>C11</t>
   </si>
 </sst>
 </file>
@@ -3061,7 +3291,7 @@
         <v>304</v>
       </c>
       <c r="J1" t="s">
-        <v>497</v>
+        <v>471</v>
       </c>
       <c r="K1" t="s">
         <v>307</v>
@@ -3107,10 +3337,10 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>499</v>
+        <v>473</v>
       </c>
       <c r="D3" t="s">
-        <v>500</v>
+        <v>474</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -3136,10 +3366,10 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>575</v>
+        <v>549</v>
       </c>
       <c r="D4" t="s">
-        <v>576</v>
+        <v>550</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -3148,7 +3378,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="s">
-        <v>577</v>
+        <v>551</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -3157,7 +3387,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="s">
-        <v>576</v>
+        <v>550</v>
       </c>
     </row>
   </sheetData>
@@ -3181,28 +3411,28 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>483</v>
+        <v>457</v>
       </c>
       <c r="B1" t="s">
-        <v>729</v>
+        <v>703</v>
       </c>
       <c r="C1" t="s">
-        <v>484</v>
+        <v>458</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>485</v>
+        <v>459</v>
       </c>
       <c r="E1" t="s">
-        <v>479</v>
+        <v>453</v>
       </c>
       <c r="F1" t="s">
-        <v>486</v>
+        <v>460</v>
       </c>
       <c r="G1" t="s">
-        <v>487</v>
+        <v>461</v>
       </c>
       <c r="H1" t="s">
-        <v>488</v>
+        <v>462</v>
       </c>
       <c r="I1" t="s">
         <v>292</v>
@@ -3211,7 +3441,7 @@
         <v>311</v>
       </c>
       <c r="K1" t="s">
-        <v>540</v>
+        <v>514</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -3222,16 +3452,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>666</v>
+        <v>640</v>
       </c>
       <c r="D2" s="12">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>681</v>
+        <v>655</v>
       </c>
       <c r="H2" t="s">
-        <v>498</v>
+        <v>472</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3245,16 +3475,16 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>633</v>
+        <v>607</v>
       </c>
       <c r="D3" s="12">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>723</v>
+        <v>697</v>
       </c>
       <c r="H3" t="s">
-        <v>498</v>
+        <v>472</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3268,16 +3498,16 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>660</v>
+        <v>634</v>
       </c>
       <c r="D4" s="12">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>723</v>
+        <v>697</v>
       </c>
       <c r="H4" t="s">
-        <v>498</v>
+        <v>472</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3291,16 +3521,16 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>469</v>
+        <v>443</v>
       </c>
       <c r="D5" s="12">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>416</v>
+        <v>390</v>
       </c>
       <c r="H5" t="s">
-        <v>498</v>
+        <v>472</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3314,16 +3544,16 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>470</v>
+        <v>444</v>
       </c>
       <c r="D6" s="12">
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>416</v>
+        <v>390</v>
       </c>
       <c r="H6" t="s">
-        <v>498</v>
+        <v>472</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3337,16 +3567,16 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>633</v>
+        <v>607</v>
       </c>
       <c r="D7" s="12">
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>631</v>
+        <v>605</v>
       </c>
       <c r="H7" t="s">
-        <v>498</v>
+        <v>472</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3360,22 +3590,22 @@
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>645</v>
+        <v>619</v>
       </c>
       <c r="D8" s="12">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>631</v>
+        <v>605</v>
       </c>
       <c r="H8" t="s">
-        <v>498</v>
+        <v>472</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>646</v>
+        <v>620</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -3386,16 +3616,16 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>634</v>
+        <v>608</v>
       </c>
       <c r="D9" s="12">
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>631</v>
+        <v>605</v>
       </c>
       <c r="H9" t="s">
-        <v>498</v>
+        <v>472</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -3409,16 +3639,16 @@
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>644</v>
+        <v>618</v>
       </c>
       <c r="D10" s="12">
         <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>631</v>
+        <v>605</v>
       </c>
       <c r="H10" t="s">
-        <v>498</v>
+        <v>472</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -3432,16 +3662,16 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>697</v>
+        <v>671</v>
       </c>
       <c r="D11" s="12">
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>695</v>
+        <v>669</v>
       </c>
       <c r="H11" t="s">
-        <v>498</v>
+        <v>472</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -3455,16 +3685,16 @@
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>698</v>
+        <v>672</v>
       </c>
       <c r="D12" s="12">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>695</v>
+        <v>669</v>
       </c>
       <c r="H12" t="s">
-        <v>498</v>
+        <v>472</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -3478,16 +3708,16 @@
         <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>699</v>
+        <v>673</v>
       </c>
       <c r="D13" s="12">
         <v>2</v>
       </c>
       <c r="E13" t="s">
-        <v>695</v>
+        <v>669</v>
       </c>
       <c r="H13" t="s">
-        <v>498</v>
+        <v>472</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -3501,25 +3731,25 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>467</v>
+        <v>441</v>
       </c>
       <c r="D14" s="12">
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>413</v>
+        <v>387</v>
       </c>
       <c r="G14" t="s">
-        <v>426</v>
+        <v>400</v>
       </c>
       <c r="H14" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>432</v>
+        <v>406</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
@@ -3530,25 +3760,25 @@
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>468</v>
+        <v>442</v>
       </c>
       <c r="D15" s="12">
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>413</v>
+        <v>387</v>
       </c>
       <c r="G15" t="s">
-        <v>429</v>
+        <v>403</v>
       </c>
       <c r="H15" t="s">
-        <v>498</v>
+        <v>472</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15" t="s">
-        <v>434</v>
+        <v>408</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
@@ -3559,19 +3789,19 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>727</v>
+        <v>701</v>
       </c>
       <c r="D16" s="12">
         <v>0</v>
       </c>
       <c r="E16" t="s">
-        <v>726</v>
+        <v>700</v>
       </c>
       <c r="G16" t="s">
-        <v>510</v>
+        <v>484</v>
       </c>
       <c r="H16" t="s">
-        <v>498</v>
+        <v>472</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -3585,19 +3815,19 @@
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>728</v>
+        <v>702</v>
       </c>
       <c r="D17" s="12">
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>726</v>
+        <v>700</v>
       </c>
       <c r="G17" t="s">
-        <v>511</v>
+        <v>485</v>
       </c>
       <c r="H17" t="s">
-        <v>498</v>
+        <v>472</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -3611,13 +3841,13 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>418</v>
+        <v>392</v>
       </c>
       <c r="D18" s="12">
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>711</v>
+        <v>685</v>
       </c>
       <c r="H18" t="s">
         <v>323</v>
@@ -3626,10 +3856,10 @@
         <v>0</v>
       </c>
       <c r="J18" t="s">
-        <v>419</v>
+        <v>393</v>
       </c>
       <c r="K18" t="s">
-        <v>541</v>
+        <v>515</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
@@ -3640,25 +3870,25 @@
         <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>420</v>
+        <v>394</v>
       </c>
       <c r="D19" s="12">
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>711</v>
+        <v>685</v>
       </c>
       <c r="H19" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
       <c r="J19" t="s">
-        <v>422</v>
+        <v>396</v>
       </c>
       <c r="K19" t="s">
-        <v>542</v>
+        <v>516</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
@@ -3669,25 +3899,25 @@
         <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>423</v>
+        <v>397</v>
       </c>
       <c r="D20" s="12">
         <v>2</v>
       </c>
       <c r="E20" t="s">
-        <v>711</v>
+        <v>685</v>
       </c>
       <c r="H20" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
       <c r="J20" t="s">
-        <v>424</v>
+        <v>398</v>
       </c>
       <c r="K20" t="s">
-        <v>543</v>
+        <v>517</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
@@ -3698,16 +3928,16 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>471</v>
+        <v>445</v>
       </c>
       <c r="D21" s="12" t="s">
+        <v>446</v>
+      </c>
+      <c r="E21" t="s">
+        <v>391</v>
+      </c>
+      <c r="H21" t="s">
         <v>472</v>
-      </c>
-      <c r="E21" t="s">
-        <v>417</v>
-      </c>
-      <c r="H21" t="s">
-        <v>498</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -3721,16 +3951,16 @@
         <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>473</v>
+        <v>447</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>474</v>
+        <v>448</v>
       </c>
       <c r="E22" t="s">
-        <v>417</v>
+        <v>391</v>
       </c>
       <c r="H22" t="s">
-        <v>498</v>
+        <v>472</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -3744,16 +3974,16 @@
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>475</v>
+        <v>449</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>476</v>
+        <v>450</v>
       </c>
       <c r="E23" t="s">
-        <v>417</v>
+        <v>391</v>
       </c>
       <c r="H23" t="s">
-        <v>498</v>
+        <v>472</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -3767,16 +3997,16 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>425</v>
+        <v>399</v>
       </c>
       <c r="D24" s="12">
         <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>714</v>
+        <v>688</v>
       </c>
       <c r="G24" t="s">
-        <v>426</v>
+        <v>400</v>
       </c>
       <c r="H24" t="s">
         <v>323</v>
@@ -3785,10 +4015,10 @@
         <v>0</v>
       </c>
       <c r="J24" t="s">
-        <v>427</v>
+        <v>401</v>
       </c>
       <c r="K24" t="s">
-        <v>544</v>
+        <v>518</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
@@ -3799,28 +4029,28 @@
         <v>2</v>
       </c>
       <c r="C25" t="s">
-        <v>428</v>
+        <v>402</v>
       </c>
       <c r="D25" s="12">
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>714</v>
+        <v>688</v>
       </c>
       <c r="G25" t="s">
-        <v>429</v>
+        <v>403</v>
       </c>
       <c r="H25" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="I25">
         <v>0</v>
       </c>
       <c r="J25" t="s">
-        <v>430</v>
+        <v>404</v>
       </c>
       <c r="K25" t="s">
-        <v>545</v>
+        <v>519</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
@@ -3831,16 +4061,16 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>431</v>
+        <v>405</v>
       </c>
       <c r="D26" s="12">
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>396</v>
+        <v>370</v>
       </c>
       <c r="G26" t="s">
-        <v>426</v>
+        <v>400</v>
       </c>
       <c r="H26" t="s">
         <v>323</v>
@@ -3849,10 +4079,10 @@
         <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>432</v>
+        <v>406</v>
       </c>
       <c r="K26" t="s">
-        <v>546</v>
+        <v>520</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
@@ -3863,28 +4093,28 @@
         <v>2</v>
       </c>
       <c r="C27" t="s">
-        <v>433</v>
+        <v>407</v>
       </c>
       <c r="D27" s="12">
         <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>713</v>
+        <v>687</v>
       </c>
       <c r="G27" t="s">
-        <v>429</v>
+        <v>403</v>
       </c>
       <c r="H27" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27" t="s">
-        <v>434</v>
+        <v>408</v>
       </c>
       <c r="K27" t="s">
-        <v>547</v>
+        <v>521</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
@@ -3895,16 +4125,16 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>441</v>
+        <v>415</v>
       </c>
       <c r="D28" s="12" t="s">
         <v>323</v>
       </c>
       <c r="E28" t="s">
-        <v>718</v>
+        <v>692</v>
       </c>
       <c r="G28" t="s">
-        <v>426</v>
+        <v>400</v>
       </c>
       <c r="H28" t="s">
         <v>323</v>
@@ -3913,10 +4143,10 @@
         <v>0</v>
       </c>
       <c r="J28" t="s">
-        <v>442</v>
+        <v>416</v>
       </c>
       <c r="K28" t="s">
-        <v>548</v>
+        <v>522</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
@@ -3927,28 +4157,28 @@
         <v>2</v>
       </c>
       <c r="C29" t="s">
-        <v>443</v>
+        <v>417</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="E29" t="s">
-        <v>718</v>
+        <v>692</v>
       </c>
       <c r="G29" t="s">
-        <v>429</v>
+        <v>403</v>
       </c>
       <c r="H29" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="I29">
         <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>444</v>
+        <v>418</v>
       </c>
       <c r="K29" t="s">
-        <v>549</v>
+        <v>523</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
@@ -3959,16 +4189,16 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>431</v>
+        <v>405</v>
       </c>
       <c r="D30" s="12">
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>407</v>
+        <v>381</v>
       </c>
       <c r="G30" t="s">
-        <v>426</v>
+        <v>400</v>
       </c>
       <c r="H30" t="s">
         <v>323</v>
@@ -3977,7 +4207,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>432</v>
+        <v>406</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
@@ -3988,25 +4218,25 @@
         <v>2</v>
       </c>
       <c r="C31" t="s">
-        <v>449</v>
+        <v>423</v>
       </c>
       <c r="D31" s="12">
         <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>407</v>
+        <v>381</v>
       </c>
       <c r="G31" t="s">
-        <v>429</v>
+        <v>403</v>
       </c>
       <c r="H31" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="I31">
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>450</v>
+        <v>424</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
@@ -4017,16 +4247,16 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>445</v>
+        <v>419</v>
       </c>
       <c r="D32" s="12">
         <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>404</v>
+        <v>378</v>
       </c>
       <c r="G32" t="s">
-        <v>446</v>
+        <v>420</v>
       </c>
       <c r="H32" t="s">
         <v>323</v>
@@ -4035,7 +4265,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>445</v>
+        <v>419</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
@@ -4046,25 +4276,25 @@
         <v>2</v>
       </c>
       <c r="C33" t="s">
-        <v>447</v>
+        <v>421</v>
       </c>
       <c r="D33" s="12">
         <v>2</v>
       </c>
       <c r="E33" t="s">
-        <v>404</v>
+        <v>378</v>
       </c>
       <c r="G33" t="s">
-        <v>448</v>
+        <v>422</v>
       </c>
       <c r="H33" t="s">
+        <v>395</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33" t="s">
         <v>421</v>
-      </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
-      <c r="J33" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
@@ -4075,25 +4305,25 @@
         <v>0</v>
       </c>
       <c r="C34" t="s">
-        <v>451</v>
+        <v>425</v>
       </c>
       <c r="D34" s="12">
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>410</v>
+        <v>384</v>
       </c>
       <c r="G34" t="s">
-        <v>452</v>
+        <v>426</v>
       </c>
       <c r="H34" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34" t="s">
-        <v>453</v>
+        <v>427</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
@@ -4110,19 +4340,19 @@
         <v>1</v>
       </c>
       <c r="E35" t="s">
-        <v>410</v>
+        <v>384</v>
       </c>
       <c r="G35" t="s">
-        <v>452</v>
+        <v>426</v>
       </c>
       <c r="H35" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
       <c r="J35" t="s">
-        <v>454</v>
+        <v>428</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
@@ -4139,19 +4369,19 @@
         <v>2</v>
       </c>
       <c r="E36" t="s">
-        <v>410</v>
+        <v>384</v>
       </c>
       <c r="G36" t="s">
-        <v>452</v>
+        <v>426</v>
       </c>
       <c r="H36" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="I36">
         <v>0</v>
       </c>
       <c r="J36" t="s">
-        <v>455</v>
+        <v>429</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
@@ -4168,19 +4398,19 @@
         <v>3</v>
       </c>
       <c r="E37" t="s">
-        <v>410</v>
+        <v>384</v>
       </c>
       <c r="G37" t="s">
-        <v>429</v>
+        <v>403</v>
       </c>
       <c r="H37" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="I37">
         <v>0</v>
       </c>
       <c r="J37" t="s">
-        <v>456</v>
+        <v>430</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
@@ -4191,25 +4421,25 @@
         <v>4</v>
       </c>
       <c r="C38" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="D38" s="12">
         <v>4</v>
       </c>
       <c r="E38" t="s">
-        <v>410</v>
+        <v>384</v>
       </c>
       <c r="G38" t="s">
-        <v>426</v>
+        <v>400</v>
       </c>
       <c r="H38" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="I38">
         <v>0</v>
       </c>
       <c r="J38" t="s">
-        <v>458</v>
+        <v>432</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
@@ -4226,19 +4456,19 @@
         <v>5</v>
       </c>
       <c r="E39" t="s">
-        <v>410</v>
+        <v>384</v>
       </c>
       <c r="G39" t="s">
-        <v>446</v>
+        <v>420</v>
       </c>
       <c r="H39" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="I39">
         <v>0</v>
       </c>
       <c r="J39" t="s">
-        <v>459</v>
+        <v>433</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
@@ -4249,25 +4479,25 @@
         <v>6</v>
       </c>
       <c r="C40" t="s">
-        <v>460</v>
+        <v>434</v>
       </c>
       <c r="D40" s="12">
         <v>6</v>
       </c>
       <c r="E40" t="s">
-        <v>410</v>
+        <v>384</v>
       </c>
       <c r="G40" t="s">
-        <v>446</v>
+        <v>420</v>
       </c>
       <c r="H40" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="I40">
         <v>0</v>
       </c>
       <c r="J40" t="s">
-        <v>461</v>
+        <v>435</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
@@ -4278,25 +4508,25 @@
         <v>7</v>
       </c>
       <c r="C41" t="s">
-        <v>462</v>
+        <v>436</v>
       </c>
       <c r="D41" s="12">
         <v>7</v>
       </c>
       <c r="E41" t="s">
-        <v>410</v>
+        <v>384</v>
       </c>
       <c r="G41" t="s">
-        <v>429</v>
+        <v>403</v>
       </c>
       <c r="H41" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="I41">
         <v>0</v>
       </c>
       <c r="J41" t="s">
-        <v>463</v>
+        <v>437</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
@@ -4313,19 +4543,19 @@
         <v>8</v>
       </c>
       <c r="E42" t="s">
-        <v>410</v>
+        <v>384</v>
       </c>
       <c r="G42" t="s">
-        <v>446</v>
+        <v>420</v>
       </c>
       <c r="H42" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="I42">
         <v>0</v>
       </c>
       <c r="J42" t="s">
-        <v>464</v>
+        <v>438</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
@@ -4336,25 +4566,25 @@
         <v>9</v>
       </c>
       <c r="C43" t="s">
-        <v>465</v>
+        <v>439</v>
       </c>
       <c r="D43" s="12">
         <v>9</v>
       </c>
       <c r="E43" t="s">
-        <v>410</v>
+        <v>384</v>
       </c>
       <c r="G43" t="s">
-        <v>429</v>
+        <v>403</v>
       </c>
       <c r="H43" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="I43">
         <v>0</v>
       </c>
       <c r="J43" t="s">
-        <v>466</v>
+        <v>440</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
@@ -4365,13 +4595,13 @@
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>436</v>
+        <v>410</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>437</v>
+        <v>411</v>
       </c>
       <c r="E44" t="s">
-        <v>719</v>
+        <v>693</v>
       </c>
       <c r="H44" t="s">
         <v>323</v>
@@ -4380,10 +4610,10 @@
         <v>0</v>
       </c>
       <c r="J44" t="s">
-        <v>438</v>
+        <v>412</v>
       </c>
       <c r="K44" t="s">
-        <v>551</v>
+        <v>525</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
@@ -4394,25 +4624,25 @@
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>439</v>
+        <v>413</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>370</v>
+        <v>344</v>
       </c>
       <c r="E45" t="s">
-        <v>719</v>
+        <v>693</v>
       </c>
       <c r="H45" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="I45">
         <v>0</v>
       </c>
       <c r="J45" t="s">
-        <v>440</v>
+        <v>414</v>
       </c>
       <c r="K45" t="s">
-        <v>550</v>
+        <v>524</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
@@ -4423,16 +4653,16 @@
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>431</v>
+        <v>405</v>
       </c>
       <c r="D46" s="12">
         <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>720</v>
+        <v>694</v>
       </c>
       <c r="G46" t="s">
-        <v>426</v>
+        <v>400</v>
       </c>
       <c r="H46" t="s">
         <v>323</v>
@@ -4441,10 +4671,10 @@
         <v>0</v>
       </c>
       <c r="J46" t="s">
-        <v>432</v>
+        <v>406</v>
       </c>
       <c r="K46" t="s">
-        <v>546</v>
+        <v>520</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.2">
@@ -4455,28 +4685,28 @@
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>435</v>
+        <v>409</v>
       </c>
       <c r="D47" s="12">
         <v>1</v>
       </c>
       <c r="E47" t="s">
-        <v>720</v>
+        <v>694</v>
       </c>
       <c r="G47" t="s">
-        <v>429</v>
+        <v>403</v>
       </c>
       <c r="H47" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="I47">
         <v>0</v>
       </c>
       <c r="J47" t="s">
-        <v>434</v>
+        <v>408</v>
       </c>
       <c r="K47" t="s">
-        <v>552</v>
+        <v>526</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
@@ -4487,19 +4717,19 @@
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>506</v>
+        <v>480</v>
       </c>
       <c r="D48" s="12">
         <v>1</v>
       </c>
       <c r="E48" t="s">
-        <v>721</v>
+        <v>695</v>
       </c>
       <c r="G48" t="s">
-        <v>509</v>
+        <v>483</v>
       </c>
       <c r="H48" t="s">
-        <v>498</v>
+        <v>472</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -4513,19 +4743,19 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>507</v>
+        <v>481</v>
       </c>
       <c r="D49" s="12">
         <v>2</v>
       </c>
       <c r="E49" t="s">
-        <v>721</v>
+        <v>695</v>
       </c>
       <c r="G49" t="s">
-        <v>510</v>
+        <v>484</v>
       </c>
       <c r="H49" t="s">
-        <v>498</v>
+        <v>472</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -4539,19 +4769,19 @@
         <v>3</v>
       </c>
       <c r="C50" t="s">
-        <v>508</v>
+        <v>482</v>
       </c>
       <c r="D50" s="12">
         <v>3</v>
       </c>
       <c r="E50" t="s">
-        <v>721</v>
+        <v>695</v>
       </c>
       <c r="G50" t="s">
-        <v>511</v>
+        <v>485</v>
       </c>
       <c r="H50" t="s">
-        <v>498</v>
+        <v>472</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -4575,25 +4805,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>493</v>
+        <v>467</v>
       </c>
       <c r="B1" t="s">
-        <v>494</v>
+        <v>468</v>
       </c>
       <c r="C1" t="s">
-        <v>495</v>
+        <v>469</v>
       </c>
       <c r="D1" t="s">
-        <v>496</v>
+        <v>470</v>
       </c>
       <c r="E1" t="s">
-        <v>705</v>
+        <v>679</v>
       </c>
       <c r="F1" t="s">
-        <v>706</v>
+        <v>680</v>
       </c>
       <c r="G1" t="s">
-        <v>707</v>
+        <v>681</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -4604,7 +4834,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>503</v>
+        <v>477</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -4624,7 +4854,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>489</v>
+        <v>463</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -4644,7 +4874,7 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>490</v>
+        <v>464</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -4664,7 +4894,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>491</v>
+        <v>465</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -4684,7 +4914,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>492</v>
+        <v>466</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -4714,19 +4944,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>502</v>
+        <v>476</v>
       </c>
       <c r="B1" t="s">
-        <v>376</v>
+        <v>350</v>
       </c>
       <c r="C1" t="s">
         <v>285</v>
       </c>
       <c r="D1" t="s">
-        <v>638</v>
+        <v>612</v>
       </c>
       <c r="E1" t="s">
-        <v>639</v>
+        <v>613</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -4734,7 +4964,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>635</v>
+        <v>609</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -4743,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>640</v>
+        <v>614</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -4751,7 +4981,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>636</v>
+        <v>610</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -4760,7 +4990,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>641</v>
+        <v>615</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -4768,7 +4998,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>637</v>
+        <v>611</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -4777,7 +5007,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>642</v>
+        <v>616</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -4785,7 +5015,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>451</v>
+        <v>425</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -4794,7 +5024,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>643</v>
+        <v>617</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -4802,7 +5032,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>658</v>
+        <v>632</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -4828,15 +5058,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>647</v>
+        <v>621</v>
       </c>
       <c r="B1" t="s">
-        <v>648</v>
+        <v>622</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>649</v>
+        <v>623</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -4844,7 +5074,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>650</v>
+        <v>624</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4852,7 +5082,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>651</v>
+        <v>625</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4860,7 +5090,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>652</v>
+        <v>626</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -4868,7 +5098,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>653</v>
+        <v>627</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -4891,16 +5121,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>620</v>
+        <v>594</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>621</v>
+        <v>595</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>622</v>
+        <v>596</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>623</v>
+        <v>597</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>292</v>
@@ -4911,13 +5141,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>619</v>
+        <v>593</v>
       </c>
       <c r="C2" s="9">
         <v>2</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>680</v>
+        <v>654</v>
       </c>
       <c r="E2" s="9">
         <v>0</v>
@@ -5171,7 +5401,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>531</v>
+        <v>505</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -5183,7 +5413,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>532</v>
+        <v>506</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5192,10 +5422,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>593</v>
+        <v>567</v>
       </c>
       <c r="N7" t="s">
-        <v>617</v>
+        <v>591</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -5203,7 +5433,7 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>582</v>
+        <v>556</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -5212,7 +5442,7 @@
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>556</v>
+        <v>530</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -5227,10 +5457,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="s">
-        <v>556</v>
+        <v>530</v>
       </c>
       <c r="N8" t="s">
-        <v>610</v>
+        <v>584</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -5238,7 +5468,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>526</v>
+        <v>500</v>
       </c>
       <c r="C9">
         <v>7</v>
@@ -5247,16 +5477,16 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>530</v>
+        <v>504</v>
       </c>
       <c r="F9" t="s">
-        <v>527</v>
+        <v>501</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>519</v>
+        <v>493</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -5265,10 +5495,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="s">
-        <v>528</v>
+        <v>502</v>
       </c>
       <c r="N9" t="s">
-        <v>529</v>
+        <v>503</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -5276,7 +5506,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>597</v>
+        <v>571</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -5285,16 +5515,16 @@
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>702</v>
+        <v>676</v>
       </c>
       <c r="F10" t="s">
-        <v>598</v>
+        <v>572</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>532</v>
+        <v>506</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -5303,13 +5533,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>600</v>
+        <v>574</v>
       </c>
       <c r="L10" t="s">
-        <v>599</v>
+        <v>573</v>
       </c>
       <c r="N10" t="s">
-        <v>611</v>
+        <v>585</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -5408,7 +5638,7 @@
         <v>3</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>703</v>
+        <v>677</v>
       </c>
       <c r="F13" t="s">
         <v>32</v>
@@ -5727,7 +5957,7 @@
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>501</v>
+        <v>475</v>
       </c>
       <c r="F21" t="s">
         <v>74</v>
@@ -6008,7 +6238,7 @@
         <v>4</v>
       </c>
       <c r="E28" t="s">
-        <v>594</v>
+        <v>568</v>
       </c>
       <c r="F28" t="s">
         <v>109</v>
@@ -6026,10 +6256,10 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="L28" t="s">
-        <v>595</v>
+        <v>569</v>
       </c>
       <c r="N28" t="s">
         <v>110</v>
@@ -6040,7 +6270,7 @@
         <v>118</v>
       </c>
       <c r="B29" t="s">
-        <v>625</v>
+        <v>599</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -6075,7 +6305,7 @@
         <v>119</v>
       </c>
       <c r="B30" t="s">
-        <v>626</v>
+        <v>600</v>
       </c>
       <c r="C30">
         <v>118</v>
@@ -6087,7 +6317,7 @@
         <v>114</v>
       </c>
       <c r="F30" t="s">
-        <v>601</v>
+        <v>575</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -6116,7 +6346,7 @@
         <v>500</v>
       </c>
       <c r="B31" t="s">
-        <v>664</v>
+        <v>638</v>
       </c>
       <c r="C31">
         <v>108</v>
@@ -6143,7 +6373,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>701</v>
+        <v>675</v>
       </c>
       <c r="L31" t="s">
         <v>120</v>
@@ -6184,7 +6414,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>700</v>
+        <v>674</v>
       </c>
       <c r="L32" t="s">
         <v>123</v>
@@ -6198,7 +6428,7 @@
         <v>502</v>
       </c>
       <c r="B33" t="s">
-        <v>516</v>
+        <v>490</v>
       </c>
       <c r="C33">
         <v>108</v>
@@ -6207,16 +6437,16 @@
         <v>3</v>
       </c>
       <c r="E33" t="s">
-        <v>517</v>
+        <v>491</v>
       </c>
       <c r="F33" t="s">
-        <v>518</v>
+        <v>492</v>
       </c>
       <c r="G33">
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>519</v>
+        <v>493</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -6225,13 +6455,13 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>523</v>
+        <v>497</v>
       </c>
       <c r="L33" t="s">
-        <v>520</v>
+        <v>494</v>
       </c>
       <c r="N33" t="s">
-        <v>615</v>
+        <v>589</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
@@ -7663,7 +7893,7 @@
         <v>1047</v>
       </c>
       <c r="B80" t="s">
-        <v>691</v>
+        <v>665</v>
       </c>
       <c r="C80">
         <v>118</v>
@@ -7672,16 +7902,16 @@
         <v>2</v>
       </c>
       <c r="E80" t="s">
-        <v>591</v>
+        <v>565</v>
       </c>
       <c r="F80" t="s">
-        <v>624</v>
+        <v>598</v>
       </c>
       <c r="G80">
         <v>0</v>
       </c>
       <c r="H80" t="s">
-        <v>519</v>
+        <v>493</v>
       </c>
       <c r="I80">
         <v>1</v>
@@ -7690,7 +7920,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>592</v>
+        <v>566</v>
       </c>
       <c r="L80" t="s">
         <v>64</v>
@@ -7701,7 +7931,7 @@
         <v>1049</v>
       </c>
       <c r="B81" t="s">
-        <v>627</v>
+        <v>601</v>
       </c>
       <c r="C81">
         <v>119</v>
@@ -7733,19 +7963,19 @@
         <v>1048</v>
       </c>
       <c r="B82" t="s">
-        <v>690</v>
+        <v>664</v>
       </c>
       <c r="C82">
         <v>119</v>
       </c>
       <c r="E82" t="s">
-        <v>514</v>
+        <v>488</v>
       </c>
       <c r="G82">
         <v>0</v>
       </c>
       <c r="H82" t="s">
-        <v>513</v>
+        <v>487</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -7754,7 +7984,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>692</v>
+        <v>666</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.2">
@@ -7762,7 +7992,7 @@
         <v>1050</v>
       </c>
       <c r="B83" t="s">
-        <v>628</v>
+        <v>602</v>
       </c>
       <c r="C83">
         <v>119</v>
@@ -8417,7 +8647,7 @@
         <v>999</v>
       </c>
       <c r="E103" t="s">
-        <v>679</v>
+        <v>653</v>
       </c>
       <c r="F103" t="s">
         <v>268</v>
@@ -8577,7 +8807,7 @@
         <v>1090</v>
       </c>
       <c r="B108" t="s">
-        <v>515</v>
+        <v>489</v>
       </c>
       <c r="C108">
         <v>1078</v>
@@ -8586,13 +8816,13 @@
         <v>5</v>
       </c>
       <c r="E108" t="s">
-        <v>514</v>
+        <v>488</v>
       </c>
       <c r="G108">
         <v>0</v>
       </c>
       <c r="H108" t="s">
-        <v>513</v>
+        <v>487</v>
       </c>
       <c r="I108">
         <v>0</v>
@@ -8601,7 +8831,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>512</v>
+        <v>486</v>
       </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.2">
@@ -8641,7 +8871,7 @@
         <v>1084</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>629</v>
+        <v>603</v>
       </c>
       <c r="C110" s="4">
         <v>118</v>
@@ -8650,10 +8880,10 @@
         <v>999</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>678</v>
+        <v>652</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>602</v>
+        <v>576</v>
       </c>
       <c r="G110" s="4">
         <v>0</v>
@@ -8675,7 +8905,7 @@
       </c>
       <c r="M110" s="4"/>
       <c r="N110" t="s">
-        <v>612</v>
+        <v>586</v>
       </c>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.2">
@@ -8858,7 +9088,7 @@
         <v>1092</v>
       </c>
       <c r="B116" t="s">
-        <v>533</v>
+        <v>507</v>
       </c>
       <c r="C116">
         <v>111</v>
@@ -8870,19 +9100,19 @@
         <v>0</v>
       </c>
       <c r="H116" t="s">
+        <v>487</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+      <c r="J116">
+        <v>0</v>
+      </c>
+      <c r="K116" t="s">
+        <v>508</v>
+      </c>
+      <c r="M116" t="s">
         <v>513</v>
-      </c>
-      <c r="I116">
-        <v>0</v>
-      </c>
-      <c r="J116">
-        <v>0</v>
-      </c>
-      <c r="K116" t="s">
-        <v>534</v>
-      </c>
-      <c r="M116" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.2">
@@ -8890,7 +9120,7 @@
         <v>1091</v>
       </c>
       <c r="B117" t="s">
-        <v>536</v>
+        <v>510</v>
       </c>
       <c r="C117">
         <v>111</v>
@@ -8902,19 +9132,19 @@
         <v>0</v>
       </c>
       <c r="H117" t="s">
+        <v>487</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+      <c r="J117">
+        <v>0</v>
+      </c>
+      <c r="K117" t="s">
+        <v>509</v>
+      </c>
+      <c r="M117" t="s">
         <v>513</v>
-      </c>
-      <c r="I117">
-        <v>0</v>
-      </c>
-      <c r="J117">
-        <v>0</v>
-      </c>
-      <c r="K117" t="s">
-        <v>535</v>
-      </c>
-      <c r="M117" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.2">
@@ -8922,7 +9152,7 @@
         <v>1102</v>
       </c>
       <c r="B118" t="s">
-        <v>521</v>
+        <v>495</v>
       </c>
       <c r="C118">
         <v>502</v>
@@ -8934,7 +9164,7 @@
         <v>0</v>
       </c>
       <c r="H118" t="s">
-        <v>513</v>
+        <v>487</v>
       </c>
       <c r="I118">
         <v>0</v>
@@ -8943,10 +9173,10 @@
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>524</v>
+        <v>498</v>
       </c>
       <c r="M118" t="s">
-        <v>538</v>
+        <v>512</v>
       </c>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.2">
@@ -8954,7 +9184,7 @@
         <v>1103</v>
       </c>
       <c r="B119" t="s">
-        <v>522</v>
+        <v>496</v>
       </c>
       <c r="C119">
         <v>502</v>
@@ -8966,7 +9196,7 @@
         <v>0</v>
       </c>
       <c r="H119" t="s">
-        <v>513</v>
+        <v>487</v>
       </c>
       <c r="I119">
         <v>0</v>
@@ -8975,10 +9205,10 @@
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>525</v>
+        <v>499</v>
       </c>
       <c r="M119" t="s">
-        <v>537</v>
+        <v>511</v>
       </c>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.2">
@@ -8986,7 +9216,7 @@
         <v>1104</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>553</v>
+        <v>527</v>
       </c>
       <c r="C120" s="5">
         <v>9</v>
@@ -8995,16 +9225,16 @@
         <v>1</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>556</v>
+        <v>530</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>557</v>
+        <v>531</v>
       </c>
       <c r="G120" s="5">
         <v>0</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>519</v>
+        <v>493</v>
       </c>
       <c r="I120" s="5">
         <v>0</v>
@@ -9013,14 +9243,14 @@
         <v>0</v>
       </c>
       <c r="K120" s="5" t="s">
-        <v>563</v>
+        <v>537</v>
       </c>
       <c r="L120" s="5" t="s">
-        <v>565</v>
+        <v>539</v>
       </c>
       <c r="M120" s="5"/>
       <c r="N120" t="s">
-        <v>613</v>
+        <v>587</v>
       </c>
     </row>
     <row r="121" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -9028,7 +9258,7 @@
         <v>1105</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>558</v>
+        <v>532</v>
       </c>
       <c r="C121" s="5">
         <v>1104</v>
@@ -9042,7 +9272,7 @@
         <v>0</v>
       </c>
       <c r="H121" s="5" t="s">
-        <v>513</v>
+        <v>487</v>
       </c>
       <c r="I121" s="5">
         <v>0</v>
@@ -9051,7 +9281,7 @@
         <v>0</v>
       </c>
       <c r="K121" s="5" t="s">
-        <v>560</v>
+        <v>534</v>
       </c>
       <c r="L121" s="5"/>
       <c r="M121" s="5"/>
@@ -9061,7 +9291,7 @@
         <v>1106</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>559</v>
+        <v>533</v>
       </c>
       <c r="C122" s="5">
         <v>1104</v>
@@ -9075,7 +9305,7 @@
         <v>0</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>513</v>
+        <v>487</v>
       </c>
       <c r="I122" s="5">
         <v>0</v>
@@ -9084,7 +9314,7 @@
         <v>0</v>
       </c>
       <c r="K122" s="5" t="s">
-        <v>561</v>
+        <v>535</v>
       </c>
       <c r="L122" s="5"/>
       <c r="M122" s="5"/>
@@ -9094,7 +9324,7 @@
         <v>1107</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>521</v>
+        <v>495</v>
       </c>
       <c r="C123" s="5">
         <v>1104</v>
@@ -9108,7 +9338,7 @@
         <v>0</v>
       </c>
       <c r="H123" s="5" t="s">
-        <v>513</v>
+        <v>487</v>
       </c>
       <c r="I123" s="5">
         <v>0</v>
@@ -9117,7 +9347,7 @@
         <v>0</v>
       </c>
       <c r="K123" s="5" t="s">
-        <v>562</v>
+        <v>536</v>
       </c>
       <c r="L123" s="5"/>
       <c r="M123" s="5"/>
@@ -9127,7 +9357,7 @@
         <v>1108</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>574</v>
+        <v>548</v>
       </c>
       <c r="C124" s="6">
         <v>108</v>
@@ -9136,16 +9366,16 @@
         <v>1</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>569</v>
+        <v>543</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>570</v>
+        <v>544</v>
       </c>
       <c r="G124" s="6">
         <v>0</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>519</v>
+        <v>493</v>
       </c>
       <c r="I124" s="6">
         <v>0</v>
@@ -9154,14 +9384,14 @@
         <v>0</v>
       </c>
       <c r="K124" s="6" t="s">
-        <v>571</v>
+        <v>545</v>
       </c>
       <c r="L124" s="6" t="s">
-        <v>566</v>
+        <v>540</v>
       </c>
       <c r="M124" s="6"/>
       <c r="N124" t="s">
-        <v>616</v>
+        <v>590</v>
       </c>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.2">
@@ -9169,7 +9399,7 @@
         <v>1109</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>567</v>
+        <v>541</v>
       </c>
       <c r="C125" s="6">
         <v>1108</v>
@@ -9183,7 +9413,7 @@
         <v>0</v>
       </c>
       <c r="H125" s="6" t="s">
-        <v>513</v>
+        <v>487</v>
       </c>
       <c r="I125" s="6">
         <v>0</v>
@@ -9192,7 +9422,7 @@
         <v>0</v>
       </c>
       <c r="K125" s="6" t="s">
-        <v>572</v>
+        <v>546</v>
       </c>
       <c r="L125" s="6"/>
       <c r="M125" s="6"/>
@@ -9202,7 +9432,7 @@
         <v>1110</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>568</v>
+        <v>542</v>
       </c>
       <c r="C126" s="6">
         <v>1108</v>
@@ -9216,7 +9446,7 @@
         <v>0</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>513</v>
+        <v>487</v>
       </c>
       <c r="I126" s="6">
         <v>0</v>
@@ -9225,7 +9455,7 @@
         <v>0</v>
       </c>
       <c r="K126" s="6" t="s">
-        <v>573</v>
+        <v>547</v>
       </c>
       <c r="L126" s="6"/>
       <c r="M126" s="6"/>
@@ -9235,7 +9465,7 @@
         <v>1111</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>583</v>
+        <v>557</v>
       </c>
       <c r="C127" s="4">
         <v>9</v>
@@ -9244,16 +9474,16 @@
         <v>1</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>584</v>
+        <v>558</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>585</v>
+        <v>559</v>
       </c>
       <c r="G127" s="4">
         <v>0</v>
       </c>
       <c r="H127" s="4" t="s">
-        <v>519</v>
+        <v>493</v>
       </c>
       <c r="I127" s="4">
         <v>0</v>
@@ -9262,16 +9492,16 @@
         <v>0</v>
       </c>
       <c r="K127" s="4" t="s">
-        <v>586</v>
+        <v>560</v>
       </c>
       <c r="L127" s="4" t="s">
-        <v>584</v>
+        <v>558</v>
       </c>
       <c r="M127" s="4" t="s">
-        <v>583</v>
+        <v>557</v>
       </c>
       <c r="N127" s="4" t="s">
-        <v>618</v>
+        <v>592</v>
       </c>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.2">
@@ -9279,7 +9509,7 @@
         <v>1112</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>589</v>
+        <v>563</v>
       </c>
       <c r="C128" s="4">
         <v>1111</v>
@@ -9293,7 +9523,7 @@
         <v>0</v>
       </c>
       <c r="H128" s="4" t="s">
-        <v>513</v>
+        <v>487</v>
       </c>
       <c r="I128" s="4">
         <v>0</v>
@@ -9302,7 +9532,7 @@
         <v>0</v>
       </c>
       <c r="K128" s="4" t="s">
-        <v>587</v>
+        <v>561</v>
       </c>
       <c r="L128" s="4"/>
       <c r="M128" s="4"/>
@@ -9312,7 +9542,7 @@
         <v>1113</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>590</v>
+        <v>564</v>
       </c>
       <c r="C129" s="4">
         <v>1111</v>
@@ -9326,7 +9556,7 @@
         <v>0</v>
       </c>
       <c r="H129" s="4" t="s">
-        <v>513</v>
+        <v>487</v>
       </c>
       <c r="I129" s="4">
         <v>0</v>
@@ -9335,7 +9565,7 @@
         <v>0</v>
       </c>
       <c r="K129" s="4" t="s">
-        <v>588</v>
+        <v>562</v>
       </c>
       <c r="L129" s="4"/>
       <c r="M129" s="4"/>
@@ -9345,7 +9575,7 @@
         <v>1114</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>607</v>
+        <v>581</v>
       </c>
       <c r="C130" s="7">
         <v>2</v>
@@ -9354,16 +9584,16 @@
         <v>1</v>
       </c>
       <c r="E130" s="7" t="s">
-        <v>677</v>
+        <v>651</v>
       </c>
       <c r="F130" s="7" t="s">
-        <v>603</v>
+        <v>577</v>
       </c>
       <c r="G130" s="7">
         <v>0</v>
       </c>
       <c r="H130" s="7" t="s">
-        <v>519</v>
+        <v>493</v>
       </c>
       <c r="I130" s="7">
         <v>0</v>
@@ -9372,14 +9602,14 @@
         <v>0</v>
       </c>
       <c r="K130" s="7" t="s">
-        <v>604</v>
+        <v>578</v>
       </c>
       <c r="L130" s="7" t="s">
-        <v>520</v>
+        <v>494</v>
       </c>
       <c r="M130" s="7"/>
       <c r="N130" t="s">
-        <v>614</v>
+        <v>588</v>
       </c>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.2">
@@ -9387,7 +9617,7 @@
         <v>1115</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>608</v>
+        <v>582</v>
       </c>
       <c r="C131" s="7">
         <v>1114</v>
@@ -9401,7 +9631,7 @@
         <v>0</v>
       </c>
       <c r="H131" s="7" t="s">
-        <v>513</v>
+        <v>487</v>
       </c>
       <c r="I131" s="7">
         <v>0</v>
@@ -9410,7 +9640,7 @@
         <v>0</v>
       </c>
       <c r="K131" s="7" t="s">
-        <v>606</v>
+        <v>580</v>
       </c>
       <c r="L131" s="7"/>
       <c r="M131" s="7"/>
@@ -9420,7 +9650,7 @@
         <v>1116</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>609</v>
+        <v>583</v>
       </c>
       <c r="C132" s="7">
         <v>1114</v>
@@ -9434,7 +9664,7 @@
         <v>0</v>
       </c>
       <c r="H132" s="7" t="s">
-        <v>513</v>
+        <v>487</v>
       </c>
       <c r="I132" s="7">
         <v>0</v>
@@ -9443,7 +9673,7 @@
         <v>0</v>
       </c>
       <c r="K132" s="7" t="s">
-        <v>605</v>
+        <v>579</v>
       </c>
       <c r="L132" s="7"/>
       <c r="M132" s="7"/>
@@ -9453,7 +9683,7 @@
         <v>1093</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>667</v>
+        <v>641</v>
       </c>
       <c r="C133" s="4">
         <v>0</v>
@@ -9462,10 +9692,10 @@
         <v>999</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>668</v>
+        <v>642</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>669</v>
+        <v>643</v>
       </c>
       <c r="G133" s="4">
         <v>0</v>
@@ -9480,10 +9710,10 @@
         <v>1</v>
       </c>
       <c r="K133" s="4" t="s">
-        <v>670</v>
+        <v>644</v>
       </c>
       <c r="L133" s="4" t="s">
-        <v>671</v>
+        <v>645</v>
       </c>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.2">
@@ -9516,7 +9746,7 @@
         <v>0</v>
       </c>
       <c r="K134" s="4" t="s">
-        <v>672</v>
+        <v>646</v>
       </c>
       <c r="L134" s="4"/>
     </row>
@@ -9550,7 +9780,7 @@
         <v>0</v>
       </c>
       <c r="K135" s="4" t="s">
-        <v>673</v>
+        <v>647</v>
       </c>
       <c r="L135" s="4"/>
     </row>
@@ -9584,7 +9814,7 @@
         <v>0</v>
       </c>
       <c r="K136" s="4" t="s">
-        <v>674</v>
+        <v>648</v>
       </c>
       <c r="L136" s="4"/>
     </row>
@@ -9618,7 +9848,7 @@
         <v>0</v>
       </c>
       <c r="K137" s="4" t="s">
-        <v>675</v>
+        <v>649</v>
       </c>
       <c r="L137" s="4"/>
     </row>
@@ -9652,7 +9882,7 @@
         <v>0</v>
       </c>
       <c r="K138" s="4" t="s">
-        <v>676</v>
+        <v>650</v>
       </c>
       <c r="L138" s="4"/>
     </row>
@@ -9661,7 +9891,7 @@
         <v>1117</v>
       </c>
       <c r="B139" s="15" t="s">
-        <v>682</v>
+        <v>656</v>
       </c>
       <c r="C139" s="15">
         <v>118</v>
@@ -9670,10 +9900,10 @@
         <v>999</v>
       </c>
       <c r="E139" s="15" t="s">
-        <v>693</v>
+        <v>667</v>
       </c>
       <c r="F139" s="16" t="s">
-        <v>689</v>
+        <v>663</v>
       </c>
       <c r="G139" s="15">
         <v>0</v>
@@ -9688,10 +9918,10 @@
         <v>0</v>
       </c>
       <c r="K139" s="15" t="s">
-        <v>683</v>
+        <v>657</v>
       </c>
       <c r="L139" s="15" t="s">
-        <v>565</v>
+        <v>539</v>
       </c>
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.2">
@@ -9724,7 +9954,7 @@
         <v>0</v>
       </c>
       <c r="K140" s="15" t="s">
-        <v>684</v>
+        <v>658</v>
       </c>
       <c r="L140" s="15"/>
     </row>
@@ -9758,7 +9988,7 @@
         <v>0</v>
       </c>
       <c r="K141" s="15" t="s">
-        <v>685</v>
+        <v>659</v>
       </c>
       <c r="L141" s="15"/>
     </row>
@@ -9792,7 +10022,7 @@
         <v>0</v>
       </c>
       <c r="K142" s="15" t="s">
-        <v>686</v>
+        <v>660</v>
       </c>
       <c r="L142" s="15"/>
     </row>
@@ -9826,7 +10056,7 @@
         <v>0</v>
       </c>
       <c r="K143" s="15" t="s">
-        <v>687</v>
+        <v>661</v>
       </c>
       <c r="L143" s="15"/>
     </row>
@@ -9860,7 +10090,7 @@
         <v>0</v>
       </c>
       <c r="K144" s="15" t="s">
-        <v>688</v>
+        <v>662</v>
       </c>
       <c r="L144" s="15"/>
     </row>
@@ -10001,10 +10231,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>578</v>
+        <v>552</v>
       </c>
       <c r="C4" t="s">
-        <v>575</v>
+        <v>549</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -10025,7 +10255,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="s">
-        <v>578</v>
+        <v>552</v>
       </c>
     </row>
   </sheetData>
@@ -10042,10 +10272,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>367</v>
+        <v>341</v>
       </c>
       <c r="B1" t="s">
-        <v>368</v>
+        <v>342</v>
       </c>
       <c r="C1" t="s">
         <v>311</v>
@@ -10267,7 +10497,7 @@
         <v>1084</v>
       </c>
       <c r="C28" t="s">
-        <v>579</v>
+        <v>553</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -10278,7 +10508,7 @@
         <v>1085</v>
       </c>
       <c r="C29" t="s">
-        <v>579</v>
+        <v>553</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -10289,7 +10519,7 @@
         <v>1086</v>
       </c>
       <c r="C30" t="s">
-        <v>579</v>
+        <v>553</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
@@ -10300,7 +10530,7 @@
         <v>1087</v>
       </c>
       <c r="C31" t="s">
-        <v>579</v>
+        <v>553</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -10311,7 +10541,7 @@
         <v>1088</v>
       </c>
       <c r="C32" t="s">
-        <v>579</v>
+        <v>553</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -10322,7 +10552,7 @@
         <v>1089</v>
       </c>
       <c r="C33" t="s">
-        <v>579</v>
+        <v>553</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -10333,7 +10563,7 @@
         <v>1048</v>
       </c>
       <c r="C34" t="s">
-        <v>580</v>
+        <v>554</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -10344,7 +10574,7 @@
         <v>1049</v>
       </c>
       <c r="C35" t="s">
-        <v>580</v>
+        <v>554</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
@@ -10355,7 +10585,7 @@
         <v>1050</v>
       </c>
       <c r="C36" t="s">
-        <v>580</v>
+        <v>554</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -10366,7 +10596,7 @@
         <v>119</v>
       </c>
       <c r="C37" t="s">
-        <v>580</v>
+        <v>554</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
@@ -10377,7 +10607,7 @@
         <v>3</v>
       </c>
       <c r="C38" t="s">
-        <v>581</v>
+        <v>555</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
@@ -10440,7 +10670,7 @@
         <v>324</v>
       </c>
       <c r="C2" t="s">
-        <v>704</v>
+        <v>678</v>
       </c>
       <c r="D2" s="12">
         <v>123456</v>
@@ -10489,7 +10719,7 @@
         <v>323</v>
       </c>
       <c r="F4" t="s">
-        <v>663</v>
+        <v>637</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -10497,19 +10727,19 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>654</v>
+        <v>628</v>
       </c>
       <c r="C5" t="s">
-        <v>655</v>
+        <v>629</v>
       </c>
       <c r="D5" s="12">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="F5" t="s">
-        <v>661</v>
+        <v>635</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -10517,19 +10747,19 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>656</v>
+        <v>630</v>
       </c>
       <c r="C6" t="s">
-        <v>657</v>
+        <v>631</v>
       </c>
       <c r="D6" s="12">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="F6" t="s">
-        <v>662</v>
+        <v>636</v>
       </c>
     </row>
   </sheetData>
@@ -10545,7 +10775,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>366</v>
+        <v>340</v>
       </c>
       <c r="B1" t="s">
         <v>315</v>
@@ -10597,75 +10827,75 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>374</v>
+        <v>348</v>
       </c>
       <c r="B1" t="s">
-        <v>376</v>
+        <v>350</v>
       </c>
       <c r="C1" t="s">
-        <v>377</v>
+        <v>351</v>
       </c>
       <c r="D1" t="s">
-        <v>378</v>
+        <v>352</v>
       </c>
       <c r="E1" t="s">
-        <v>379</v>
+        <v>353</v>
       </c>
       <c r="F1" t="s">
-        <v>380</v>
+        <v>354</v>
       </c>
       <c r="G1" t="s">
-        <v>381</v>
+        <v>355</v>
       </c>
       <c r="H1" t="s">
-        <v>382</v>
+        <v>356</v>
       </c>
       <c r="I1" t="s">
-        <v>383</v>
+        <v>357</v>
       </c>
       <c r="J1" t="s">
-        <v>384</v>
+        <v>358</v>
       </c>
       <c r="K1" t="s">
-        <v>385</v>
+        <v>359</v>
       </c>
       <c r="L1" t="s">
-        <v>386</v>
+        <v>360</v>
       </c>
       <c r="M1" t="s">
-        <v>387</v>
+        <v>361</v>
       </c>
       <c r="N1" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="O1" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="P1" t="s">
-        <v>390</v>
+        <v>364</v>
       </c>
       <c r="Q1" t="s">
-        <v>391</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>375</v>
+        <v>349</v>
       </c>
       <c r="B2" t="s">
-        <v>369</v>
+        <v>343</v>
       </c>
       <c r="C2" t="s">
-        <v>370</v>
+        <v>344</v>
       </c>
       <c r="D2" t="s">
-        <v>371</v>
+        <v>345</v>
       </c>
       <c r="E2" t="s">
-        <v>372</v>
+        <v>346</v>
       </c>
       <c r="F2" t="s">
-        <v>373</v>
+        <v>347</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -10697,247 +10927,1129 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F9C4135-AFDC-4222-9830-710D942A3AED}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="14.375" customWidth="1"/>
+    <col min="3" max="4" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>362</v>
+        <v>336</v>
       </c>
       <c r="B1" t="s">
-        <v>363</v>
+        <v>337</v>
       </c>
       <c r="C1" t="s">
-        <v>364</v>
+        <v>338</v>
       </c>
       <c r="D1" t="s">
-        <v>365</v>
+        <v>704</v>
       </c>
       <c r="E1" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+        <v>339</v>
+      </c>
+      <c r="F1" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>336</v>
+        <v>705</v>
       </c>
       <c r="C2" t="s">
-        <v>337</v>
-      </c>
-      <c r="D2">
+        <v>718</v>
+      </c>
+      <c r="D2" t="s">
+        <v>719</v>
+      </c>
+      <c r="E2">
         <v>1</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>338</v>
+        <v>706</v>
       </c>
       <c r="C3" t="s">
-        <v>339</v>
-      </c>
-      <c r="D3">
+        <v>718</v>
+      </c>
+      <c r="D3" t="s">
+        <v>720</v>
+      </c>
+      <c r="E3">
         <v>2</v>
       </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>340</v>
+        <v>707</v>
       </c>
       <c r="C4" t="s">
-        <v>341</v>
-      </c>
-      <c r="D4">
+        <v>718</v>
+      </c>
+      <c r="D4" t="s">
+        <v>722</v>
+      </c>
+      <c r="E4">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>342</v>
+        <v>708</v>
       </c>
       <c r="C5" t="s">
-        <v>343</v>
-      </c>
-      <c r="D5">
+        <v>718</v>
+      </c>
+      <c r="D5" t="s">
+        <v>721</v>
+      </c>
+      <c r="E5">
         <v>4</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>344</v>
+        <v>709</v>
       </c>
       <c r="C6" t="s">
-        <v>345</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
+        <v>723</v>
+      </c>
+      <c r="D6" t="s">
+        <v>719</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>346</v>
+        <v>710</v>
       </c>
       <c r="C7" t="s">
-        <v>347</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
+        <v>723</v>
+      </c>
+      <c r="D7" t="s">
+        <v>720</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>348</v>
+        <v>711</v>
       </c>
       <c r="C8" t="s">
-        <v>349</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
+        <v>723</v>
+      </c>
+      <c r="D8" t="s">
+        <v>722</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>350</v>
+        <v>712</v>
       </c>
       <c r="C9" t="s">
-        <v>351</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
+        <v>723</v>
+      </c>
+      <c r="D9" t="s">
+        <v>721</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>352</v>
+        <v>713</v>
       </c>
       <c r="C10" t="s">
-        <v>353</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
+        <v>724</v>
+      </c>
+      <c r="D10" t="s">
+        <v>719</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>354</v>
+        <v>714</v>
       </c>
       <c r="C11" t="s">
-        <v>355</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
+        <v>724</v>
+      </c>
+      <c r="D11" t="s">
+        <v>720</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>356</v>
+        <v>715</v>
       </c>
       <c r="C12" t="s">
-        <v>357</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
+        <v>724</v>
+      </c>
+      <c r="D12" t="s">
+        <v>722</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>358</v>
+        <v>716</v>
       </c>
       <c r="C13" t="s">
-        <v>359</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
+        <v>724</v>
+      </c>
+      <c r="D13" t="s">
+        <v>721</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>360</v>
+        <v>717</v>
       </c>
       <c r="C14" t="s">
-        <v>361</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
+        <v>751</v>
+      </c>
+      <c r="D14" t="s">
+        <v>721</v>
       </c>
       <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>763</v>
+      </c>
+      <c r="C15" t="s">
+        <v>752</v>
+      </c>
+      <c r="D15" t="s">
+        <v>721</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>764</v>
+      </c>
+      <c r="C16" t="s">
+        <v>753</v>
+      </c>
+      <c r="D16" t="s">
+        <v>721</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>765</v>
+      </c>
+      <c r="C17" t="s">
+        <v>754</v>
+      </c>
+      <c r="D17" t="s">
+        <v>721</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>766</v>
+      </c>
+      <c r="C18" t="s">
+        <v>755</v>
+      </c>
+      <c r="D18" t="s">
+        <v>721</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>767</v>
+      </c>
+      <c r="C19" t="s">
+        <v>756</v>
+      </c>
+      <c r="D19" t="s">
+        <v>721</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>768</v>
+      </c>
+      <c r="C20" t="s">
+        <v>757</v>
+      </c>
+      <c r="D20" t="s">
+        <v>721</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>769</v>
+      </c>
+      <c r="C21" t="s">
+        <v>758</v>
+      </c>
+      <c r="D21" t="s">
+        <v>721</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>770</v>
+      </c>
+      <c r="C22" t="s">
+        <v>759</v>
+      </c>
+      <c r="D22" t="s">
+        <v>721</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>771</v>
+      </c>
+      <c r="C23" t="s">
+        <v>760</v>
+      </c>
+      <c r="D23" t="s">
+        <v>721</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>772</v>
+      </c>
+      <c r="C24" t="s">
+        <v>761</v>
+      </c>
+      <c r="D24" t="s">
+        <v>721</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>773</v>
+      </c>
+      <c r="C25" t="s">
+        <v>762</v>
+      </c>
+      <c r="D25" t="s">
+        <v>721</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>725</v>
+      </c>
+      <c r="C26" t="s">
+        <v>745</v>
+      </c>
+      <c r="D26" t="s">
+        <v>722</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>726</v>
+      </c>
+      <c r="C27" t="s">
+        <v>745</v>
+      </c>
+      <c r="D27" t="s">
+        <v>721</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>727</v>
+      </c>
+      <c r="C28" t="s">
+        <v>746</v>
+      </c>
+      <c r="D28" t="s">
+        <v>719</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>728</v>
+      </c>
+      <c r="C29" t="s">
+        <v>746</v>
+      </c>
+      <c r="D29" t="s">
+        <v>720</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>729</v>
+      </c>
+      <c r="C30" t="s">
+        <v>746</v>
+      </c>
+      <c r="D30" t="s">
+        <v>722</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>730</v>
+      </c>
+      <c r="C31" t="s">
+        <v>746</v>
+      </c>
+      <c r="D31" t="s">
+        <v>721</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>731</v>
+      </c>
+      <c r="C32" t="s">
+        <v>747</v>
+      </c>
+      <c r="D32" t="s">
+        <v>719</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>732</v>
+      </c>
+      <c r="C33" t="s">
+        <v>747</v>
+      </c>
+      <c r="D33" t="s">
+        <v>720</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>733</v>
+      </c>
+      <c r="C34" t="s">
+        <v>747</v>
+      </c>
+      <c r="D34" t="s">
+        <v>722</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>734</v>
+      </c>
+      <c r="C35" t="s">
+        <v>747</v>
+      </c>
+      <c r="D35" t="s">
+        <v>721</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>735</v>
+      </c>
+      <c r="C36" t="s">
+        <v>748</v>
+      </c>
+      <c r="D36" t="s">
+        <v>719</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>736</v>
+      </c>
+      <c r="C37" t="s">
+        <v>748</v>
+      </c>
+      <c r="D37" t="s">
+        <v>720</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>737</v>
+      </c>
+      <c r="C38" t="s">
+        <v>748</v>
+      </c>
+      <c r="D38" t="s">
+        <v>722</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>738</v>
+      </c>
+      <c r="C39" t="s">
+        <v>748</v>
+      </c>
+      <c r="D39" t="s">
+        <v>721</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>739</v>
+      </c>
+      <c r="C40" t="s">
+        <v>749</v>
+      </c>
+      <c r="D40" t="s">
+        <v>719</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>740</v>
+      </c>
+      <c r="C41" t="s">
+        <v>749</v>
+      </c>
+      <c r="D41" t="s">
+        <v>720</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>741</v>
+      </c>
+      <c r="C42" t="s">
+        <v>749</v>
+      </c>
+      <c r="D42" t="s">
+        <v>722</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>742</v>
+      </c>
+      <c r="C43" t="s">
+        <v>749</v>
+      </c>
+      <c r="D43" t="s">
+        <v>721</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>743</v>
+      </c>
+      <c r="C44" t="s">
+        <v>750</v>
+      </c>
+      <c r="D44" t="s">
+        <v>722</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>744</v>
+      </c>
+      <c r="C45" t="s">
+        <v>750</v>
+      </c>
+      <c r="D45" t="s">
+        <v>721</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>774</v>
+      </c>
+      <c r="C46" t="s">
+        <v>775</v>
+      </c>
+      <c r="D46" t="s">
+        <v>720</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>776</v>
+      </c>
+      <c r="C47" t="s">
+        <v>775</v>
+      </c>
+      <c r="D47" t="s">
+        <v>722</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>777</v>
+      </c>
+      <c r="C48" t="s">
+        <v>775</v>
+      </c>
+      <c r="D48" t="s">
+        <v>721</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>780</v>
+      </c>
+      <c r="C49" t="s">
+        <v>778</v>
+      </c>
+      <c r="D49" t="s">
+        <v>722</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>781</v>
+      </c>
+      <c r="C50" t="s">
+        <v>779</v>
+      </c>
+      <c r="D50" t="s">
+        <v>721</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>785</v>
+      </c>
+      <c r="C51" t="s">
+        <v>782</v>
+      </c>
+      <c r="D51" t="s">
+        <v>720</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>786</v>
+      </c>
+      <c r="C52" t="s">
+        <v>783</v>
+      </c>
+      <c r="D52" t="s">
+        <v>722</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>787</v>
+      </c>
+      <c r="C53" t="s">
+        <v>784</v>
+      </c>
+      <c r="D53" t="s">
+        <v>721</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>791</v>
+      </c>
+      <c r="C54" t="s">
+        <v>788</v>
+      </c>
+      <c r="D54" t="s">
+        <v>720</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>792</v>
+      </c>
+      <c r="C55" t="s">
+        <v>789</v>
+      </c>
+      <c r="D55" t="s">
+        <v>722</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>793</v>
+      </c>
+      <c r="C56" t="s">
+        <v>790</v>
+      </c>
+      <c r="D56" t="s">
+        <v>721</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
         <v>0</v>
       </c>
     </row>
@@ -10962,28 +12074,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>477</v>
+        <v>451</v>
       </c>
       <c r="B1" t="s">
-        <v>708</v>
+        <v>682</v>
       </c>
       <c r="C1" t="s">
-        <v>478</v>
+        <v>452</v>
       </c>
       <c r="D1" t="s">
-        <v>479</v>
+        <v>453</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>706</v>
+        <v>680</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>480</v>
+        <v>454</v>
       </c>
       <c r="G1" t="s">
         <v>311</v>
       </c>
       <c r="H1" t="s">
-        <v>481</v>
+        <v>455</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -10994,22 +12106,22 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>553</v>
+        <v>527</v>
       </c>
       <c r="D2" t="s">
-        <v>554</v>
+        <v>528</v>
       </c>
       <c r="E2" s="3">
         <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="G2" t="s">
-        <v>555</v>
+        <v>529</v>
       </c>
       <c r="H2" t="s">
-        <v>596</v>
+        <v>570</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -11020,16 +12132,16 @@
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>665</v>
+        <v>639</v>
       </c>
       <c r="D3" t="s">
-        <v>681</v>
+        <v>655</v>
       </c>
       <c r="E3" s="3">
         <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -11040,16 +12152,16 @@
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>659</v>
+        <v>633</v>
       </c>
       <c r="D4" t="s">
-        <v>724</v>
+        <v>698</v>
       </c>
       <c r="E4" s="3">
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -11060,10 +12172,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>415</v>
+        <v>389</v>
       </c>
       <c r="D5" t="s">
-        <v>722</v>
+        <v>696</v>
       </c>
       <c r="E5" s="3">
         <v>0</v>
@@ -11080,19 +12192,19 @@
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>630</v>
+        <v>604</v>
       </c>
       <c r="D6" t="s">
-        <v>632</v>
+        <v>606</v>
       </c>
       <c r="E6" s="3">
         <v>0</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="G6" t="s">
-        <v>630</v>
+        <v>604</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -11103,19 +12215,19 @@
         <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>694</v>
+        <v>668</v>
       </c>
       <c r="D7" t="s">
-        <v>695</v>
+        <v>669</v>
       </c>
       <c r="E7" s="3">
         <v>0</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="G7" t="s">
-        <v>696</v>
+        <v>670</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -11126,10 +12238,10 @@
         <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>412</v>
+        <v>386</v>
       </c>
       <c r="D8" t="s">
-        <v>413</v>
+        <v>387</v>
       </c>
       <c r="E8" s="3">
         <v>0</v>
@@ -11138,7 +12250,7 @@
         <v>323</v>
       </c>
       <c r="G8" t="s">
-        <v>414</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -11149,19 +12261,19 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>725</v>
+        <v>699</v>
       </c>
       <c r="D9" t="s">
-        <v>726</v>
+        <v>700</v>
       </c>
       <c r="E9" s="3">
         <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="G9" t="s">
-        <v>505</v>
+        <v>479</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -11172,10 +12284,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="s">
-        <v>392</v>
+        <v>366</v>
       </c>
       <c r="D10" t="s">
-        <v>712</v>
+        <v>686</v>
       </c>
       <c r="E10" s="3">
         <v>0</v>
@@ -11184,7 +12296,7 @@
         <v>323</v>
       </c>
       <c r="G10" t="s">
-        <v>393</v>
+        <v>367</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -11195,10 +12307,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="s">
-        <v>709</v>
+        <v>683</v>
       </c>
       <c r="D11" t="s">
-        <v>417</v>
+        <v>391</v>
       </c>
       <c r="E11" s="3">
         <v>0</v>
@@ -11207,7 +12319,7 @@
         <v>323</v>
       </c>
       <c r="G11" t="s">
-        <v>710</v>
+        <v>684</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -11218,10 +12330,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>394</v>
+        <v>368</v>
       </c>
       <c r="D12" t="s">
-        <v>715</v>
+        <v>689</v>
       </c>
       <c r="E12" s="3">
         <v>0</v>
@@ -11230,7 +12342,7 @@
         <v>323</v>
       </c>
       <c r="G12" t="s">
-        <v>395</v>
+        <v>369</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -11241,10 +12353,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="s">
-        <v>716</v>
+        <v>690</v>
       </c>
       <c r="D13" t="s">
-        <v>713</v>
+        <v>687</v>
       </c>
       <c r="E13" s="3">
         <v>0</v>
@@ -11253,7 +12365,7 @@
         <v>323</v>
       </c>
       <c r="G13" t="s">
-        <v>397</v>
+        <v>371</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -11264,10 +12376,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="s">
-        <v>717</v>
+        <v>691</v>
       </c>
       <c r="D14" t="s">
-        <v>718</v>
+        <v>692</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -11276,7 +12388,7 @@
         <v>323</v>
       </c>
       <c r="G14" t="s">
-        <v>402</v>
+        <v>376</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -11287,10 +12399,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>406</v>
+        <v>380</v>
       </c>
       <c r="D15" t="s">
-        <v>407</v>
+        <v>381</v>
       </c>
       <c r="E15" s="3">
         <v>0</v>
@@ -11299,7 +12411,7 @@
         <v>323</v>
       </c>
       <c r="G15" t="s">
-        <v>408</v>
+        <v>382</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -11310,19 +12422,19 @@
         <v>0</v>
       </c>
       <c r="C16" t="s">
-        <v>403</v>
+        <v>377</v>
       </c>
       <c r="D16" t="s">
-        <v>404</v>
+        <v>378</v>
       </c>
       <c r="E16" s="3">
         <v>0</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="G16" t="s">
-        <v>405</v>
+        <v>379</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -11333,10 +12445,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="s">
-        <v>409</v>
+        <v>383</v>
       </c>
       <c r="D17" t="s">
-        <v>410</v>
+        <v>384</v>
       </c>
       <c r="E17" s="3">
         <v>0</v>
@@ -11345,7 +12457,7 @@
         <v>323</v>
       </c>
       <c r="G17" t="s">
-        <v>411</v>
+        <v>385</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
@@ -11356,10 +12468,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="s">
-        <v>400</v>
+        <v>374</v>
       </c>
       <c r="D18" t="s">
-        <v>719</v>
+        <v>693</v>
       </c>
       <c r="E18" s="3">
         <v>0</v>
@@ -11368,7 +12480,7 @@
         <v>323</v>
       </c>
       <c r="G18" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
@@ -11379,10 +12491,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="s">
-        <v>398</v>
+        <v>372</v>
       </c>
       <c r="D19" t="s">
-        <v>720</v>
+        <v>694</v>
       </c>
       <c r="E19" s="3">
         <v>0</v>
@@ -11391,7 +12503,7 @@
         <v>323</v>
       </c>
       <c r="G19" t="s">
-        <v>399</v>
+        <v>373</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
@@ -11402,19 +12514,19 @@
         <v>0</v>
       </c>
       <c r="C20" t="s">
-        <v>504</v>
+        <v>478</v>
       </c>
       <c r="D20" t="s">
-        <v>721</v>
+        <v>695</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="G20" t="s">
-        <v>505</v>
+        <v>479</v>
       </c>
     </row>
   </sheetData>

--- a/Ams.WebApi/wwwroot/data.xlsx
+++ b/Ams.WebApi/wwwroot/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\App Develop\VS2024\Lean.Ams\Ams.WebApi\wwwroot\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\App Develop\VS2024\ZrAdminNetCore\Ams.WebApi\wwwroot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C52716-F2D8-40FB-9FE3-53F3CC0C5938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{663C4B2E-E147-4142-BFB8-1602308FE9D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="849" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="849" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="user" sheetId="2" r:id="rId1"/>
@@ -29,8 +29,6 @@
     <sheet name="notice" sheetId="13" r:id="rId14"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">dict_data!$A$1:$K$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">dict_type!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">menu!$A$1:$A$119</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -38,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1301" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="714">
   <si>
     <t>系统管理</t>
   </si>
@@ -900,9 +898,6 @@
     <t>ParentId</t>
   </si>
   <si>
-    <t>OrderNum</t>
-  </si>
-  <si>
     <t>Path</t>
   </si>
   <si>
@@ -918,10 +913,6 @@
     <t>Visible</t>
   </si>
   <si>
-    <t>Status</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Perms</t>
   </si>
   <si>
@@ -964,12 +955,6 @@
     <t>Sex</t>
   </si>
   <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>DelFlag</t>
-  </si>
-  <si>
     <t>DeptId</t>
   </si>
   <si>
@@ -1001,14 +986,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>RoleSort</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DelFlag</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>DataScope</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1063,6 +1040,84 @@
     <t>ConfigType</t>
   </si>
   <si>
+    <t>CEO</t>
+  </si>
+  <si>
+    <t>董事长</t>
+  </si>
+  <si>
+    <t>SE</t>
+  </si>
+  <si>
+    <t>项目经理</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>人力资源</t>
+  </si>
+  <si>
+    <t>USER</t>
+  </si>
+  <si>
+    <t>普通员工</t>
+  </si>
+  <si>
+    <t>PM</t>
+  </si>
+  <si>
+    <t>人事经理</t>
+  </si>
+  <si>
+    <t>GM</t>
+  </si>
+  <si>
+    <t>总经理</t>
+  </si>
+  <si>
+    <t>COO</t>
+  </si>
+  <si>
+    <t>首席运营官</t>
+  </si>
+  <si>
+    <t>CFO</t>
+  </si>
+  <si>
+    <t>首席财务官</t>
+  </si>
+  <si>
+    <t>CTO</t>
+  </si>
+  <si>
+    <t>首席技术官</t>
+  </si>
+  <si>
+    <t>HRD</t>
+  </si>
+  <si>
+    <t>人力资源总监</t>
+  </si>
+  <si>
+    <t>VP</t>
+  </si>
+  <si>
+    <t>副总裁</t>
+  </si>
+  <si>
+    <t>OD</t>
+  </si>
+  <si>
+    <t>运营总监</t>
+  </si>
+  <si>
+    <t>MD</t>
+  </si>
+  <si>
+    <t>市场总监</t>
+  </si>
+  <si>
     <t>PostId</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1075,10 +1130,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>PostSort</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>UserId</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1174,15 +1225,24 @@
     <t>用户性别</t>
   </si>
   <si>
+    <t>sys_user_sex</t>
+  </si>
+  <si>
     <t>用户性别列表</t>
   </si>
   <si>
     <t>菜单状态</t>
   </si>
   <si>
+    <t>sys_show_hide</t>
+  </si>
+  <si>
     <t>菜单状态列表</t>
   </si>
   <si>
+    <t>系统开关</t>
+  </si>
+  <si>
     <t>sys_normal_disable</t>
   </si>
   <si>
@@ -1192,15 +1252,27 @@
     <t>任务状态</t>
   </si>
   <si>
+    <t>sys_job_status</t>
+  </si>
+  <si>
     <t>任务状态列表</t>
   </si>
   <si>
     <t>任务分组</t>
   </si>
   <si>
+    <t>sys_job_group</t>
+  </si>
+  <si>
     <t>任务分组列表</t>
   </si>
   <si>
+    <t>系统是否</t>
+  </si>
+  <si>
+    <t>sys_yes_no</t>
+  </si>
+  <si>
     <t>系统是否列表</t>
   </si>
   <si>
@@ -1246,9 +1318,15 @@
     <t>sys_article_status</t>
   </si>
   <si>
+    <t>多语言类型</t>
+  </si>
+  <si>
     <t>sys_lang_type</t>
   </si>
   <si>
+    <t>多语言字典类型</t>
+  </si>
+  <si>
     <t>男</t>
   </si>
   <si>
@@ -1532,6 +1610,13 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>sys_job_type</t>
+  </si>
+  <si>
+    <t>sys_job_type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>任务类型列表</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2125,6 +2210,10 @@
   </si>
   <si>
     <t>内容目录类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>article_category_type</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2307,405 +2396,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>IsStatus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsDeleted</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>SortingNum</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsStatus</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsDeleted</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DictCategory</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>语言类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>语言字典类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sys_gender_type</t>
-  </si>
-  <si>
-    <t>sys_gender_type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sys_normal_disable</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sys_menu_show</t>
-  </si>
-  <si>
-    <t>sys_menu_show</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>系统状态</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>系统是否</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sys_normal_whether</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sys_tasks_group</t>
-  </si>
-  <si>
-    <t>sys_tasks_status</t>
-  </si>
-  <si>
-    <t>sys_tasks_type</t>
-  </si>
-  <si>
-    <t>sys_article_status</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sys_article_category</t>
-  </si>
-  <si>
-    <t>sys_article_category</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>字典分类</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sys_dict_type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>系统</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据库</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>SortingNum</t>
-  </si>
-  <si>
-    <t>PostLevel</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M2</t>
-  </si>
-  <si>
-    <t>M3</t>
-  </si>
-  <si>
-    <t>M4</t>
-  </si>
-  <si>
-    <t>M5</t>
-  </si>
-  <si>
-    <t>M6</t>
-  </si>
-  <si>
-    <t>M7</t>
-  </si>
-  <si>
-    <t>M8</t>
-  </si>
-  <si>
-    <t>M9</t>
-  </si>
-  <si>
-    <t>M10</t>
-  </si>
-  <si>
-    <t>M11</t>
-  </si>
-  <si>
-    <t>M12</t>
-  </si>
-  <si>
-    <t>M13</t>
-  </si>
-  <si>
-    <t>主管</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>副部长</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>部长</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>P1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>P2</t>
-  </si>
-  <si>
-    <t>P3</t>
-  </si>
-  <si>
-    <t>P4</t>
-  </si>
-  <si>
-    <t>P5</t>
-  </si>
-  <si>
-    <t>P6</t>
-  </si>
-  <si>
-    <t>P7</t>
-  </si>
-  <si>
-    <t>P8</t>
-  </si>
-  <si>
-    <t>P9</t>
-  </si>
-  <si>
-    <t>P10</t>
-  </si>
-  <si>
-    <t>P11</t>
-  </si>
-  <si>
-    <t>P12</t>
-  </si>
-  <si>
-    <t>P13</t>
-  </si>
-  <si>
-    <t>P14</t>
-  </si>
-  <si>
-    <t>P15</t>
-  </si>
-  <si>
-    <t>P16</t>
-  </si>
-  <si>
-    <t>P17</t>
-  </si>
-  <si>
-    <t>P18</t>
-  </si>
-  <si>
-    <t>P19</t>
-  </si>
-  <si>
-    <t>P20</t>
-  </si>
-  <si>
-    <t>助理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>专员</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高级专员</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>副总监</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>总监</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>资深专家</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>总经理助理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>副总经理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>总经理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>副总裁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高级副总裁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>总裁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高级总裁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>首席执行官</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>副主席</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主席</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高级主席</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>董事长</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>M14</t>
-  </si>
-  <si>
-    <t>M15</t>
-  </si>
-  <si>
-    <t>M16</t>
-  </si>
-  <si>
-    <t>M17</t>
-  </si>
-  <si>
-    <t>M18</t>
-  </si>
-  <si>
-    <t>M19</t>
-  </si>
-  <si>
-    <t>M20</t>
-  </si>
-  <si>
-    <t>M21</t>
-  </si>
-  <si>
-    <t>M22</t>
-  </si>
-  <si>
-    <t>M23</t>
-  </si>
-  <si>
-    <t>M24</t>
-  </si>
-  <si>
-    <t>C1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>员工</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>C3</t>
-  </si>
-  <si>
-    <t>组长</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>副组长</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>C4</t>
-  </si>
-  <si>
-    <t>C5</t>
-  </si>
-  <si>
-    <t>副主任</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主任</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高级主任</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>C6</t>
-  </si>
-  <si>
-    <t>C7</t>
-  </si>
-  <si>
-    <t>C8</t>
-  </si>
-  <si>
-    <t>副理经</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>经理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>高级经理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>C9</t>
-  </si>
-  <si>
-    <t>C10</t>
-  </si>
-  <si>
-    <t>C11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3264,43 +2967,43 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C1" t="s">
+        <v>299</v>
+      </c>
+      <c r="D1" t="s">
         <v>300</v>
       </c>
-      <c r="B1" t="s">
-        <v>309</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>301</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
+        <v>306</v>
+      </c>
+      <c r="G1" t="s">
+        <v>303</v>
+      </c>
+      <c r="H1" t="s">
+        <v>304</v>
+      </c>
+      <c r="I1" t="s">
         <v>302</v>
       </c>
-      <c r="E1" t="s">
-        <v>303</v>
-      </c>
-      <c r="F1" t="s">
-        <v>310</v>
-      </c>
-      <c r="G1" t="s">
-        <v>305</v>
-      </c>
-      <c r="H1" t="s">
-        <v>306</v>
-      </c>
-      <c r="I1" t="s">
-        <v>304</v>
-      </c>
       <c r="J1" t="s">
-        <v>471</v>
+        <v>499</v>
       </c>
       <c r="K1" t="s">
+        <v>710</v>
+      </c>
+      <c r="L1" t="s">
+        <v>711</v>
+      </c>
+      <c r="M1" t="s">
         <v>307</v>
-      </c>
-      <c r="L1" t="s">
-        <v>308</v>
-      </c>
-      <c r="M1" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
@@ -3311,7 +3014,7 @@
         <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -3320,7 +3023,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -3329,7 +3032,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
@@ -3337,10 +3040,10 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>473</v>
+        <v>501</v>
       </c>
       <c r="D3" t="s">
-        <v>474</v>
+        <v>502</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -3349,7 +3052,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -3358,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
@@ -3366,10 +3069,10 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>549</v>
+        <v>579</v>
       </c>
       <c r="D4" t="s">
-        <v>550</v>
+        <v>580</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -3378,7 +3081,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -3387,7 +3090,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="s">
-        <v>550</v>
+        <v>580</v>
       </c>
     </row>
   </sheetData>
@@ -3399,7 +3102,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66E508F4-5906-4688-BE06-7243F5B00B2A}">
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="12.25" customWidth="1"/>
@@ -3411,37 +3114,37 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>457</v>
+        <v>485</v>
       </c>
       <c r="B1" t="s">
-        <v>703</v>
+        <v>712</v>
       </c>
       <c r="C1" t="s">
-        <v>458</v>
+        <v>486</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>459</v>
+        <v>487</v>
       </c>
       <c r="E1" t="s">
-        <v>453</v>
+        <v>481</v>
       </c>
       <c r="F1" t="s">
-        <v>460</v>
+        <v>488</v>
       </c>
       <c r="G1" t="s">
-        <v>461</v>
+        <v>489</v>
       </c>
       <c r="H1" t="s">
-        <v>462</v>
+        <v>490</v>
       </c>
       <c r="I1" t="s">
-        <v>292</v>
+        <v>710</v>
       </c>
       <c r="J1" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="K1" t="s">
-        <v>514</v>
+        <v>544</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -3452,19 +3155,25 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>640</v>
+        <v>420</v>
       </c>
       <c r="D2" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>655</v>
+        <v>386</v>
       </c>
       <c r="H2" t="s">
-        <v>472</v>
+        <v>317</v>
       </c>
       <c r="I2">
         <v>0</v>
+      </c>
+      <c r="J2" t="s">
+        <v>421</v>
+      </c>
+      <c r="K2" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -3472,22 +3181,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>607</v>
+        <v>422</v>
       </c>
       <c r="D3" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>697</v>
+        <v>386</v>
       </c>
       <c r="H3" t="s">
-        <v>472</v>
+        <v>423</v>
       </c>
       <c r="I3">
         <v>0</v>
+      </c>
+      <c r="J3" t="s">
+        <v>424</v>
+      </c>
+      <c r="K3" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -3495,22 +3210,28 @@
         <v>3</v>
       </c>
       <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>425</v>
+      </c>
+      <c r="D4" s="12">
         <v>2</v>
       </c>
-      <c r="C4" t="s">
-        <v>634</v>
-      </c>
-      <c r="D4" s="12">
-        <v>1</v>
-      </c>
       <c r="E4" t="s">
-        <v>697</v>
+        <v>386</v>
       </c>
       <c r="H4" t="s">
-        <v>472</v>
+        <v>423</v>
       </c>
       <c r="I4">
         <v>0</v>
+      </c>
+      <c r="J4" t="s">
+        <v>426</v>
+      </c>
+      <c r="K4" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -3521,19 +3242,28 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>443</v>
+        <v>427</v>
       </c>
       <c r="D5" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>390</v>
+        <v>389</v>
+      </c>
+      <c r="G5" t="s">
+        <v>428</v>
       </c>
       <c r="H5" t="s">
-        <v>472</v>
+        <v>317</v>
       </c>
       <c r="I5">
         <v>0</v>
+      </c>
+      <c r="J5" t="s">
+        <v>429</v>
+      </c>
+      <c r="K5" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -3544,19 +3274,28 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>444</v>
+        <v>430</v>
       </c>
       <c r="D6" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>390</v>
+        <v>389</v>
+      </c>
+      <c r="G6" t="s">
+        <v>431</v>
       </c>
       <c r="H6" t="s">
-        <v>472</v>
+        <v>423</v>
       </c>
       <c r="I6">
         <v>0</v>
+      </c>
+      <c r="J6" t="s">
+        <v>432</v>
+      </c>
+      <c r="K6" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -3567,19 +3306,28 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>607</v>
+        <v>433</v>
       </c>
       <c r="D7" s="12">
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>605</v>
+        <v>392</v>
+      </c>
+      <c r="G7" t="s">
+        <v>428</v>
       </c>
       <c r="H7" t="s">
-        <v>472</v>
+        <v>317</v>
       </c>
       <c r="I7">
         <v>0</v>
+      </c>
+      <c r="J7" t="s">
+        <v>434</v>
+      </c>
+      <c r="K7" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -3590,22 +3338,28 @@
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>619</v>
+        <v>435</v>
       </c>
       <c r="D8" s="12">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>605</v>
+        <v>392</v>
+      </c>
+      <c r="G8" t="s">
+        <v>431</v>
       </c>
       <c r="H8" t="s">
-        <v>472</v>
+        <v>423</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>620</v>
+        <v>436</v>
+      </c>
+      <c r="K8" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
@@ -3613,22 +3367,31 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>608</v>
+        <v>433</v>
       </c>
       <c r="D9" s="12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>605</v>
+        <v>395</v>
+      </c>
+      <c r="G9" t="s">
+        <v>428</v>
       </c>
       <c r="H9" t="s">
-        <v>472</v>
+        <v>317</v>
       </c>
       <c r="I9">
         <v>0</v>
+      </c>
+      <c r="J9" t="s">
+        <v>434</v>
+      </c>
+      <c r="K9" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
@@ -3636,22 +3399,31 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>618</v>
+        <v>437</v>
       </c>
       <c r="D10" s="12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>605</v>
+        <v>395</v>
+      </c>
+      <c r="G10" t="s">
+        <v>431</v>
       </c>
       <c r="H10" t="s">
-        <v>472</v>
+        <v>423</v>
       </c>
       <c r="I10">
         <v>0</v>
+      </c>
+      <c r="J10" t="s">
+        <v>436</v>
+      </c>
+      <c r="K10" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
@@ -3662,19 +3434,25 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>671</v>
-      </c>
-      <c r="D11" s="12">
-        <v>0</v>
+        <v>438</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>439</v>
       </c>
       <c r="E11" t="s">
-        <v>669</v>
+        <v>398</v>
       </c>
       <c r="H11" t="s">
-        <v>472</v>
+        <v>317</v>
       </c>
       <c r="I11">
         <v>0</v>
+      </c>
+      <c r="J11" t="s">
+        <v>440</v>
+      </c>
+      <c r="K11" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
@@ -3685,19 +3463,25 @@
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>672</v>
-      </c>
-      <c r="D12" s="12">
-        <v>1</v>
+        <v>441</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>363</v>
       </c>
       <c r="E12" t="s">
-        <v>669</v>
+        <v>398</v>
       </c>
       <c r="H12" t="s">
-        <v>472</v>
+        <v>423</v>
       </c>
       <c r="I12">
         <v>0</v>
+      </c>
+      <c r="J12" t="s">
+        <v>442</v>
+      </c>
+      <c r="K12" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
@@ -3705,22 +3489,31 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>673</v>
-      </c>
-      <c r="D13" s="12">
-        <v>2</v>
+        <v>443</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>317</v>
       </c>
       <c r="E13" t="s">
-        <v>669</v>
+        <v>401</v>
+      </c>
+      <c r="G13" t="s">
+        <v>428</v>
       </c>
       <c r="H13" t="s">
-        <v>472</v>
+        <v>317</v>
       </c>
       <c r="I13">
         <v>0</v>
+      </c>
+      <c r="J13" t="s">
+        <v>444</v>
+      </c>
+      <c r="K13" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
@@ -3728,28 +3521,31 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>441</v>
-      </c>
-      <c r="D14" s="12">
-        <v>0</v>
+        <v>445</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>423</v>
       </c>
       <c r="E14" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="G14" t="s">
-        <v>400</v>
+        <v>431</v>
       </c>
       <c r="H14" t="s">
-        <v>395</v>
+        <v>423</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>406</v>
+        <v>446</v>
+      </c>
+      <c r="K14" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
@@ -3757,28 +3553,28 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="D15" s="12">
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>387</v>
+        <v>404</v>
       </c>
       <c r="G15" t="s">
-        <v>403</v>
+        <v>448</v>
       </c>
       <c r="H15" t="s">
-        <v>472</v>
+        <v>317</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15" t="s">
-        <v>408</v>
+        <v>447</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
@@ -3786,866 +3582,794 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>701</v>
+        <v>449</v>
       </c>
       <c r="D16" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16" t="s">
-        <v>700</v>
+        <v>404</v>
       </c>
       <c r="G16" t="s">
-        <v>484</v>
+        <v>450</v>
       </c>
       <c r="H16" t="s">
-        <v>472</v>
+        <v>423</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J16" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>702</v>
+        <v>433</v>
       </c>
       <c r="D17" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>700</v>
+        <v>407</v>
       </c>
       <c r="G17" t="s">
-        <v>485</v>
+        <v>428</v>
       </c>
       <c r="H17" t="s">
-        <v>472</v>
+        <v>317</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J17" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>392</v>
+        <v>451</v>
       </c>
       <c r="D18" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>685</v>
+        <v>407</v>
+      </c>
+      <c r="G18" t="s">
+        <v>431</v>
       </c>
       <c r="H18" t="s">
-        <v>323</v>
+        <v>423</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18" t="s">
-        <v>393</v>
-      </c>
-      <c r="K18" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C19" t="s">
-        <v>394</v>
+        <v>453</v>
       </c>
       <c r="D19" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>685</v>
+        <v>410</v>
+      </c>
+      <c r="G19" t="s">
+        <v>454</v>
       </c>
       <c r="H19" t="s">
-        <v>395</v>
+        <v>423</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
       <c r="J19" t="s">
-        <v>396</v>
-      </c>
-      <c r="K19" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>397</v>
+        <v>259</v>
       </c>
       <c r="D20" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>685</v>
+        <v>410</v>
+      </c>
+      <c r="G20" t="s">
+        <v>454</v>
       </c>
       <c r="H20" t="s">
-        <v>395</v>
+        <v>423</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
       <c r="J20" t="s">
-        <v>398</v>
-      </c>
-      <c r="K20" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>445</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>446</v>
+        <v>263</v>
+      </c>
+      <c r="D21" s="12">
+        <v>2</v>
       </c>
       <c r="E21" t="s">
-        <v>391</v>
+        <v>410</v>
+      </c>
+      <c r="G21" t="s">
+        <v>454</v>
       </c>
       <c r="H21" t="s">
-        <v>472</v>
+        <v>423</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J21" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>447</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>448</v>
+        <v>261</v>
+      </c>
+      <c r="D22" s="12">
+        <v>3</v>
       </c>
       <c r="E22" t="s">
-        <v>391</v>
+        <v>410</v>
+      </c>
+      <c r="G22" t="s">
+        <v>431</v>
       </c>
       <c r="H22" t="s">
-        <v>472</v>
+        <v>423</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J22" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C23" t="s">
-        <v>449</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>450</v>
+        <v>459</v>
+      </c>
+      <c r="D23" s="12">
+        <v>4</v>
       </c>
       <c r="E23" t="s">
-        <v>391</v>
+        <v>410</v>
+      </c>
+      <c r="G23" t="s">
+        <v>428</v>
       </c>
       <c r="H23" t="s">
-        <v>472</v>
+        <v>423</v>
       </c>
       <c r="I23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J23" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C24" t="s">
-        <v>399</v>
+        <v>265</v>
       </c>
       <c r="D24" s="12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E24" t="s">
-        <v>688</v>
+        <v>410</v>
       </c>
       <c r="G24" t="s">
-        <v>400</v>
+        <v>448</v>
       </c>
       <c r="H24" t="s">
-        <v>323</v>
+        <v>423</v>
       </c>
       <c r="I24">
         <v>0</v>
       </c>
       <c r="J24" t="s">
-        <v>401</v>
-      </c>
-      <c r="K24" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C25" t="s">
-        <v>402</v>
+        <v>462</v>
       </c>
       <c r="D25" s="12">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E25" t="s">
-        <v>688</v>
+        <v>410</v>
       </c>
       <c r="G25" t="s">
-        <v>403</v>
+        <v>448</v>
       </c>
       <c r="H25" t="s">
-        <v>395</v>
+        <v>423</v>
       </c>
       <c r="I25">
         <v>0</v>
       </c>
       <c r="J25" t="s">
-        <v>404</v>
-      </c>
-      <c r="K25" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C26" t="s">
-        <v>405</v>
+        <v>464</v>
       </c>
       <c r="D26" s="12">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E26" t="s">
-        <v>370</v>
+        <v>410</v>
       </c>
       <c r="G26" t="s">
-        <v>400</v>
+        <v>431</v>
       </c>
       <c r="H26" t="s">
-        <v>323</v>
+        <v>423</v>
       </c>
       <c r="I26">
         <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>406</v>
-      </c>
-      <c r="K26" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>407</v>
+        <v>243</v>
       </c>
       <c r="D27" s="12">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E27" t="s">
-        <v>687</v>
+        <v>410</v>
       </c>
       <c r="G27" t="s">
-        <v>403</v>
+        <v>448</v>
       </c>
       <c r="H27" t="s">
-        <v>395</v>
+        <v>423</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27" t="s">
-        <v>408</v>
-      </c>
-      <c r="K27" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C28" t="s">
-        <v>415</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>323</v>
+        <v>467</v>
+      </c>
+      <c r="D28" s="12">
+        <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>692</v>
+        <v>410</v>
       </c>
       <c r="G28" t="s">
-        <v>400</v>
+        <v>431</v>
       </c>
       <c r="H28" t="s">
-        <v>323</v>
+        <v>423</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28" t="s">
-        <v>416</v>
-      </c>
-      <c r="K28" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>417</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>395</v>
+        <v>469</v>
+      </c>
+      <c r="D29" s="12">
+        <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>692</v>
+        <v>413</v>
       </c>
       <c r="G29" t="s">
-        <v>403</v>
+        <v>428</v>
       </c>
       <c r="H29" t="s">
-        <v>395</v>
+        <v>423</v>
       </c>
       <c r="I29">
         <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>418</v>
-      </c>
-      <c r="K29" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" t="s">
-        <v>405</v>
+        <v>470</v>
       </c>
       <c r="D30" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>381</v>
+        <v>413</v>
       </c>
       <c r="G30" t="s">
-        <v>400</v>
+        <v>431</v>
       </c>
       <c r="H30" t="s">
-        <v>323</v>
+        <v>500</v>
       </c>
       <c r="I30">
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>423</v>
+        <v>471</v>
       </c>
       <c r="D31" s="12">
         <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>381</v>
-      </c>
-      <c r="G31" t="s">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="H31" t="s">
-        <v>395</v>
+        <v>500</v>
       </c>
       <c r="I31">
         <v>0</v>
       </c>
-      <c r="J31" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" t="s">
-        <v>419</v>
+        <v>472</v>
       </c>
       <c r="D32" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" t="s">
-        <v>378</v>
-      </c>
-      <c r="G32" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="H32" t="s">
-        <v>323</v>
+        <v>500</v>
       </c>
       <c r="I32">
         <v>0</v>
       </c>
-      <c r="J32" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>421</v>
-      </c>
-      <c r="D33" s="12">
-        <v>2</v>
+        <v>473</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>474</v>
       </c>
       <c r="E33" t="s">
-        <v>378</v>
-      </c>
-      <c r="G33" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="H33" t="s">
-        <v>395</v>
+        <v>500</v>
       </c>
       <c r="I33">
         <v>0</v>
       </c>
-      <c r="J33" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>425</v>
-      </c>
-      <c r="D34" s="12">
-        <v>0</v>
+        <v>475</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>476</v>
       </c>
       <c r="E34" t="s">
-        <v>384</v>
-      </c>
-      <c r="G34" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="H34" t="s">
-        <v>395</v>
+        <v>500</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
-      <c r="J34" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C35" t="s">
-        <v>259</v>
-      </c>
-      <c r="D35" s="12">
-        <v>1</v>
+        <v>477</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>478</v>
       </c>
       <c r="E35" t="s">
-        <v>384</v>
-      </c>
-      <c r="G35" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="H35" t="s">
-        <v>395</v>
+        <v>500</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
-      <c r="J35" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>263</v>
+        <v>510</v>
       </c>
       <c r="D36" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>384</v>
+        <v>507</v>
       </c>
       <c r="G36" t="s">
-        <v>426</v>
+        <v>513</v>
       </c>
       <c r="H36" t="s">
-        <v>395</v>
+        <v>500</v>
       </c>
       <c r="I36">
         <v>0</v>
       </c>
-      <c r="J36" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>261</v>
+        <v>511</v>
       </c>
       <c r="D37" s="12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37" t="s">
-        <v>384</v>
+        <v>507</v>
       </c>
       <c r="G37" t="s">
-        <v>403</v>
+        <v>514</v>
       </c>
       <c r="H37" t="s">
-        <v>395</v>
+        <v>500</v>
       </c>
       <c r="I37">
         <v>0</v>
       </c>
-      <c r="J37" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C38" t="s">
-        <v>431</v>
+        <v>512</v>
       </c>
       <c r="D38" s="12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E38" t="s">
-        <v>384</v>
+        <v>507</v>
       </c>
       <c r="G38" t="s">
-        <v>400</v>
+        <v>515</v>
       </c>
       <c r="H38" t="s">
-        <v>395</v>
+        <v>500</v>
       </c>
       <c r="I38">
         <v>0</v>
       </c>
-      <c r="J38" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>265</v>
+        <v>637</v>
       </c>
       <c r="D39" s="12">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>384</v>
-      </c>
-      <c r="G39" t="s">
-        <v>420</v>
+        <v>635</v>
       </c>
       <c r="H39" t="s">
-        <v>395</v>
+        <v>500</v>
       </c>
       <c r="I39">
         <v>0</v>
       </c>
-      <c r="J39" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C40" t="s">
-        <v>434</v>
+        <v>649</v>
       </c>
       <c r="D40" s="12">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E40" t="s">
-        <v>384</v>
-      </c>
-      <c r="G40" t="s">
-        <v>420</v>
+        <v>635</v>
       </c>
       <c r="H40" t="s">
-        <v>395</v>
+        <v>500</v>
       </c>
       <c r="I40">
         <v>0</v>
       </c>
       <c r="J40" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C41" t="s">
-        <v>436</v>
+        <v>638</v>
       </c>
       <c r="D41" s="12">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E41" t="s">
-        <v>384</v>
-      </c>
-      <c r="G41" t="s">
-        <v>403</v>
+        <v>635</v>
       </c>
       <c r="H41" t="s">
-        <v>395</v>
+        <v>500</v>
       </c>
       <c r="I41">
         <v>0</v>
       </c>
-      <c r="J41" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C42" t="s">
-        <v>243</v>
+        <v>648</v>
       </c>
       <c r="D42" s="12">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E42" t="s">
-        <v>384</v>
-      </c>
-      <c r="G42" t="s">
-        <v>420</v>
+        <v>635</v>
       </c>
       <c r="H42" t="s">
-        <v>395</v>
+        <v>500</v>
       </c>
       <c r="I42">
         <v>0</v>
       </c>
-      <c r="J42" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>439</v>
+        <v>637</v>
       </c>
       <c r="D43" s="12">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E43" t="s">
-        <v>384</v>
-      </c>
-      <c r="G43" t="s">
-        <v>403</v>
+        <v>664</v>
       </c>
       <c r="H43" t="s">
-        <v>395</v>
+        <v>500</v>
       </c>
       <c r="I43">
         <v>0</v>
       </c>
-      <c r="J43" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>410</v>
-      </c>
-      <c r="D44" s="12" t="s">
-        <v>411</v>
+        <v>665</v>
+      </c>
+      <c r="D44" s="12">
+        <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>693</v>
+        <v>664</v>
       </c>
       <c r="H44" t="s">
-        <v>323</v>
+        <v>500</v>
       </c>
       <c r="I44">
         <v>0</v>
       </c>
-      <c r="J44" t="s">
-        <v>412</v>
-      </c>
-      <c r="K44" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>413</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>344</v>
+        <v>671</v>
+      </c>
+      <c r="D45" s="12">
+        <v>1</v>
       </c>
       <c r="E45" t="s">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="H45" t="s">
-        <v>395</v>
+        <v>500</v>
       </c>
       <c r="I45">
         <v>0</v>
       </c>
-      <c r="J45" t="s">
-        <v>414</v>
-      </c>
-      <c r="K45" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -4653,31 +4377,22 @@
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>405</v>
+        <v>702</v>
       </c>
       <c r="D46" s="12">
         <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>694</v>
-      </c>
-      <c r="G46" t="s">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="H46" t="s">
-        <v>323</v>
+        <v>500</v>
       </c>
       <c r="I46">
         <v>0</v>
       </c>
-      <c r="J46" t="s">
-        <v>406</v>
-      </c>
-      <c r="K46" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -4685,114 +4400,45 @@
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>409</v>
+        <v>703</v>
       </c>
       <c r="D47" s="12">
         <v>1</v>
       </c>
       <c r="E47" t="s">
-        <v>694</v>
-      </c>
-      <c r="G47" t="s">
-        <v>403</v>
+        <v>700</v>
       </c>
       <c r="H47" t="s">
-        <v>395</v>
+        <v>500</v>
       </c>
       <c r="I47">
         <v>0</v>
       </c>
-      <c r="J47" t="s">
-        <v>408</v>
-      </c>
-      <c r="K47" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C48" t="s">
-        <v>480</v>
+        <v>704</v>
       </c>
       <c r="D48" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48" t="s">
-        <v>695</v>
-      </c>
-      <c r="G48" t="s">
-        <v>483</v>
+        <v>700</v>
       </c>
       <c r="H48" t="s">
-        <v>472</v>
+        <v>500</v>
       </c>
       <c r="I48">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49">
-        <v>2</v>
-      </c>
-      <c r="C49" t="s">
-        <v>481</v>
-      </c>
-      <c r="D49" s="12">
-        <v>2</v>
-      </c>
-      <c r="E49" t="s">
-        <v>695</v>
-      </c>
-      <c r="G49" t="s">
-        <v>484</v>
-      </c>
-      <c r="H49" t="s">
-        <v>472</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50">
-        <v>3</v>
-      </c>
-      <c r="C50" t="s">
-        <v>482</v>
-      </c>
-      <c r="D50" s="12">
-        <v>3</v>
-      </c>
-      <c r="E50" t="s">
-        <v>695</v>
-      </c>
-      <c r="G50" t="s">
-        <v>485</v>
-      </c>
-      <c r="H50" t="s">
-        <v>472</v>
-      </c>
-      <c r="I50">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K1" xr:uid="{66E508F4-5906-4688-BE06-7243F5B00B2A}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K50">
-      <sortCondition ref="E1"/>
-    </sortState>
-  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4805,25 +4451,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>467</v>
+        <v>495</v>
       </c>
       <c r="B1" t="s">
-        <v>468</v>
+        <v>496</v>
       </c>
       <c r="C1" t="s">
-        <v>469</v>
+        <v>497</v>
       </c>
       <c r="D1" t="s">
-        <v>470</v>
+        <v>498</v>
       </c>
       <c r="E1" t="s">
-        <v>679</v>
+        <v>712</v>
       </c>
       <c r="F1" t="s">
-        <v>680</v>
+        <v>710</v>
       </c>
       <c r="G1" t="s">
-        <v>681</v>
+        <v>711</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -4834,7 +4480,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>477</v>
+        <v>505</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -4854,7 +4500,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>463</v>
+        <v>491</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -4874,7 +4520,7 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>464</v>
+        <v>492</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -4894,7 +4540,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>465</v>
+        <v>493</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -4914,7 +4560,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>466</v>
+        <v>494</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -4944,19 +4590,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>476</v>
+        <v>504</v>
       </c>
       <c r="B1" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="C1" t="s">
         <v>285</v>
       </c>
       <c r="D1" t="s">
-        <v>612</v>
+        <v>642</v>
       </c>
       <c r="E1" t="s">
-        <v>613</v>
+        <v>643</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -4964,7 +4610,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>609</v>
+        <v>639</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -4973,7 +4619,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>614</v>
+        <v>644</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -4981,7 +4627,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>610</v>
+        <v>640</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -4990,7 +4636,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>615</v>
+        <v>645</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -4998,7 +4644,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>611</v>
+        <v>641</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5007,7 +4653,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>616</v>
+        <v>646</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -5015,7 +4661,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>425</v>
+        <v>453</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -5024,7 +4670,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>617</v>
+        <v>647</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -5032,7 +4678,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>632</v>
+        <v>662</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -5058,15 +4704,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>621</v>
+        <v>651</v>
       </c>
       <c r="B1" t="s">
-        <v>622</v>
+        <v>652</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>623</v>
+        <v>653</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -5074,7 +4720,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>624</v>
+        <v>654</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5082,7 +4728,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>625</v>
+        <v>655</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -5090,7 +4736,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>626</v>
+        <v>656</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -5098,7 +4744,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>627</v>
+        <v>657</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -5121,19 +4767,19 @@
   <sheetData>
     <row r="1" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>594</v>
+        <v>624</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>595</v>
+        <v>625</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>596</v>
+        <v>626</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>597</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>292</v>
+        <v>627</v>
+      </c>
+      <c r="E1" t="s">
+        <v>710</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="54.6" customHeight="1" x14ac:dyDescent="0.2">
@@ -5141,13 +4787,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>593</v>
+        <v>623</v>
       </c>
       <c r="C2" s="9">
         <v>2</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>654</v>
+        <v>685</v>
       </c>
       <c r="E2" s="9">
         <v>0</v>
@@ -5185,37 +4831,37 @@
         <v>285</v>
       </c>
       <c r="D1" t="s">
+        <v>713</v>
+      </c>
+      <c r="E1" t="s">
         <v>286</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>287</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>288</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>289</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>290</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
+        <v>710</v>
+      </c>
+      <c r="K1" t="s">
         <v>291</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>292</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
+        <v>294</v>
+      </c>
+      <c r="N1" t="s">
         <v>293</v>
-      </c>
-      <c r="L1" t="s">
-        <v>294</v>
-      </c>
-      <c r="M1" t="s">
-        <v>296</v>
-      </c>
-      <c r="N1" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
@@ -5401,7 +5047,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>505</v>
+        <v>535</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -5413,7 +5059,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>506</v>
+        <v>536</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5422,10 +5068,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>567</v>
+        <v>597</v>
       </c>
       <c r="N7" t="s">
-        <v>591</v>
+        <v>621</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -5433,7 +5079,7 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>556</v>
+        <v>586</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -5442,7 +5088,7 @@
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>530</v>
+        <v>560</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -5457,10 +5103,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="s">
-        <v>530</v>
+        <v>560</v>
       </c>
       <c r="N8" t="s">
-        <v>584</v>
+        <v>614</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -5468,7 +5114,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>500</v>
+        <v>530</v>
       </c>
       <c r="C9">
         <v>7</v>
@@ -5477,16 +5123,16 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>504</v>
+        <v>534</v>
       </c>
       <c r="F9" t="s">
-        <v>501</v>
+        <v>531</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>493</v>
+        <v>523</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -5495,10 +5141,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="s">
-        <v>502</v>
+        <v>532</v>
       </c>
       <c r="N9" t="s">
-        <v>503</v>
+        <v>533</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -5506,7 +5152,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>571</v>
+        <v>601</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -5515,16 +5161,16 @@
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>676</v>
+        <v>707</v>
       </c>
       <c r="F10" t="s">
-        <v>572</v>
+        <v>602</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>506</v>
+        <v>536</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -5533,13 +5179,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>574</v>
+        <v>604</v>
       </c>
       <c r="L10" t="s">
-        <v>573</v>
+        <v>603</v>
       </c>
       <c r="N10" t="s">
-        <v>585</v>
+        <v>615</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -5638,7 +5284,7 @@
         <v>3</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>677</v>
+        <v>708</v>
       </c>
       <c r="F13" t="s">
         <v>32</v>
@@ -5957,7 +5603,7 @@
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>475</v>
+        <v>503</v>
       </c>
       <c r="F21" t="s">
         <v>74</v>
@@ -6238,7 +5884,7 @@
         <v>4</v>
       </c>
       <c r="E28" t="s">
-        <v>568</v>
+        <v>598</v>
       </c>
       <c r="F28" t="s">
         <v>109</v>
@@ -6256,10 +5902,10 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>538</v>
+        <v>568</v>
       </c>
       <c r="L28" t="s">
-        <v>569</v>
+        <v>599</v>
       </c>
       <c r="N28" t="s">
         <v>110</v>
@@ -6270,7 +5916,7 @@
         <v>118</v>
       </c>
       <c r="B29" t="s">
-        <v>599</v>
+        <v>629</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -6305,7 +5951,7 @@
         <v>119</v>
       </c>
       <c r="B30" t="s">
-        <v>600</v>
+        <v>630</v>
       </c>
       <c r="C30">
         <v>118</v>
@@ -6317,7 +5963,7 @@
         <v>114</v>
       </c>
       <c r="F30" t="s">
-        <v>575</v>
+        <v>605</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -6346,7 +5992,7 @@
         <v>500</v>
       </c>
       <c r="B31" t="s">
-        <v>638</v>
+        <v>669</v>
       </c>
       <c r="C31">
         <v>108</v>
@@ -6373,7 +6019,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>675</v>
+        <v>706</v>
       </c>
       <c r="L31" t="s">
         <v>120</v>
@@ -6414,7 +6060,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>674</v>
+        <v>705</v>
       </c>
       <c r="L32" t="s">
         <v>123</v>
@@ -6428,7 +6074,7 @@
         <v>502</v>
       </c>
       <c r="B33" t="s">
-        <v>490</v>
+        <v>520</v>
       </c>
       <c r="C33">
         <v>108</v>
@@ -6437,16 +6083,16 @@
         <v>3</v>
       </c>
       <c r="E33" t="s">
-        <v>491</v>
+        <v>521</v>
       </c>
       <c r="F33" t="s">
-        <v>492</v>
+        <v>522</v>
       </c>
       <c r="G33">
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>493</v>
+        <v>523</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -6455,13 +6101,13 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>497</v>
+        <v>527</v>
       </c>
       <c r="L33" t="s">
-        <v>494</v>
+        <v>524</v>
       </c>
       <c r="N33" t="s">
-        <v>589</v>
+        <v>619</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
@@ -7893,7 +7539,7 @@
         <v>1047</v>
       </c>
       <c r="B80" t="s">
-        <v>665</v>
+        <v>696</v>
       </c>
       <c r="C80">
         <v>118</v>
@@ -7902,16 +7548,16 @@
         <v>2</v>
       </c>
       <c r="E80" t="s">
-        <v>565</v>
+        <v>595</v>
       </c>
       <c r="F80" t="s">
-        <v>598</v>
+        <v>628</v>
       </c>
       <c r="G80">
         <v>0</v>
       </c>
       <c r="H80" t="s">
-        <v>493</v>
+        <v>523</v>
       </c>
       <c r="I80">
         <v>1</v>
@@ -7920,7 +7566,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>566</v>
+        <v>596</v>
       </c>
       <c r="L80" t="s">
         <v>64</v>
@@ -7931,7 +7577,7 @@
         <v>1049</v>
       </c>
       <c r="B81" t="s">
-        <v>601</v>
+        <v>631</v>
       </c>
       <c r="C81">
         <v>119</v>
@@ -7963,19 +7609,19 @@
         <v>1048</v>
       </c>
       <c r="B82" t="s">
-        <v>664</v>
+        <v>695</v>
       </c>
       <c r="C82">
         <v>119</v>
       </c>
       <c r="E82" t="s">
-        <v>488</v>
+        <v>518</v>
       </c>
       <c r="G82">
         <v>0</v>
       </c>
       <c r="H82" t="s">
-        <v>487</v>
+        <v>517</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -7984,7 +7630,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>666</v>
+        <v>697</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.2">
@@ -7992,7 +7638,7 @@
         <v>1050</v>
       </c>
       <c r="B83" t="s">
-        <v>602</v>
+        <v>632</v>
       </c>
       <c r="C83">
         <v>119</v>
@@ -8647,7 +8293,7 @@
         <v>999</v>
       </c>
       <c r="E103" t="s">
-        <v>653</v>
+        <v>684</v>
       </c>
       <c r="F103" t="s">
         <v>268</v>
@@ -8807,7 +8453,7 @@
         <v>1090</v>
       </c>
       <c r="B108" t="s">
-        <v>489</v>
+        <v>519</v>
       </c>
       <c r="C108">
         <v>1078</v>
@@ -8816,13 +8462,13 @@
         <v>5</v>
       </c>
       <c r="E108" t="s">
-        <v>488</v>
+        <v>518</v>
       </c>
       <c r="G108">
         <v>0</v>
       </c>
       <c r="H108" t="s">
-        <v>487</v>
+        <v>517</v>
       </c>
       <c r="I108">
         <v>0</v>
@@ -8831,7 +8477,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>486</v>
+        <v>516</v>
       </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.2">
@@ -8871,7 +8517,7 @@
         <v>1084</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>603</v>
+        <v>633</v>
       </c>
       <c r="C110" s="4">
         <v>118</v>
@@ -8880,10 +8526,10 @@
         <v>999</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>652</v>
+        <v>683</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>576</v>
+        <v>606</v>
       </c>
       <c r="G110" s="4">
         <v>0</v>
@@ -8905,7 +8551,7 @@
       </c>
       <c r="M110" s="4"/>
       <c r="N110" t="s">
-        <v>586</v>
+        <v>616</v>
       </c>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.2">
@@ -9088,7 +8734,7 @@
         <v>1092</v>
       </c>
       <c r="B116" t="s">
-        <v>507</v>
+        <v>537</v>
       </c>
       <c r="C116">
         <v>111</v>
@@ -9100,7 +8746,7 @@
         <v>0</v>
       </c>
       <c r="H116" t="s">
-        <v>487</v>
+        <v>517</v>
       </c>
       <c r="I116">
         <v>0</v>
@@ -9109,10 +8755,10 @@
         <v>0</v>
       </c>
       <c r="K116" t="s">
-        <v>508</v>
+        <v>538</v>
       </c>
       <c r="M116" t="s">
-        <v>513</v>
+        <v>543</v>
       </c>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.2">
@@ -9120,7 +8766,7 @@
         <v>1091</v>
       </c>
       <c r="B117" t="s">
-        <v>510</v>
+        <v>540</v>
       </c>
       <c r="C117">
         <v>111</v>
@@ -9132,7 +8778,7 @@
         <v>0</v>
       </c>
       <c r="H117" t="s">
-        <v>487</v>
+        <v>517</v>
       </c>
       <c r="I117">
         <v>0</v>
@@ -9141,10 +8787,10 @@
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>509</v>
+        <v>539</v>
       </c>
       <c r="M117" t="s">
-        <v>513</v>
+        <v>543</v>
       </c>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.2">
@@ -9152,7 +8798,7 @@
         <v>1102</v>
       </c>
       <c r="B118" t="s">
-        <v>495</v>
+        <v>525</v>
       </c>
       <c r="C118">
         <v>502</v>
@@ -9164,7 +8810,7 @@
         <v>0</v>
       </c>
       <c r="H118" t="s">
-        <v>487</v>
+        <v>517</v>
       </c>
       <c r="I118">
         <v>0</v>
@@ -9173,10 +8819,10 @@
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>498</v>
+        <v>528</v>
       </c>
       <c r="M118" t="s">
-        <v>512</v>
+        <v>542</v>
       </c>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.2">
@@ -9184,7 +8830,7 @@
         <v>1103</v>
       </c>
       <c r="B119" t="s">
-        <v>496</v>
+        <v>526</v>
       </c>
       <c r="C119">
         <v>502</v>
@@ -9196,7 +8842,7 @@
         <v>0</v>
       </c>
       <c r="H119" t="s">
-        <v>487</v>
+        <v>517</v>
       </c>
       <c r="I119">
         <v>0</v>
@@ -9205,10 +8851,10 @@
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>499</v>
+        <v>529</v>
       </c>
       <c r="M119" t="s">
-        <v>511</v>
+        <v>541</v>
       </c>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.2">
@@ -9216,7 +8862,7 @@
         <v>1104</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>527</v>
+        <v>557</v>
       </c>
       <c r="C120" s="5">
         <v>9</v>
@@ -9225,16 +8871,16 @@
         <v>1</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>530</v>
+        <v>560</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>531</v>
+        <v>561</v>
       </c>
       <c r="G120" s="5">
         <v>0</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>493</v>
+        <v>523</v>
       </c>
       <c r="I120" s="5">
         <v>0</v>
@@ -9243,14 +8889,14 @@
         <v>0</v>
       </c>
       <c r="K120" s="5" t="s">
-        <v>537</v>
+        <v>567</v>
       </c>
       <c r="L120" s="5" t="s">
-        <v>539</v>
+        <v>569</v>
       </c>
       <c r="M120" s="5"/>
       <c r="N120" t="s">
-        <v>587</v>
+        <v>617</v>
       </c>
     </row>
     <row r="121" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -9258,7 +8904,7 @@
         <v>1105</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>532</v>
+        <v>562</v>
       </c>
       <c r="C121" s="5">
         <v>1104</v>
@@ -9272,7 +8918,7 @@
         <v>0</v>
       </c>
       <c r="H121" s="5" t="s">
-        <v>487</v>
+        <v>517</v>
       </c>
       <c r="I121" s="5">
         <v>0</v>
@@ -9281,7 +8927,7 @@
         <v>0</v>
       </c>
       <c r="K121" s="5" t="s">
-        <v>534</v>
+        <v>564</v>
       </c>
       <c r="L121" s="5"/>
       <c r="M121" s="5"/>
@@ -9291,7 +8937,7 @@
         <v>1106</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>533</v>
+        <v>563</v>
       </c>
       <c r="C122" s="5">
         <v>1104</v>
@@ -9305,7 +8951,7 @@
         <v>0</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>487</v>
+        <v>517</v>
       </c>
       <c r="I122" s="5">
         <v>0</v>
@@ -9314,7 +8960,7 @@
         <v>0</v>
       </c>
       <c r="K122" s="5" t="s">
-        <v>535</v>
+        <v>565</v>
       </c>
       <c r="L122" s="5"/>
       <c r="M122" s="5"/>
@@ -9324,7 +8970,7 @@
         <v>1107</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>495</v>
+        <v>525</v>
       </c>
       <c r="C123" s="5">
         <v>1104</v>
@@ -9338,7 +8984,7 @@
         <v>0</v>
       </c>
       <c r="H123" s="5" t="s">
-        <v>487</v>
+        <v>517</v>
       </c>
       <c r="I123" s="5">
         <v>0</v>
@@ -9347,7 +8993,7 @@
         <v>0</v>
       </c>
       <c r="K123" s="5" t="s">
-        <v>536</v>
+        <v>566</v>
       </c>
       <c r="L123" s="5"/>
       <c r="M123" s="5"/>
@@ -9357,7 +9003,7 @@
         <v>1108</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>548</v>
+        <v>578</v>
       </c>
       <c r="C124" s="6">
         <v>108</v>
@@ -9366,16 +9012,16 @@
         <v>1</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>543</v>
+        <v>573</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>544</v>
+        <v>574</v>
       </c>
       <c r="G124" s="6">
         <v>0</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>493</v>
+        <v>523</v>
       </c>
       <c r="I124" s="6">
         <v>0</v>
@@ -9384,14 +9030,14 @@
         <v>0</v>
       </c>
       <c r="K124" s="6" t="s">
-        <v>545</v>
+        <v>575</v>
       </c>
       <c r="L124" s="6" t="s">
-        <v>540</v>
+        <v>570</v>
       </c>
       <c r="M124" s="6"/>
       <c r="N124" t="s">
-        <v>590</v>
+        <v>620</v>
       </c>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.2">
@@ -9399,7 +9045,7 @@
         <v>1109</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>541</v>
+        <v>571</v>
       </c>
       <c r="C125" s="6">
         <v>1108</v>
@@ -9413,7 +9059,7 @@
         <v>0</v>
       </c>
       <c r="H125" s="6" t="s">
-        <v>487</v>
+        <v>517</v>
       </c>
       <c r="I125" s="6">
         <v>0</v>
@@ -9422,7 +9068,7 @@
         <v>0</v>
       </c>
       <c r="K125" s="6" t="s">
-        <v>546</v>
+        <v>576</v>
       </c>
       <c r="L125" s="6"/>
       <c r="M125" s="6"/>
@@ -9432,7 +9078,7 @@
         <v>1110</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>542</v>
+        <v>572</v>
       </c>
       <c r="C126" s="6">
         <v>1108</v>
@@ -9446,7 +9092,7 @@
         <v>0</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>487</v>
+        <v>517</v>
       </c>
       <c r="I126" s="6">
         <v>0</v>
@@ -9455,7 +9101,7 @@
         <v>0</v>
       </c>
       <c r="K126" s="6" t="s">
-        <v>547</v>
+        <v>577</v>
       </c>
       <c r="L126" s="6"/>
       <c r="M126" s="6"/>
@@ -9465,7 +9111,7 @@
         <v>1111</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>557</v>
+        <v>587</v>
       </c>
       <c r="C127" s="4">
         <v>9</v>
@@ -9474,16 +9120,16 @@
         <v>1</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>558</v>
+        <v>588</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>559</v>
+        <v>589</v>
       </c>
       <c r="G127" s="4">
         <v>0</v>
       </c>
       <c r="H127" s="4" t="s">
-        <v>493</v>
+        <v>523</v>
       </c>
       <c r="I127" s="4">
         <v>0</v>
@@ -9492,16 +9138,16 @@
         <v>0</v>
       </c>
       <c r="K127" s="4" t="s">
-        <v>560</v>
+        <v>590</v>
       </c>
       <c r="L127" s="4" t="s">
-        <v>558</v>
+        <v>588</v>
       </c>
       <c r="M127" s="4" t="s">
-        <v>557</v>
+        <v>587</v>
       </c>
       <c r="N127" s="4" t="s">
-        <v>592</v>
+        <v>622</v>
       </c>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.2">
@@ -9509,7 +9155,7 @@
         <v>1112</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>563</v>
+        <v>593</v>
       </c>
       <c r="C128" s="4">
         <v>1111</v>
@@ -9523,7 +9169,7 @@
         <v>0</v>
       </c>
       <c r="H128" s="4" t="s">
-        <v>487</v>
+        <v>517</v>
       </c>
       <c r="I128" s="4">
         <v>0</v>
@@ -9532,7 +9178,7 @@
         <v>0</v>
       </c>
       <c r="K128" s="4" t="s">
-        <v>561</v>
+        <v>591</v>
       </c>
       <c r="L128" s="4"/>
       <c r="M128" s="4"/>
@@ -9542,7 +9188,7 @@
         <v>1113</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>564</v>
+        <v>594</v>
       </c>
       <c r="C129" s="4">
         <v>1111</v>
@@ -9556,7 +9202,7 @@
         <v>0</v>
       </c>
       <c r="H129" s="4" t="s">
-        <v>487</v>
+        <v>517</v>
       </c>
       <c r="I129" s="4">
         <v>0</v>
@@ -9565,7 +9211,7 @@
         <v>0</v>
       </c>
       <c r="K129" s="4" t="s">
-        <v>562</v>
+        <v>592</v>
       </c>
       <c r="L129" s="4"/>
       <c r="M129" s="4"/>
@@ -9575,7 +9221,7 @@
         <v>1114</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>581</v>
+        <v>611</v>
       </c>
       <c r="C130" s="7">
         <v>2</v>
@@ -9584,16 +9230,16 @@
         <v>1</v>
       </c>
       <c r="E130" s="7" t="s">
-        <v>651</v>
+        <v>682</v>
       </c>
       <c r="F130" s="7" t="s">
-        <v>577</v>
+        <v>607</v>
       </c>
       <c r="G130" s="7">
         <v>0</v>
       </c>
       <c r="H130" s="7" t="s">
-        <v>493</v>
+        <v>523</v>
       </c>
       <c r="I130" s="7">
         <v>0</v>
@@ -9602,14 +9248,14 @@
         <v>0</v>
       </c>
       <c r="K130" s="7" t="s">
-        <v>578</v>
+        <v>608</v>
       </c>
       <c r="L130" s="7" t="s">
-        <v>494</v>
+        <v>524</v>
       </c>
       <c r="M130" s="7"/>
       <c r="N130" t="s">
-        <v>588</v>
+        <v>618</v>
       </c>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.2">
@@ -9617,7 +9263,7 @@
         <v>1115</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>582</v>
+        <v>612</v>
       </c>
       <c r="C131" s="7">
         <v>1114</v>
@@ -9631,7 +9277,7 @@
         <v>0</v>
       </c>
       <c r="H131" s="7" t="s">
-        <v>487</v>
+        <v>517</v>
       </c>
       <c r="I131" s="7">
         <v>0</v>
@@ -9640,7 +9286,7 @@
         <v>0</v>
       </c>
       <c r="K131" s="7" t="s">
-        <v>580</v>
+        <v>610</v>
       </c>
       <c r="L131" s="7"/>
       <c r="M131" s="7"/>
@@ -9650,7 +9296,7 @@
         <v>1116</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>583</v>
+        <v>613</v>
       </c>
       <c r="C132" s="7">
         <v>1114</v>
@@ -9664,7 +9310,7 @@
         <v>0</v>
       </c>
       <c r="H132" s="7" t="s">
-        <v>487</v>
+        <v>517</v>
       </c>
       <c r="I132" s="7">
         <v>0</v>
@@ -9673,7 +9319,7 @@
         <v>0</v>
       </c>
       <c r="K132" s="7" t="s">
-        <v>579</v>
+        <v>609</v>
       </c>
       <c r="L132" s="7"/>
       <c r="M132" s="7"/>
@@ -9683,7 +9329,7 @@
         <v>1093</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>641</v>
+        <v>672</v>
       </c>
       <c r="C133" s="4">
         <v>0</v>
@@ -9692,10 +9338,10 @@
         <v>999</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>642</v>
+        <v>673</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>643</v>
+        <v>674</v>
       </c>
       <c r="G133" s="4">
         <v>0</v>
@@ -9710,10 +9356,10 @@
         <v>1</v>
       </c>
       <c r="K133" s="4" t="s">
-        <v>644</v>
+        <v>675</v>
       </c>
       <c r="L133" s="4" t="s">
-        <v>645</v>
+        <v>676</v>
       </c>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.2">
@@ -9746,7 +9392,7 @@
         <v>0</v>
       </c>
       <c r="K134" s="4" t="s">
-        <v>646</v>
+        <v>677</v>
       </c>
       <c r="L134" s="4"/>
     </row>
@@ -9780,7 +9426,7 @@
         <v>0</v>
       </c>
       <c r="K135" s="4" t="s">
-        <v>647</v>
+        <v>678</v>
       </c>
       <c r="L135" s="4"/>
     </row>
@@ -9814,7 +9460,7 @@
         <v>0</v>
       </c>
       <c r="K136" s="4" t="s">
-        <v>648</v>
+        <v>679</v>
       </c>
       <c r="L136" s="4"/>
     </row>
@@ -9848,7 +9494,7 @@
         <v>0</v>
       </c>
       <c r="K137" s="4" t="s">
-        <v>649</v>
+        <v>680</v>
       </c>
       <c r="L137" s="4"/>
     </row>
@@ -9882,7 +9528,7 @@
         <v>0</v>
       </c>
       <c r="K138" s="4" t="s">
-        <v>650</v>
+        <v>681</v>
       </c>
       <c r="L138" s="4"/>
     </row>
@@ -9891,7 +9537,7 @@
         <v>1117</v>
       </c>
       <c r="B139" s="15" t="s">
-        <v>656</v>
+        <v>687</v>
       </c>
       <c r="C139" s="15">
         <v>118</v>
@@ -9900,10 +9546,10 @@
         <v>999</v>
       </c>
       <c r="E139" s="15" t="s">
-        <v>667</v>
+        <v>698</v>
       </c>
       <c r="F139" s="16" t="s">
-        <v>663</v>
+        <v>694</v>
       </c>
       <c r="G139" s="15">
         <v>0</v>
@@ -9918,10 +9564,10 @@
         <v>0</v>
       </c>
       <c r="K139" s="15" t="s">
-        <v>657</v>
+        <v>688</v>
       </c>
       <c r="L139" s="15" t="s">
-        <v>539</v>
+        <v>569</v>
       </c>
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.2">
@@ -9954,7 +9600,7 @@
         <v>0</v>
       </c>
       <c r="K140" s="15" t="s">
-        <v>658</v>
+        <v>689</v>
       </c>
       <c r="L140" s="15"/>
     </row>
@@ -9988,7 +9634,7 @@
         <v>0</v>
       </c>
       <c r="K141" s="15" t="s">
-        <v>659</v>
+        <v>690</v>
       </c>
       <c r="L141" s="15"/>
     </row>
@@ -10022,7 +9668,7 @@
         <v>0</v>
       </c>
       <c r="K142" s="15" t="s">
-        <v>660</v>
+        <v>691</v>
       </c>
       <c r="L142" s="15"/>
     </row>
@@ -10056,7 +9702,7 @@
         <v>0</v>
       </c>
       <c r="K143" s="15" t="s">
-        <v>661</v>
+        <v>692</v>
       </c>
       <c r="L143" s="15"/>
     </row>
@@ -10090,7 +9736,7 @@
         <v>0</v>
       </c>
       <c r="K144" s="15" t="s">
-        <v>662</v>
+        <v>693</v>
       </c>
       <c r="L144" s="15"/>
     </row>
@@ -10132,34 +9778,34 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D1" t="s">
+        <v>712</v>
+      </c>
+      <c r="E1" t="s">
+        <v>314</v>
+      </c>
+      <c r="F1" t="s">
         <v>315</v>
       </c>
-      <c r="B1" t="s">
+      <c r="G1" t="s">
         <v>316</v>
       </c>
-      <c r="C1" t="s">
-        <v>317</v>
-      </c>
-      <c r="D1" t="s">
-        <v>318</v>
-      </c>
-      <c r="E1" t="s">
-        <v>320</v>
-      </c>
-      <c r="F1" t="s">
-        <v>321</v>
-      </c>
-      <c r="G1" t="s">
-        <v>322</v>
-      </c>
       <c r="H1" t="s">
-        <v>292</v>
+        <v>710</v>
       </c>
       <c r="I1" t="s">
-        <v>319</v>
+        <v>711</v>
       </c>
       <c r="J1" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -10167,7 +9813,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -10191,7 +9837,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -10199,10 +9845,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C3" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -10223,7 +9869,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -10231,10 +9877,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>552</v>
+        <v>582</v>
       </c>
       <c r="C4" t="s">
-        <v>549</v>
+        <v>579</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -10255,7 +9901,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="s">
-        <v>552</v>
+        <v>582</v>
       </c>
     </row>
   </sheetData>
@@ -10272,13 +9918,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="B1" t="s">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="C1" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -10497,7 +10143,7 @@
         <v>1084</v>
       </c>
       <c r="C28" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -10508,7 +10154,7 @@
         <v>1085</v>
       </c>
       <c r="C29" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -10519,7 +10165,7 @@
         <v>1086</v>
       </c>
       <c r="C30" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
@@ -10530,7 +10176,7 @@
         <v>1087</v>
       </c>
       <c r="C31" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -10541,7 +10187,7 @@
         <v>1088</v>
       </c>
       <c r="C32" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -10552,7 +10198,7 @@
         <v>1089</v>
       </c>
       <c r="C33" t="s">
-        <v>553</v>
+        <v>583</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -10563,7 +10209,7 @@
         <v>1048</v>
       </c>
       <c r="C34" t="s">
-        <v>554</v>
+        <v>584</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -10574,7 +10220,7 @@
         <v>1049</v>
       </c>
       <c r="C35" t="s">
-        <v>554</v>
+        <v>584</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
@@ -10585,7 +10231,7 @@
         <v>1050</v>
       </c>
       <c r="C36" t="s">
-        <v>554</v>
+        <v>584</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -10596,7 +10242,7 @@
         <v>119</v>
       </c>
       <c r="C37" t="s">
-        <v>554</v>
+        <v>584</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
@@ -10607,7 +10253,7 @@
         <v>3</v>
       </c>
       <c r="C38" t="s">
-        <v>555</v>
+        <v>585</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
@@ -10644,22 +10290,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="B1" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -10667,19 +10313,19 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C2" t="s">
-        <v>678</v>
+        <v>709</v>
       </c>
       <c r="D2" s="12">
         <v>123456</v>
       </c>
       <c r="E2" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F2" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -10687,19 +10333,19 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="C3" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="D3" s="12">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F3" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -10707,19 +10353,19 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C4" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="D4" s="12" t="b">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F4" t="s">
-        <v>637</v>
+        <v>668</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -10727,19 +10373,19 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>628</v>
+        <v>658</v>
       </c>
       <c r="C5" t="s">
-        <v>629</v>
+        <v>659</v>
       </c>
       <c r="D5" s="12">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>456</v>
+        <v>484</v>
       </c>
       <c r="F5" t="s">
-        <v>635</v>
+        <v>666</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -10747,19 +10393,19 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>630</v>
+        <v>660</v>
       </c>
       <c r="C6" t="s">
-        <v>631</v>
+        <v>661</v>
       </c>
       <c r="D6" s="12">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>456</v>
+        <v>484</v>
       </c>
       <c r="F6" t="s">
-        <v>636</v>
+        <v>667</v>
       </c>
     </row>
   </sheetData>
@@ -10775,10 +10421,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>340</v>
+        <v>359</v>
       </c>
       <c r="B1" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -10827,75 +10473,75 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>348</v>
+        <v>367</v>
       </c>
       <c r="B1" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="C1" t="s">
-        <v>351</v>
+        <v>370</v>
       </c>
       <c r="D1" t="s">
-        <v>352</v>
+        <v>371</v>
       </c>
       <c r="E1" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="F1" t="s">
-        <v>354</v>
+        <v>373</v>
       </c>
       <c r="G1" t="s">
-        <v>355</v>
+        <v>374</v>
       </c>
       <c r="H1" t="s">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="I1" t="s">
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="J1" t="s">
-        <v>358</v>
+        <v>377</v>
       </c>
       <c r="K1" t="s">
-        <v>359</v>
+        <v>378</v>
       </c>
       <c r="L1" t="s">
-        <v>360</v>
+        <v>379</v>
       </c>
       <c r="M1" t="s">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="N1" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="O1" t="s">
-        <v>363</v>
+        <v>382</v>
       </c>
       <c r="P1" t="s">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="Q1" t="s">
-        <v>365</v>
+        <v>384</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="B2" t="s">
-        <v>343</v>
+        <v>362</v>
       </c>
       <c r="C2" t="s">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="D2" t="s">
-        <v>345</v>
+        <v>364</v>
       </c>
       <c r="E2" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="F2" t="s">
-        <v>347</v>
+        <v>366</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -10927,1129 +10573,247 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F9C4135-AFDC-4222-9830-710D942A3AED}">
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="4" width="14.375" customWidth="1"/>
+    <col min="3" max="3" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="B1" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="C1" t="s">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="D1" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="E1" t="s">
-        <v>339</v>
-      </c>
-      <c r="F1" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>705</v>
+        <v>330</v>
       </c>
       <c r="C2" t="s">
-        <v>718</v>
-      </c>
-      <c r="D2" t="s">
-        <v>719</v>
+        <v>331</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>706</v>
+        <v>332</v>
       </c>
       <c r="C3" t="s">
-        <v>718</v>
-      </c>
-      <c r="D3" t="s">
-        <v>720</v>
+        <v>333</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>707</v>
+        <v>334</v>
       </c>
       <c r="C4" t="s">
-        <v>718</v>
-      </c>
-      <c r="D4" t="s">
-        <v>722</v>
+        <v>335</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>708</v>
+        <v>336</v>
       </c>
       <c r="C5" t="s">
-        <v>718</v>
-      </c>
-      <c r="D5" t="s">
-        <v>721</v>
+        <v>337</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>709</v>
+        <v>338</v>
       </c>
       <c r="C6" t="s">
-        <v>723</v>
-      </c>
-      <c r="D6" t="s">
-        <v>719</v>
+        <v>339</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>710</v>
+        <v>340</v>
       </c>
       <c r="C7" t="s">
-        <v>723</v>
-      </c>
-      <c r="D7" t="s">
-        <v>720</v>
+        <v>341</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>711</v>
+        <v>342</v>
       </c>
       <c r="C8" t="s">
-        <v>723</v>
-      </c>
-      <c r="D8" t="s">
-        <v>722</v>
+        <v>343</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>712</v>
+        <v>344</v>
       </c>
       <c r="C9" t="s">
-        <v>723</v>
-      </c>
-      <c r="D9" t="s">
-        <v>721</v>
+        <v>345</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>713</v>
+        <v>346</v>
       </c>
       <c r="C10" t="s">
-        <v>724</v>
-      </c>
-      <c r="D10" t="s">
-        <v>719</v>
+        <v>347</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>714</v>
+        <v>348</v>
       </c>
       <c r="C11" t="s">
-        <v>724</v>
-      </c>
-      <c r="D11" t="s">
-        <v>720</v>
+        <v>349</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>715</v>
+        <v>350</v>
       </c>
       <c r="C12" t="s">
-        <v>724</v>
-      </c>
-      <c r="D12" t="s">
-        <v>722</v>
+        <v>351</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>716</v>
+        <v>352</v>
       </c>
       <c r="C13" t="s">
-        <v>724</v>
-      </c>
-      <c r="D13" t="s">
-        <v>721</v>
+        <v>353</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>717</v>
+        <v>354</v>
       </c>
       <c r="C14" t="s">
-        <v>751</v>
-      </c>
-      <c r="D14" t="s">
-        <v>721</v>
+        <v>355</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>763</v>
-      </c>
-      <c r="C15" t="s">
-        <v>752</v>
-      </c>
-      <c r="D15" t="s">
-        <v>721</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>764</v>
-      </c>
-      <c r="C16" t="s">
-        <v>753</v>
-      </c>
-      <c r="D16" t="s">
-        <v>721</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>765</v>
-      </c>
-      <c r="C17" t="s">
-        <v>754</v>
-      </c>
-      <c r="D17" t="s">
-        <v>721</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>766</v>
-      </c>
-      <c r="C18" t="s">
-        <v>755</v>
-      </c>
-      <c r="D18" t="s">
-        <v>721</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>767</v>
-      </c>
-      <c r="C19" t="s">
-        <v>756</v>
-      </c>
-      <c r="D19" t="s">
-        <v>721</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>768</v>
-      </c>
-      <c r="C20" t="s">
-        <v>757</v>
-      </c>
-      <c r="D20" t="s">
-        <v>721</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>769</v>
-      </c>
-      <c r="C21" t="s">
-        <v>758</v>
-      </c>
-      <c r="D21" t="s">
-        <v>721</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>770</v>
-      </c>
-      <c r="C22" t="s">
-        <v>759</v>
-      </c>
-      <c r="D22" t="s">
-        <v>721</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>771</v>
-      </c>
-      <c r="C23" t="s">
-        <v>760</v>
-      </c>
-      <c r="D23" t="s">
-        <v>721</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>772</v>
-      </c>
-      <c r="C24" t="s">
-        <v>761</v>
-      </c>
-      <c r="D24" t="s">
-        <v>721</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25" t="s">
-        <v>773</v>
-      </c>
-      <c r="C25" t="s">
-        <v>762</v>
-      </c>
-      <c r="D25" t="s">
-        <v>721</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="s">
-        <v>725</v>
-      </c>
-      <c r="C26" t="s">
-        <v>745</v>
-      </c>
-      <c r="D26" t="s">
-        <v>722</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27" t="s">
-        <v>726</v>
-      </c>
-      <c r="C27" t="s">
-        <v>745</v>
-      </c>
-      <c r="D27" t="s">
-        <v>721</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" t="s">
-        <v>727</v>
-      </c>
-      <c r="C28" t="s">
-        <v>746</v>
-      </c>
-      <c r="D28" t="s">
-        <v>719</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29" t="s">
-        <v>728</v>
-      </c>
-      <c r="C29" t="s">
-        <v>746</v>
-      </c>
-      <c r="D29" t="s">
-        <v>720</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30" t="s">
-        <v>729</v>
-      </c>
-      <c r="C30" t="s">
-        <v>746</v>
-      </c>
-      <c r="D30" t="s">
-        <v>722</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31" t="s">
-        <v>730</v>
-      </c>
-      <c r="C31" t="s">
-        <v>746</v>
-      </c>
-      <c r="D31" t="s">
-        <v>721</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-      <c r="F31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32" t="s">
-        <v>731</v>
-      </c>
-      <c r="C32" t="s">
-        <v>747</v>
-      </c>
-      <c r="D32" t="s">
-        <v>719</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-      <c r="F32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="s">
-        <v>732</v>
-      </c>
-      <c r="C33" t="s">
-        <v>747</v>
-      </c>
-      <c r="D33" t="s">
-        <v>720</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-      <c r="F33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="s">
-        <v>733</v>
-      </c>
-      <c r="C34" t="s">
-        <v>747</v>
-      </c>
-      <c r="D34" t="s">
-        <v>722</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-      <c r="F34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35" t="s">
-        <v>734</v>
-      </c>
-      <c r="C35" t="s">
-        <v>747</v>
-      </c>
-      <c r="D35" t="s">
-        <v>721</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-      <c r="F35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" t="s">
-        <v>735</v>
-      </c>
-      <c r="C36" t="s">
-        <v>748</v>
-      </c>
-      <c r="D36" t="s">
-        <v>719</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-      <c r="F36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37" t="s">
-        <v>736</v>
-      </c>
-      <c r="C37" t="s">
-        <v>748</v>
-      </c>
-      <c r="D37" t="s">
-        <v>720</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-      <c r="F37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="s">
-        <v>737</v>
-      </c>
-      <c r="C38" t="s">
-        <v>748</v>
-      </c>
-      <c r="D38" t="s">
-        <v>722</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-      <c r="F38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="s">
-        <v>738</v>
-      </c>
-      <c r="C39" t="s">
-        <v>748</v>
-      </c>
-      <c r="D39" t="s">
-        <v>721</v>
-      </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-      <c r="F39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="s">
-        <v>739</v>
-      </c>
-      <c r="C40" t="s">
-        <v>749</v>
-      </c>
-      <c r="D40" t="s">
-        <v>719</v>
-      </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
-      <c r="F40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="s">
-        <v>740</v>
-      </c>
-      <c r="C41" t="s">
-        <v>749</v>
-      </c>
-      <c r="D41" t="s">
-        <v>720</v>
-      </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
-      <c r="F41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="s">
-        <v>741</v>
-      </c>
-      <c r="C42" t="s">
-        <v>749</v>
-      </c>
-      <c r="D42" t="s">
-        <v>722</v>
-      </c>
-      <c r="E42">
-        <v>0</v>
-      </c>
-      <c r="F42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="s">
-        <v>742</v>
-      </c>
-      <c r="C43" t="s">
-        <v>749</v>
-      </c>
-      <c r="D43" t="s">
-        <v>721</v>
-      </c>
-      <c r="E43">
-        <v>0</v>
-      </c>
-      <c r="F43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" t="s">
-        <v>743</v>
-      </c>
-      <c r="C44" t="s">
-        <v>750</v>
-      </c>
-      <c r="D44" t="s">
-        <v>722</v>
-      </c>
-      <c r="E44">
-        <v>0</v>
-      </c>
-      <c r="F44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45" t="s">
-        <v>744</v>
-      </c>
-      <c r="C45" t="s">
-        <v>750</v>
-      </c>
-      <c r="D45" t="s">
-        <v>721</v>
-      </c>
-      <c r="E45">
-        <v>0</v>
-      </c>
-      <c r="F45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46" t="s">
-        <v>774</v>
-      </c>
-      <c r="C46" t="s">
-        <v>775</v>
-      </c>
-      <c r="D46" t="s">
-        <v>720</v>
-      </c>
-      <c r="E46">
-        <v>0</v>
-      </c>
-      <c r="F46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="s">
-        <v>776</v>
-      </c>
-      <c r="C47" t="s">
-        <v>775</v>
-      </c>
-      <c r="D47" t="s">
-        <v>722</v>
-      </c>
-      <c r="E47">
-        <v>0</v>
-      </c>
-      <c r="F47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="s">
-        <v>777</v>
-      </c>
-      <c r="C48" t="s">
-        <v>775</v>
-      </c>
-      <c r="D48" t="s">
-        <v>721</v>
-      </c>
-      <c r="E48">
-        <v>0</v>
-      </c>
-      <c r="F48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="s">
-        <v>780</v>
-      </c>
-      <c r="C49" t="s">
-        <v>778</v>
-      </c>
-      <c r="D49" t="s">
-        <v>722</v>
-      </c>
-      <c r="E49">
-        <v>0</v>
-      </c>
-      <c r="F49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="s">
-        <v>781</v>
-      </c>
-      <c r="C50" t="s">
-        <v>779</v>
-      </c>
-      <c r="D50" t="s">
-        <v>721</v>
-      </c>
-      <c r="E50">
-        <v>0</v>
-      </c>
-      <c r="F50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="s">
-        <v>785</v>
-      </c>
-      <c r="C51" t="s">
-        <v>782</v>
-      </c>
-      <c r="D51" t="s">
-        <v>720</v>
-      </c>
-      <c r="E51">
-        <v>0</v>
-      </c>
-      <c r="F51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="s">
-        <v>786</v>
-      </c>
-      <c r="C52" t="s">
-        <v>783</v>
-      </c>
-      <c r="D52" t="s">
-        <v>722</v>
-      </c>
-      <c r="E52">
-        <v>0</v>
-      </c>
-      <c r="F52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="s">
-        <v>787</v>
-      </c>
-      <c r="C53" t="s">
-        <v>784</v>
-      </c>
-      <c r="D53" t="s">
-        <v>721</v>
-      </c>
-      <c r="E53">
-        <v>0</v>
-      </c>
-      <c r="F53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="s">
-        <v>791</v>
-      </c>
-      <c r="C54" t="s">
-        <v>788</v>
-      </c>
-      <c r="D54" t="s">
-        <v>720</v>
-      </c>
-      <c r="E54">
-        <v>0</v>
-      </c>
-      <c r="F54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="s">
-        <v>792</v>
-      </c>
-      <c r="C55" t="s">
-        <v>789</v>
-      </c>
-      <c r="D55" t="s">
-        <v>722</v>
-      </c>
-      <c r="E55">
-        <v>0</v>
-      </c>
-      <c r="F55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="s">
-        <v>793</v>
-      </c>
-      <c r="C56" t="s">
-        <v>790</v>
-      </c>
-      <c r="D56" t="s">
-        <v>721</v>
-      </c>
-      <c r="E56">
-        <v>0</v>
-      </c>
-      <c r="F56">
         <v>0</v>
       </c>
     </row>
@@ -12061,480 +10825,394 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3DA66D3-8315-4018-BF52-5D786631F136}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" customWidth="1"/>
-    <col min="4" max="4" width="19.25" customWidth="1"/>
-    <col min="5" max="6" width="8.875" style="3"/>
-    <col min="7" max="7" width="17.5" customWidth="1"/>
-    <col min="8" max="8" width="70.625" customWidth="1"/>
+    <col min="2" max="2" width="13.625" customWidth="1"/>
+    <col min="3" max="3" width="19.25" customWidth="1"/>
+    <col min="4" max="5" width="8.875" style="3"/>
+    <col min="6" max="6" width="17.5" customWidth="1"/>
+    <col min="7" max="7" width="70.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>451</v>
+        <v>479</v>
       </c>
       <c r="B1" t="s">
-        <v>682</v>
+        <v>480</v>
       </c>
       <c r="C1" t="s">
-        <v>452</v>
+        <v>481</v>
       </c>
       <c r="D1" t="s">
-        <v>453</v>
+        <v>710</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>680</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>454</v>
+        <v>482</v>
+      </c>
+      <c r="F1" t="s">
+        <v>307</v>
       </c>
       <c r="G1" t="s">
-        <v>311</v>
-      </c>
-      <c r="H1" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>0</v>
+      <c r="B2" t="s">
+        <v>385</v>
       </c>
       <c r="C2" t="s">
-        <v>527</v>
-      </c>
-      <c r="D2" t="s">
-        <v>528</v>
-      </c>
-      <c r="E2" s="3">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="G2" t="s">
-        <v>529</v>
-      </c>
-      <c r="H2" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+        <v>386</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="F2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>0</v>
+      <c r="B3" t="s">
+        <v>388</v>
       </c>
       <c r="C3" t="s">
-        <v>639</v>
-      </c>
-      <c r="D3" t="s">
-        <v>655</v>
-      </c>
-      <c r="E3" s="3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+        <v>389</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="F3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>0</v>
+      <c r="B4" t="s">
+        <v>391</v>
       </c>
       <c r="C4" t="s">
-        <v>633</v>
-      </c>
-      <c r="D4" t="s">
-        <v>698</v>
-      </c>
-      <c r="E4" s="3">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+        <v>392</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="F4" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>0</v>
+      <c r="B5" t="s">
+        <v>394</v>
       </c>
       <c r="C5" t="s">
-        <v>389</v>
-      </c>
-      <c r="D5" t="s">
-        <v>696</v>
-      </c>
-      <c r="E5" s="3">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+        <v>395</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="F5" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>0</v>
+      <c r="B6" t="s">
+        <v>397</v>
       </c>
       <c r="C6" t="s">
-        <v>604</v>
-      </c>
-      <c r="D6" t="s">
-        <v>606</v>
-      </c>
-      <c r="E6" s="3">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="G6" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+        <v>398</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="F6" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>0</v>
+      <c r="B7" t="s">
+        <v>400</v>
       </c>
       <c r="C7" t="s">
-        <v>668</v>
-      </c>
-      <c r="D7" t="s">
-        <v>669</v>
-      </c>
-      <c r="E7" s="3">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="G7" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+        <v>401</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="F7" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8">
-        <v>0</v>
+      <c r="B8" t="s">
+        <v>403</v>
       </c>
       <c r="C8" t="s">
-        <v>386</v>
-      </c>
-      <c r="D8" t="s">
-        <v>387</v>
-      </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="G8" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+        <v>404</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="F8" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9">
-        <v>1</v>
+      <c r="B9" t="s">
+        <v>406</v>
       </c>
       <c r="C9" t="s">
-        <v>699</v>
-      </c>
-      <c r="D9" t="s">
-        <v>700</v>
-      </c>
-      <c r="E9" s="3">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="G9" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+        <v>407</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="F9" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10">
-        <v>0</v>
+      <c r="B10" t="s">
+        <v>409</v>
       </c>
       <c r="C10" t="s">
-        <v>366</v>
-      </c>
-      <c r="D10" t="s">
-        <v>686</v>
-      </c>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="G10" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+        <v>410</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="F10" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11">
-        <v>0</v>
+      <c r="B11" t="s">
+        <v>412</v>
       </c>
       <c r="C11" t="s">
-        <v>683</v>
-      </c>
-      <c r="D11" t="s">
-        <v>391</v>
-      </c>
-      <c r="E11" s="3">
-        <v>0</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="G11" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="F11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12">
-        <v>0</v>
+      <c r="B12" t="s">
+        <v>415</v>
       </c>
       <c r="C12" t="s">
-        <v>368</v>
-      </c>
-      <c r="D12" t="s">
-        <v>689</v>
-      </c>
-      <c r="E12" s="3">
-        <v>0</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="G12" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+        <v>416</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13">
-        <v>0</v>
+      <c r="B13" t="s">
+        <v>417</v>
       </c>
       <c r="C13" t="s">
-        <v>690</v>
-      </c>
-      <c r="D13" t="s">
-        <v>687</v>
-      </c>
-      <c r="E13" s="3">
-        <v>0</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="G13" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+        <v>418</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="F13" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14">
-        <v>0</v>
+      <c r="B14" t="s">
+        <v>506</v>
       </c>
       <c r="C14" t="s">
-        <v>691</v>
-      </c>
-      <c r="D14" t="s">
-        <v>692</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="G14" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+        <v>508</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="F14" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15">
-        <v>0</v>
+      <c r="B15" t="s">
+        <v>557</v>
       </c>
       <c r="C15" t="s">
-        <v>380</v>
-      </c>
-      <c r="D15" t="s">
-        <v>381</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>323</v>
+        <v>558</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="F15" t="s">
+        <v>559</v>
       </c>
       <c r="G15" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16">
-        <v>0</v>
+      <c r="B16" t="s">
+        <v>634</v>
       </c>
       <c r="C16" t="s">
-        <v>377</v>
-      </c>
-      <c r="D16" t="s">
-        <v>378</v>
-      </c>
-      <c r="E16" s="3">
-        <v>0</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="G16" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+        <v>636</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="F16" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17">
-        <v>0</v>
+      <c r="B17" t="s">
+        <v>663</v>
       </c>
       <c r="C17" t="s">
-        <v>383</v>
-      </c>
-      <c r="D17" t="s">
-        <v>384</v>
-      </c>
-      <c r="E17" s="3">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="G17" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+        <v>664</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18">
-        <v>0</v>
+      <c r="B18" t="s">
+        <v>670</v>
       </c>
       <c r="C18" t="s">
-        <v>374</v>
-      </c>
-      <c r="D18" t="s">
-        <v>693</v>
-      </c>
-      <c r="E18" s="3">
-        <v>0</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="G18" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+        <v>686</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19">
-        <v>0</v>
+      <c r="B19" t="s">
+        <v>699</v>
       </c>
       <c r="C19" t="s">
-        <v>372</v>
-      </c>
-      <c r="D19" t="s">
-        <v>694</v>
-      </c>
-      <c r="E19" s="3">
-        <v>0</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="G19" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20" t="s">
-        <v>478</v>
-      </c>
-      <c r="D20" t="s">
-        <v>695</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="G20" t="s">
-        <v>479</v>
+        <v>700</v>
+      </c>
+      <c r="D19" s="3">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="F19" t="s">
+        <v>701</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{D3DA66D3-8315-4018-BF52-5D786631F136}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H20">
-      <sortCondition ref="D1"/>
-    </sortState>
-  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
